--- a/vystupy/grafy/2026-10-21-dip-model.xlsx
+++ b/vystupy/grafy/2026-10-21-dip-model.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="71">
   <si>
     <t xml:space="preserve">Model DIP – předpoklady</t>
   </si>
@@ -70,7 +70,13 @@
     <t xml:space="preserve">Sleva na poplatku za fixaci (mimo DIP)</t>
   </si>
   <si>
-    <t xml:space="preserve">Zadání: investice mimo DIP s fixací se slevou 40 % (Program pro dlouhodobé investory; 40 % odpovídá fixaci na 15 let).</t>
+    <t xml:space="preserve">Zadání: investice mimo DIP s fixací se slevou 40 % (Program pro dlouhodobé investory; 40 % odpovídá fixaci na 15 let). Platí pro horizonty 20 a 30 let.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sleva na poplatku za fixaci – 10letý horizont</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zadání: u 10letého horizontu je poplatek mimo DIP s fixací 0,7 % ročně = 1 % × (1 − 30 %); s objemem klesá stejně jako u 40% slevy.</t>
   </si>
   <si>
     <t xml:space="preserve">Měsíční výnos (odvozený)</t>
@@ -97,7 +103,10 @@
     <t xml:space="preserve">Sazba ročně</t>
   </si>
   <si>
-    <t xml:space="preserve">Sazba po slevě za fixaci</t>
+    <t xml:space="preserve">Po slevě (20 a 30 let)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Po slevě (10 let)</t>
   </si>
   <si>
     <t xml:space="preserve">Zdroj: Portu magazín, Nový sazebník Portu (23. 4. 2024, platí od 1. 5. 2024), https://magazin.portu.cz/novy-sazebnik-portu-je-jednodussi-a-umoznuje-investovat-levneji/ – sazba pásma platí na celý majetek; poplatek účtovaný měsíčně (1/12 z hodnoty majetku).</t>
@@ -200,6 +209,30 @@
   </si>
   <si>
     <t xml:space="preserve">Poplatky DIP kumulovaně</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bez DIP (10 let): hodnota před poplatkem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bez DIP (10 let): sazba poplatku ročně</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bez DIP s fixací (10 let): hodnota (konec měsíce)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poplatky bez DIP (10 let) kumulovaně</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bez DIP s fixací (sleva pro 10 let)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Výhoda DIP oproti fixaci (10 let)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Výhoda DIP s reinvestováním (10 let)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poplatky bez DIP kumulovaně (10 let)</t>
   </si>
   <si>
     <t xml:space="preserve">Hodnoty ke konci roku. Daňová úspora za právě skončený rok je započtená jako nárok (vrací se v dubnu dalšího roku).</t>
@@ -691,7 +724,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -786,21 +819,32 @@
         <v>15</v>
       </c>
     </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B12" s="9" t="n">
         <f aca="false">(1+B5)^(1/12)-1</f>
         <v>0.00565414538740527</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B13" s="10" t="n">
         <f aca="false">B4*12</f>
@@ -810,30 +854,33 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B14" s="10" t="n">
         <f aca="false">MIN(B13,B6)*B7</f>
         <v>7200</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -847,6 +894,10 @@
         <f aca="false">B18*(1-$B$10)</f>
         <v>0.006</v>
       </c>
+      <c r="D18" s="13" t="n">
+        <f aca="false">B18*(1-$B$11)</f>
+        <v>0.007</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="n">
@@ -859,6 +910,10 @@
         <f aca="false">B19*(1-$B$10)</f>
         <v>0.0048</v>
       </c>
+      <c r="D19" s="13" t="n">
+        <f aca="false">B19*(1-$B$11)</f>
+        <v>0.0056</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="n">
@@ -871,6 +926,10 @@
         <f aca="false">B20*(1-$B$10)</f>
         <v>0.0036</v>
       </c>
+      <c r="D20" s="13" t="n">
+        <f aca="false">B20*(1-$B$11)</f>
+        <v>0.0042</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="n">
@@ -883,64 +942,68 @@
         <f aca="false">B21*(1-$B$10)</f>
         <v>0.0024</v>
       </c>
+      <c r="D21" s="13" t="n">
+        <f aca="false">B21*(1-$B$11)</f>
+        <v>0.0028</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -974,39 +1037,39 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1018,8 +1081,8 @@
         <v>480000</v>
       </c>
       <c r="C4" s="17" t="n">
-        <f aca="false">INDEX(Roky!$D$2:$D$32,A4+1)</f>
-        <v>666911.806161402</v>
+        <f aca="false">INDEX(Roky!$K$2:$K$32,A4+1)</f>
+        <v>663465.751335199</v>
       </c>
       <c r="D4" s="17" t="n">
         <f aca="false">INDEX(Roky!$E$2:$E$32,A4+1)</f>
@@ -1030,16 +1093,16 @@
         <v>772682.573169316</v>
       </c>
       <c r="F4" s="17" t="n">
-        <f aca="false">INDEX(Roky!$G$2:$G$32,A4+1)</f>
-        <v>81721.5932801222</v>
+        <f aca="false">INDEX(Roky!$L$2:$L$32,A4+1)</f>
+        <v>85167.6481063255</v>
       </c>
       <c r="G4" s="17" t="n">
-        <f aca="false">INDEX(Roky!$H$2:$H$32,A4+1)</f>
-        <v>105770.767007914</v>
+        <f aca="false">INDEX(Roky!$M$2:$M$32,A4+1)</f>
+        <v>109216.821834118</v>
       </c>
       <c r="H4" s="17" t="n">
-        <f aca="false">INDEX(Roky!$I$2:$I$32,A4+1)</f>
-        <v>16705.5469582312</v>
+        <f aca="false">INDEX(Roky!$N$2:$N$32,A4+1)</f>
+        <v>19421.8189220149</v>
       </c>
       <c r="I4" s="17" t="n">
         <f aca="false">INDEX(Roky!$J$2:$J$32,A4+1)</f>
@@ -1134,7 +1197,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1153,7 +1216,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L361"/>
+  <dimension ref="A1:P361"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -1166,44 +1229,60 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J1" s="15" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K1" s="15" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L1" s="15" t="s">
-        <v>58</v>
+        <v>61</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="P1" s="15" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1254,6 +1333,22 @@
         <f aca="false">0+((0+C2)+0)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>1.00565414538741</v>
       </c>
+      <c r="M2" s="19" t="n">
+        <f aca="false">(0+C2)*(1+Předpoklady!$B$12)</f>
+        <v>4022.61658154962</v>
+      </c>
+      <c r="N2" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M2,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O2" s="19" t="n">
+        <f aca="false">M2*(1-N2/12)</f>
+        <v>4020.27005521038</v>
+      </c>
+      <c r="P2" s="19" t="n">
+        <f aca="false">0+M2*N2/12</f>
+        <v>2.34652633923728</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="n">
@@ -1303,6 +1398,22 @@
         <f aca="false">L2+((G2+C3)+J2)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>3.02239571584465</v>
       </c>
+      <c r="M3" s="19" t="n">
+        <f aca="false">(O2+C3)*(1+Předpoklady!$B$12)</f>
+        <v>8065.6178281488</v>
+      </c>
+      <c r="N3" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M3,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O3" s="19" t="n">
+        <f aca="false">M3*(1-N3/12)</f>
+        <v>8060.91288441571</v>
+      </c>
+      <c r="P3" s="19" t="n">
+        <f aca="false">P2+M3*N3/12</f>
+        <v>7.05147007232408</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="n">
@@ -1352,6 +1463,22 @@
         <f aca="false">L3+((G3+C4)+J3)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>6.05568734560736</v>
       </c>
+      <c r="M4" s="19" t="n">
+        <f aca="false">(O3+C4)*(1+Předpoklady!$B$12)</f>
+        <v>12129.107039369</v>
+      </c>
+      <c r="N4" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M4,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O4" s="19" t="n">
+        <f aca="false">M4*(1-N4/12)</f>
+        <v>12122.0317269294</v>
+      </c>
+      <c r="P4" s="19" t="n">
+        <f aca="false">P3+M4*N4/12</f>
+        <v>14.126782511956</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="n">
@@ -1401,6 +1528,22 @@
         <f aca="false">L4+((G4+C5)+J4)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>10.1110211820591</v>
       </c>
+      <c r="M5" s="19" t="n">
+        <f aca="false">(O4+C5)*(1+Předpoklady!$B$12)</f>
+        <v>16213.1880382538</v>
+      </c>
+      <c r="N5" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M5,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O5" s="19" t="n">
+        <f aca="false">M5*(1-N5/12)</f>
+        <v>16203.7303452315</v>
+      </c>
+      <c r="P5" s="19" t="n">
+        <f aca="false">P4+M5*N5/12</f>
+        <v>23.5844755342707</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="n">
@@ -1450,6 +1593,22 @@
         <f aca="false">L5+((G5+C6)+J5)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>15.1939190451832</v>
       </c>
+      <c r="M6" s="19" t="n">
+        <f aca="false">(O5+C6)*(1+Předpoklady!$B$12)</f>
+        <v>20317.9651739714</v>
+      </c>
+      <c r="N6" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M6,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O6" s="19" t="n">
+        <f aca="false">M6*(1-N6/12)</f>
+        <v>20306.1130276199</v>
+      </c>
+      <c r="P6" s="19" t="n">
+        <f aca="false">P5+M6*N6/12</f>
+        <v>35.436621885754</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="n">
@@ -1499,6 +1658,22 @@
         <f aca="false">L6+((G6+C7)+J6)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>21.3099325878755</v>
       </c>
+      <c r="M7" s="19" t="n">
+        <f aca="false">(O6+C7)*(1+Předpoklady!$B$12)</f>
+        <v>24443.5433244808</v>
+      </c>
+      <c r="N7" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M7,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O7" s="19" t="n">
+        <f aca="false">M7*(1-N7/12)</f>
+        <v>24429.2845908748</v>
+      </c>
+      <c r="P7" s="19" t="n">
+        <f aca="false">P6+M7*N7/12</f>
+        <v>49.6953554917011</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="n">
@@ -1548,6 +1723,22 @@
         <f aca="false">L7+((G7+C8)+J7)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>28.4646434571237</v>
       </c>
+      <c r="M8" s="19" t="n">
+        <f aca="false">(O7+C8)*(1+Předpoklady!$B$12)</f>
+        <v>28590.0278992115</v>
+      </c>
+      <c r="N8" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M8,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O8" s="19" t="n">
+        <f aca="false">M8*(1-N8/12)</f>
+        <v>28573.350382937</v>
+      </c>
+      <c r="P8" s="19" t="n">
+        <f aca="false">P7+M8*N8/12</f>
+        <v>66.3728717662412</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="n">
@@ -1597,6 +1788,22 @@
         <f aca="false">L8+((G8+C9)+J8)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>36.6636634560578</v>
       </c>
+      <c r="M9" s="19" t="n">
+        <f aca="false">(O8+C9)*(1+Předpoklady!$B$12)</f>
+        <v>32757.524841757</v>
+      </c>
+      <c r="N9" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M9,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O9" s="19" t="n">
+        <f aca="false">M9*(1-N9/12)</f>
+        <v>32738.4162855993</v>
+      </c>
+      <c r="P9" s="19" t="n">
+        <f aca="false">P8+M9*N9/12</f>
+        <v>85.4814279239328</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="n">
@@ -1646,6 +1853,22 @@
         <f aca="false">L9+((G9+C10)+J9)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>45.912634706875</v>
       </c>
+      <c r="M10" s="19" t="n">
+        <f aca="false">(O9+C10)*(1+Předpoklady!$B$12)</f>
+        <v>36946.1406325811</v>
+      </c>
+      <c r="N10" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M10,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O10" s="19" t="n">
+        <f aca="false">M10*(1-N10/12)</f>
+        <v>36924.5887172121</v>
+      </c>
+      <c r="P10" s="19" t="n">
+        <f aca="false">P9+M10*N10/12</f>
+        <v>107.033343292938</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="n">
@@ -1695,6 +1918,22 @@
         <f aca="false">L10+((G10+C11)+J10)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>56.2172298146459</v>
       </c>
+      <c r="M11" s="19" t="n">
+        <f aca="false">(O10+C11)*(1+Předpoklady!$B$12)</f>
+        <v>41155.982291739</v>
+      </c>
+      <c r="N11" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M11,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O11" s="19" t="n">
+        <f aca="false">M11*(1-N11/12)</f>
+        <v>41131.9746354021</v>
+      </c>
+      <c r="P11" s="19" t="n">
+        <f aca="false">P10+M11*N11/12</f>
+        <v>131.040999629786</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="n">
@@ -1744,6 +1983,22 @@
         <f aca="false">L11+((G11+C12)+J11)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>67.5831520320052</v>
       </c>
+      <c r="M12" s="19" t="n">
+        <f aca="false">(O11+C12)*(1+Předpoklady!$B$12)</f>
+        <v>45387.1573816114</v>
+      </c>
+      <c r="N12" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M12,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O12" s="19" t="n">
+        <f aca="false">M12*(1-N12/12)</f>
+        <v>45360.6815398054</v>
+      </c>
+      <c r="P12" s="19" t="n">
+        <f aca="false">P11+M12*N12/12</f>
+        <v>157.516841435726</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="n">
@@ -1793,6 +2048,22 @@
         <f aca="false">L12+((G12+C13)+J12)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>80.0161354247323</v>
       </c>
+      <c r="M13" s="19" t="n">
+        <f aca="false">(O12+C13)*(1+Předpoklady!$B$12)</f>
+        <v>49639.7740096529</v>
+      </c>
+      <c r="N13" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M13,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O13" s="19" t="n">
+        <f aca="false">M13*(1-N13/12)</f>
+        <v>49610.817474814</v>
+      </c>
+      <c r="P13" s="19" t="n">
+        <f aca="false">P12+M13*N13/12</f>
+        <v>186.47337627469</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="n">
@@ -1842,6 +2113,22 @@
         <f aca="false">L13+((G13+C14)+J13)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>93.5219450382264</v>
       </c>
+      <c r="M14" s="19" t="n">
+        <f aca="false">(O13+C14)*(1+Předpoklady!$B$12)</f>
+        <v>53913.9408311542</v>
+      </c>
+      <c r="N14" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M14,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O14" s="19" t="n">
+        <f aca="false">M14*(1-N14/12)</f>
+        <v>53882.491032336</v>
+      </c>
+      <c r="P14" s="19" t="n">
+        <f aca="false">P13+M14*N14/12</f>
+        <v>217.923175092864</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="n">
@@ -1891,6 +2178,22 @@
         <f aca="false">L14+((G14+C15)+J14)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>108.106377064881</v>
       </c>
+      <c r="M15" s="19" t="n">
+        <f aca="false">(O14+C15)*(1+Předpoklady!$B$12)</f>
+        <v>58209.767052018</v>
+      </c>
+      <c r="N15" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M15,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O15" s="19" t="n">
+        <f aca="false">M15*(1-N15/12)</f>
+        <v>58175.811354571</v>
+      </c>
+      <c r="P15" s="19" t="n">
+        <f aca="false">P14+M15*N15/12</f>
+        <v>251.878872539874</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="n">
@@ -1940,6 +2243,22 @@
         <f aca="false">L15+((G15+C16)+J15)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>123.775259012363</v>
       </c>
+      <c r="M16" s="19" t="n">
+        <f aca="false">(O15+C16)*(1+Předpoklady!$B$12)</f>
+        <v>62527.3624315496</v>
+      </c>
+      <c r="N16" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M16,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O16" s="19" t="n">
+        <f aca="false">M16*(1-N16/12)</f>
+        <v>62490.8881367979</v>
+      </c>
+      <c r="P16" s="19" t="n">
+        <f aca="false">P15+M16*N16/12</f>
+        <v>288.353167291611</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="n">
@@ -1989,6 +2308,22 @@
         <f aca="false">L16+((G16+C17)+J16)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>140.534449872801</v>
       </c>
+      <c r="M17" s="19" t="n">
+        <f aca="false">(O16+C17)*(1+Předpoklady!$B$12)</f>
+        <v>66866.8372852611</v>
+      </c>
+      <c r="N17" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M17,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O17" s="19" t="n">
+        <f aca="false">M17*(1-N17/12)</f>
+        <v>66827.831630178</v>
+      </c>
+      <c r="P17" s="19" t="n">
+        <f aca="false">P16+M17*N17/12</f>
+        <v>327.35882237468</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="n">
@@ -2038,6 +2373,22 @@
         <f aca="false">L17+((G17+C18)+J17)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>160.200017754583</v>
       </c>
+      <c r="M18" s="19" t="n">
+        <f aca="false">(O17+C18)*(1+Předpoklady!$B$12)</f>
+        <v>71228.3024876897</v>
+      </c>
+      <c r="N18" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M18,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O18" s="19" t="n">
+        <f aca="false">M18*(1-N18/12)</f>
+        <v>71186.7526445718</v>
+      </c>
+      <c r="P18" s="19" t="n">
+        <f aca="false">P17+M18*N18/12</f>
+        <v>368.908665492499</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="n">
@@ -2087,6 +2438,22 @@
         <f aca="false">L18+((G18+C19)+J18)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>180.977487571716</v>
       </c>
+      <c r="M19" s="19" t="n">
+        <f aca="false">(O18+C19)*(1+Předpoklady!$B$12)</f>
+        <v>75611.8694752311</v>
+      </c>
+      <c r="N19" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M19,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O19" s="19" t="n">
+        <f aca="false">M19*(1-N19/12)</f>
+        <v>75567.7625513706</v>
+      </c>
+      <c r="P19" s="19" t="n">
+        <f aca="false">P18+M19*N19/12</f>
+        <v>413.015589353051</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="n">
@@ -2136,6 +2503,22 @@
         <f aca="false">L19+((G19+C20)+J19)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>202.872866632202</v>
       </c>
+      <c r="M20" s="19" t="n">
+        <f aca="false">(O19+C20)*(1+Předpoklady!$B$12)</f>
+        <v>80017.6502489866</v>
+      </c>
+      <c r="N20" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M20,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O20" s="19" t="n">
+        <f aca="false">M20*(1-N20/12)</f>
+        <v>79970.9732863413</v>
+      </c>
+      <c r="P20" s="19" t="n">
+        <f aca="false">P19+M20*N20/12</f>
+        <v>459.692551998293</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="18" t="n">
@@ -2185,6 +2568,22 @@
         <f aca="false">L20+((G20+C21)+J20)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>225.892194699917</v>
       </c>
+      <c r="M21" s="19" t="n">
+        <f aca="false">(O20+C21)*(1+Předpoklady!$B$12)</f>
+        <v>84445.7573776242</v>
+      </c>
+      <c r="N21" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M21,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O21" s="19" t="n">
+        <f aca="false">M21*(1-N21/12)</f>
+        <v>84396.4973524873</v>
+      </c>
+      <c r="P21" s="19" t="n">
+        <f aca="false">P20+M21*N21/12</f>
+        <v>508.95257713524</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="18" t="n">
@@ -2234,6 +2633,22 @@
         <f aca="false">L21+((G21+C22)+J21)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>250.041544169961</v>
       </c>
+      <c r="M22" s="19" t="n">
+        <f aca="false">(O21+C22)*(1+Předpoklady!$B$12)</f>
+        <v>88896.3040002556</v>
+      </c>
+      <c r="N22" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M22,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O22" s="19" t="n">
+        <f aca="false">M22*(1-N22/12)</f>
+        <v>88844.4478229221</v>
+      </c>
+      <c r="P22" s="19" t="n">
+        <f aca="false">P21+M22*N22/12</f>
+        <v>560.808754468723</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="18" t="n">
@@ -2283,6 +2698,22 @@
         <f aca="false">L22+((G22+C23)+J22)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>275.327020244956</v>
       </c>
+      <c r="M23" s="19" t="n">
+        <f aca="false">(O22+C23)*(1+Předpoklady!$B$12)</f>
+        <v>93369.4038293263</v>
+      </c>
+      <c r="N23" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M23,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O23" s="19" t="n">
+        <f aca="false">M23*(1-N23/12)</f>
+        <v>93314.9383437592</v>
+      </c>
+      <c r="P23" s="19" t="n">
+        <f aca="false">P22+M23*N23/12</f>
+        <v>615.27424003583</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="18" t="n">
@@ -2332,6 +2763,22 @@
         <f aca="false">L23+((G23+C24)+J23)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>301.754761112298</v>
       </c>
+      <c r="M24" s="19" t="n">
+        <f aca="false">(O23+C24)*(1+Předpoklady!$B$12)</f>
+        <v>97865.1711535212</v>
+      </c>
+      <c r="N24" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M24,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O24" s="19" t="n">
+        <f aca="false">M24*(1-N24/12)</f>
+        <v>97808.0831370149</v>
+      </c>
+      <c r="P24" s="19" t="n">
+        <f aca="false">P23+M24*N24/12</f>
+        <v>672.36225654205</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="18" t="n">
@@ -2381,6 +2828,22 @@
         <f aca="false">L24+((G24+C25)+J24)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>329.330938122363</v>
       </c>
+      <c r="M25" s="19" t="n">
+        <f aca="false">(O24+C25)*(1+Předpoklady!$B$12)</f>
+        <v>102383.720840685</v>
+      </c>
+      <c r="N25" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M25,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O25" s="19" t="n">
+        <f aca="false">M25*(1-N25/12)</f>
+        <v>102323.997003528</v>
+      </c>
+      <c r="P25" s="19" t="n">
+        <f aca="false">P24+M25*N25/12</f>
+        <v>732.086093699116</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="18" t="n">
@@ -2430,6 +2893,22 @@
         <f aca="false">L25+((G25+C26)+J25)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>358.061755967678</v>
       </c>
+      <c r="M26" s="19" t="n">
+        <f aca="false">(O25+C26)*(1+Předpoklady!$B$12)</f>
+        <v>106925.168340756</v>
+      </c>
+      <c r="N26" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M26,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O26" s="19" t="n">
+        <f aca="false">M26*(1-N26/12)</f>
+        <v>106862.79532589</v>
+      </c>
+      <c r="P26" s="19" t="n">
+        <f aca="false">P25+M26*N26/12</f>
+        <v>794.459108564557</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="18" t="n">
@@ -2479,6 +2958,22 @@
         <f aca="false">L26+((G26+C27)+J26)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>387.953452863061</v>
       </c>
+      <c r="M27" s="19" t="n">
+        <f aca="false">(O26+C27)*(1+Předpoklady!$B$12)</f>
+        <v>111489.629688717</v>
+      </c>
+      <c r="N27" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M27,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O27" s="19" t="n">
+        <f aca="false">M27*(1-N27/12)</f>
+        <v>111424.594071398</v>
+      </c>
+      <c r="P27" s="19" t="n">
+        <f aca="false">P26+M27*N27/12</f>
+        <v>859.494725882975</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="n">
@@ -2528,6 +3023,22 @@
         <f aca="false">L27+((G27+C28)+J27)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>419.012300726729</v>
       </c>
+      <c r="M28" s="19" t="n">
+        <f aca="false">(O27+C28)*(1+Předpoklady!$B$12)</f>
+        <v>116077.22150756</v>
+      </c>
+      <c r="N28" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M28,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O28" s="19" t="n">
+        <f aca="false">M28*(1-N28/12)</f>
+        <v>116009.509795014</v>
+      </c>
+      <c r="P28" s="19" t="n">
+        <f aca="false">P27+M28*N28/12</f>
+        <v>927.206438429052</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="18" t="n">
@@ -2577,6 +3088,22 @@
         <f aca="false">L28+((G28+C29)+J28)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>451.244605362395</v>
       </c>
+      <c r="M29" s="19" t="n">
+        <f aca="false">(O28+C29)*(1+Předpoklady!$B$12)</f>
+        <v>120688.061011267</v>
+      </c>
+      <c r="N29" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M29,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O29" s="19" t="n">
+        <f aca="false">M29*(1-N29/12)</f>
+        <v>120617.659642343</v>
+      </c>
+      <c r="P29" s="19" t="n">
+        <f aca="false">P28+M29*N29/12</f>
+        <v>997.607807352291</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="18" t="n">
@@ -2626,6 +3153,22 @@
         <f aca="false">L29+((G29+C30)+J29)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>486.466884104035</v>
       </c>
+      <c r="M30" s="19" t="n">
+        <f aca="false">(O29+C30)*(1+Předpoklady!$B$12)</f>
+        <v>125322.266007799</v>
+      </c>
+      <c r="N30" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M30,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O30" s="19" t="n">
+        <f aca="false">M30*(1-N30/12)</f>
+        <v>125249.161352628</v>
+      </c>
+      <c r="P30" s="19" t="n">
+        <f aca="false">P29+M30*N30/12</f>
+        <v>1070.71246252351</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="18" t="n">
@@ -2675,6 +3218,22 @@
         <f aca="false">L30+((G30+C31)+J30)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>522.885113518285</v>
       </c>
+      <c r="M31" s="19" t="n">
+        <f aca="false">(O30+C31)*(1+Předpoklady!$B$12)</f>
+        <v>129979.954902116</v>
+      </c>
+      <c r="N31" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M31,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O31" s="19" t="n">
+        <f aca="false">M31*(1-N31/12)</f>
+        <v>129904.133261756</v>
+      </c>
+      <c r="P31" s="19" t="n">
+        <f aca="false">P30+M31*N31/12</f>
+        <v>1146.53410288308</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="18" t="n">
@@ -2724,6 +3283,22 @@
         <f aca="false">L31+((G31+C32)+J31)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>560.505755005939</v>
       </c>
+      <c r="M32" s="19" t="n">
+        <f aca="false">(O31+C32)*(1+Předpoklady!$B$12)</f>
+        <v>134661.246699193</v>
+      </c>
+      <c r="N32" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M32,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O32" s="19" t="n">
+        <f aca="false">M32*(1-N32/12)</f>
+        <v>134582.694305285</v>
+      </c>
+      <c r="P32" s="19" t="n">
+        <f aca="false">P31+M32*N32/12</f>
+        <v>1225.08649679094</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="18" t="n">
@@ -2773,6 +3348,22 @@
         <f aca="false">L32+((G32+C33)+J32)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>599.335304877003</v>
       </c>
+      <c r="M33" s="19" t="n">
+        <f aca="false">(O32+C33)*(1+Předpoklady!$B$12)</f>
+        <v>139366.261007066</v>
+      </c>
+      <c r="N33" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M33,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O33" s="19" t="n">
+        <f aca="false">M33*(1-N33/12)</f>
+        <v>139284.964021478</v>
+      </c>
+      <c r="P33" s="19" t="n">
+        <f aca="false">P32+M33*N33/12</f>
+        <v>1306.38348237839</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="18" t="n">
@@ -2822,6 +3413,22 @@
         <f aca="false">L33+((G33+C34)+J33)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>639.380294539305</v>
       </c>
+      <c r="M34" s="19" t="n">
+        <f aca="false">(O33+C34)*(1+Předpoklady!$B$12)</f>
+        <v>144095.118039885</v>
+      </c>
+      <c r="N34" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M34,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O34" s="19" t="n">
+        <f aca="false">M34*(1-N34/12)</f>
+        <v>144011.062554361</v>
+      </c>
+      <c r="P34" s="19" t="n">
+        <f aca="false">P33+M34*N34/12</f>
+        <v>1390.43896790166</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="18" t="n">
@@ -2871,6 +3478,22 @@
         <f aca="false">L34+((G34+C35)+J34)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>680.647290688118</v>
       </c>
+      <c r="M35" s="19" t="n">
+        <f aca="false">(O34+C35)*(1+Předpoklady!$B$12)</f>
+        <v>148847.938620988</v>
+      </c>
+      <c r="N35" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M35,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O35" s="19" t="n">
+        <f aca="false">M35*(1-N35/12)</f>
+        <v>148761.110656792</v>
+      </c>
+      <c r="P35" s="19" t="n">
+        <f aca="false">P34+M35*N35/12</f>
+        <v>1477.26693209724</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="18" t="n">
@@ -2920,6 +3543,22 @@
         <f aca="false">L35+((G35+C36)+J35)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>723.142895496809</v>
       </c>
+      <c r="M36" s="19" t="n">
+        <f aca="false">(O35+C36)*(1+Předpoklady!$B$12)</f>
+        <v>153624.844185988</v>
+      </c>
+      <c r="N36" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M36,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O36" s="19" t="n">
+        <f aca="false">M36*(1-N36/12)</f>
+        <v>153535.229693546</v>
+      </c>
+      <c r="P36" s="19" t="n">
+        <f aca="false">P35+M36*N36/12</f>
+        <v>1566.88142453906</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="18" t="n">
@@ -2969,6 +3608,22 @@
         <f aca="false">L36+((G36+C37)+J36)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>766.873746808518</v>
       </c>
+      <c r="M37" s="19" t="n">
+        <f aca="false">(O36+C37)*(1+Předpoklady!$B$12)</f>
+        <v>158425.956785871</v>
+      </c>
+      <c r="N37" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M37,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O37" s="19" t="n">
+        <f aca="false">M37*(1-N37/12)</f>
+        <v>158333.541644413</v>
+      </c>
+      <c r="P37" s="19" t="n">
+        <f aca="false">P36+M37*N37/12</f>
+        <v>1659.29656599749</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="18" t="n">
@@ -3018,6 +3673,22 @@
         <f aca="false">L37+((G37+C38)+J37)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>811.846518328869</v>
       </c>
+      <c r="M38" s="19" t="n">
+        <f aca="false">(O37+C38)*(1+Předpoklady!$B$12)</f>
+        <v>163251.399090123</v>
+      </c>
+      <c r="N38" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M38,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O38" s="19" t="n">
+        <f aca="false">M38*(1-N38/12)</f>
+        <v>163156.16910732</v>
+      </c>
+      <c r="P38" s="19" t="n">
+        <f aca="false">P37+M38*N38/12</f>
+        <v>1754.52654880006</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="18" t="n">
@@ -3067,6 +3738,22 @@
         <f aca="false">L38+((G38+C39)+J38)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>858.067919819731</v>
       </c>
+      <c r="M39" s="19" t="n">
+        <f aca="false">(O38+C39)*(1+Předpoklady!$B$12)</f>
+        <v>168101.294389855</v>
+      </c>
+      <c r="N39" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M39,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O39" s="19" t="n">
+        <f aca="false">M39*(1-N39/12)</f>
+        <v>168003.235301461</v>
+      </c>
+      <c r="P39" s="19" t="n">
+        <f aca="false">P38+M39*N39/12</f>
+        <v>1852.58563719414</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="18" t="n">
@@ -3116,6 +3803,22 @@
         <f aca="false">L39+((G39+C40)+J39)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>905.544697294016</v>
       </c>
+      <c r="M40" s="19" t="n">
+        <f aca="false">(O39+C40)*(1+Předpoklady!$B$12)</f>
+        <v>172975.766600959</v>
+      </c>
+      <c r="N40" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M40,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O40" s="19" t="n">
+        <f aca="false">M40*(1-N40/12)</f>
+        <v>172874.864070442</v>
+      </c>
+      <c r="P40" s="19" t="n">
+        <f aca="false">P39+M40*N40/12</f>
+        <v>1953.48816771137</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="n">
@@ -3165,6 +3868,22 @@
         <f aca="false">L40+((G40+C41)+J40)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>954.283633211535</v>
       </c>
+      <c r="M41" s="19" t="n">
+        <f aca="false">(O40+C41)*(1+Předpoklady!$B$12)</f>
+        <v>177874.940267274</v>
+      </c>
+      <c r="N41" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M41,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O41" s="19" t="n">
+        <f aca="false">M41*(1-N41/12)</f>
+        <v>177771.179885451</v>
+      </c>
+      <c r="P41" s="19" t="n">
+        <f aca="false">P40+M41*N41/12</f>
+        <v>2057.24854953394</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="18" t="n">
@@ -3214,6 +3933,22 @@
         <f aca="false">L41+((G41+C42)+J41)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>1006.10172413761</v>
       </c>
+      <c r="M42" s="19" t="n">
+        <f aca="false">(O41+C42)*(1+Předpoklady!$B$12)</f>
+        <v>182798.940563764</v>
+      </c>
+      <c r="N42" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M42,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O42" s="19" t="n">
+        <f aca="false">M42*(1-N42/12)</f>
+        <v>182692.307848435</v>
+      </c>
+      <c r="P42" s="19" t="n">
+        <f aca="false">P41+M42*N42/12</f>
+        <v>2163.8812648628</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="18" t="n">
@@ -3263,6 +3998,22 @@
         <f aca="false">L42+((G42+C43)+J42)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>1059.20542845937</v>
       </c>
+      <c r="M43" s="19" t="n">
+        <f aca="false">(O42+C43)*(1+Předpoklady!$B$12)</f>
+        <v>187747.89329972</v>
+      </c>
+      <c r="N43" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M43,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O43" s="19" t="n">
+        <f aca="false">M43*(1-N43/12)</f>
+        <v>187638.373695295</v>
+      </c>
+      <c r="P43" s="19" t="n">
+        <f aca="false">P42+M43*N43/12</f>
+        <v>2273.40086928764</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="18" t="n">
@@ -3312,6 +4063,22 @@
         <f aca="false">L43+((G43+C44)+J43)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>1113.60169200127</v>
       </c>
+      <c r="M44" s="19" t="n">
+        <f aca="false">(O43+C44)*(1+Předpoklady!$B$12)</f>
+        <v>192721.924921974</v>
+      </c>
+      <c r="N44" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M44,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O44" s="19" t="n">
+        <f aca="false">M44*(1-N44/12)</f>
+        <v>192609.503799103</v>
+      </c>
+      <c r="P44" s="19" t="n">
+        <f aca="false">P43+M44*N44/12</f>
+        <v>2385.82199215879</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="18" t="n">
@@ -3361,6 +4128,22 @@
         <f aca="false">L44+((G44+C45)+J44)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>1169.29749811418</v>
       </c>
+      <c r="M45" s="19" t="n">
+        <f aca="false">(O44+C45)*(1+Předpoklady!$B$12)</f>
+        <v>197721.162518129</v>
+      </c>
+      <c r="N45" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M45,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O45" s="19" t="n">
+        <f aca="false">M45*(1-N45/12)</f>
+        <v>197605.825173327</v>
+      </c>
+      <c r="P45" s="19" t="n">
+        <f aca="false">P44+M45*N45/12</f>
+        <v>2501.15933696103</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="18" t="n">
@@ -3410,6 +4193,22 @@
         <f aca="false">L45+((G45+C46)+J45)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>1226.29986787813</v>
       </c>
+      <c r="M46" s="19" t="n">
+        <f aca="false">(O45+C46)*(1+Předpoklady!$B$12)</f>
+        <v>202745.733819804</v>
+      </c>
+      <c r="N46" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M46,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O46" s="19" t="n">
+        <f aca="false">M46*(1-N46/12)</f>
+        <v>202627.465475076</v>
+      </c>
+      <c r="P46" s="19" t="n">
+        <f aca="false">P45+M46*N46/12</f>
+        <v>2619.42768168925</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="18" t="n">
@@ -3459,6 +4258,22 @@
         <f aca="false">L46+((G46+C47)+J46)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>1284.61586030618</v>
       </c>
+      <c r="M47" s="19" t="n">
+        <f aca="false">(O46+C47)*(1+Předpoklady!$B$12)</f>
+        <v>207795.767205903</v>
+      </c>
+      <c r="N47" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M47,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O47" s="19" t="n">
+        <f aca="false">M47*(1-N47/12)</f>
+        <v>207674.553008367</v>
+      </c>
+      <c r="P47" s="19" t="n">
+        <f aca="false">P46+M47*N47/12</f>
+        <v>2740.64187922603</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="18" t="n">
@@ -3508,6 +4323,22 @@
         <f aca="false">L47+((G47+C48)+J47)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>1344.25257254933</v>
       </c>
+      <c r="M48" s="19" t="n">
+        <f aca="false">(O47+C48)*(1+Předpoklady!$B$12)</f>
+        <v>212871.39170589</v>
+      </c>
+      <c r="N48" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M48,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O48" s="19" t="n">
+        <f aca="false">M48*(1-N48/12)</f>
+        <v>212747.216727395</v>
+      </c>
+      <c r="P48" s="19" t="n">
+        <f aca="false">P47+M48*N48/12</f>
+        <v>2864.81685772113</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="18" t="n">
@@ -3557,6 +4388,22 @@
         <f aca="false">L48+((G48+C49)+J48)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>1405.21714010259</v>
       </c>
+      <c r="M49" s="19" t="n">
+        <f aca="false">(O48+C49)*(1+Předpoklady!$B$12)</f>
+        <v>217972.737003087</v>
+      </c>
+      <c r="N49" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M49,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O49" s="19" t="n">
+        <f aca="false">M49*(1-N49/12)</f>
+        <v>217845.586239835</v>
+      </c>
+      <c r="P49" s="19" t="n">
+        <f aca="false">P48+M49*N49/12</f>
+        <v>2991.96762097293</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="18" t="n">
@@ -3606,6 +4453,22 @@
         <f aca="false">L49+((G49+C50)+J49)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>1467.51673701215</v>
       </c>
+      <c r="M50" s="19" t="n">
+        <f aca="false">(O49+C50)*(1+Předpoklady!$B$12)</f>
+        <v>223099.933437989</v>
+      </c>
+      <c r="N50" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M50,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O50" s="19" t="n">
+        <f aca="false">M50*(1-N50/12)</f>
+        <v>222969.79181015</v>
+      </c>
+      <c r="P50" s="19" t="n">
+        <f aca="false">P49+M50*N50/12</f>
+        <v>3122.10924881176</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="18" t="n">
@@ -3655,6 +4518,22 @@
         <f aca="false">L50+((G50+C51)+J50)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>1531.15857608363</v>
       </c>
+      <c r="M51" s="19" t="n">
+        <f aca="false">(O50+C51)*(1+Předpoklady!$B$12)</f>
+        <v>228253.112011594</v>
+      </c>
+      <c r="N51" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M51,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O51" s="19" t="n">
+        <f aca="false">M51*(1-N51/12)</f>
+        <v>228119.964362921</v>
+      </c>
+      <c r="P51" s="19" t="n">
+        <f aca="false">P50+M51*N51/12</f>
+        <v>3255.25689748519</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="18" t="n">
@@ -3704,6 +4583,22 @@
         <f aca="false">L51+((G51+C52)+J51)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>1596.14990909151</v>
       </c>
+      <c r="M52" s="19" t="n">
+        <f aca="false">(O51+C52)*(1+Předpoklady!$B$12)</f>
+        <v>233432.404388748</v>
+      </c>
+      <c r="N52" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M52,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O52" s="19" t="n">
+        <f aca="false">M52*(1-N52/12)</f>
+        <v>233296.235486188</v>
+      </c>
+      <c r="P52" s="19" t="n">
+        <f aca="false">P51+M52*N52/12</f>
+        <v>3391.42580004529</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="18" t="n">
@@ -3753,6 +4648,22 @@
         <f aca="false">L52+((G52+C53)+J52)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>1662.49802698966</v>
       </c>
+      <c r="M53" s="19" t="n">
+        <f aca="false">(O52+C53)*(1+Předpoklady!$B$12)</f>
+        <v>238637.942901511</v>
+      </c>
+      <c r="N53" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M53,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O53" s="19" t="n">
+        <f aca="false">M53*(1-N53/12)</f>
+        <v>238498.737434818</v>
+      </c>
+      <c r="P53" s="19" t="n">
+        <f aca="false">P52+M53*N53/12</f>
+        <v>3530.63126673784</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="18" t="n">
@@ -3802,6 +4713,22 @@
         <f aca="false">L53+((G53+C54)+J53)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>1732.02043758472</v>
       </c>
+      <c r="M54" s="19" t="n">
+        <f aca="false">(O53+C54)*(1+Předpoklady!$B$12)</f>
+        <v>243869.860552537</v>
+      </c>
+      <c r="N54" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M54,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O54" s="19" t="n">
+        <f aca="false">M54*(1-N54/12)</f>
+        <v>243727.603133881</v>
+      </c>
+      <c r="P54" s="19" t="n">
+        <f aca="false">P53+M54*N54/12</f>
+        <v>3672.88868539349</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="18" t="n">
@@ -3851,6 +4778,22 @@
         <f aca="false">L54+((G54+C55)+J54)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>1802.92411326725</v>
       </c>
+      <c r="M55" s="19" t="n">
+        <f aca="false">(O54+C55)*(1+Předpoklady!$B$12)</f>
+        <v>249128.291018474</v>
+      </c>
+      <c r="N55" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M55,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O55" s="19" t="n">
+        <f aca="false">M55*(1-N55/12)</f>
+        <v>248982.966182046</v>
+      </c>
+      <c r="P55" s="19" t="n">
+        <f aca="false">P54+M55*N55/12</f>
+        <v>3818.21352182093</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="18" t="n">
@@ -3900,6 +4843,22 @@
         <f aca="false">L55+((G55+C56)+J55)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>1875.21651664214</v>
       </c>
+      <c r="M56" s="19" t="n">
+        <f aca="false">(O55+C56)*(1+Předpoklady!$B$12)</f>
+        <v>254413.368653376</v>
+      </c>
+      <c r="N56" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M56,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O56" s="19" t="n">
+        <f aca="false">M56*(1-N56/12)</f>
+        <v>254264.960854995</v>
+      </c>
+      <c r="P56" s="19" t="n">
+        <f aca="false">P55+M56*N56/12</f>
+        <v>3966.62132020207</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="18" t="n">
@@ -3949,6 +4908,22 @@
         <f aca="false">L56+((G56+C57)+J56)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>1948.90515063272</v>
       </c>
+      <c r="M57" s="19" t="n">
+        <f aca="false">(O56+C57)*(1+Předpoklady!$B$12)</f>
+        <v>259725.228492142</v>
+      </c>
+      <c r="N57" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M57,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O57" s="19" t="n">
+        <f aca="false">M57*(1-N57/12)</f>
+        <v>259573.722108855</v>
+      </c>
+      <c r="P57" s="19" t="n">
+        <f aca="false">P56+M57*N57/12</f>
+        <v>4118.12770348915</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="18" t="n">
@@ -3998,6 +4973,22 @@
         <f aca="false">L57+((G57+C58)+J57)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>2023.99755869861</v>
       </c>
+      <c r="M58" s="19" t="n">
+        <f aca="false">(O57+C58)*(1+Předpoklady!$B$12)</f>
+        <v>265064.006253958</v>
+      </c>
+      <c r="N58" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M58,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O58" s="19" t="n">
+        <f aca="false">M58*(1-N58/12)</f>
+        <v>264909.385583643</v>
+      </c>
+      <c r="P58" s="19" t="n">
+        <f aca="false">P57+M58*N58/12</f>
+        <v>4272.74837380396</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="18" t="n">
@@ -4047,6 +5038,22 @@
         <f aca="false">L58+((G58+C59)+J58)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>2100.50132505471</v>
       </c>
+      <c r="M59" s="19" t="n">
+        <f aca="false">(O58+C59)*(1+Předpoklady!$B$12)</f>
+        <v>270429.838345771</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M59,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O59" s="19" t="n">
+        <f aca="false">M59*(1-N59/12)</f>
+        <v>270272.087606736</v>
+      </c>
+      <c r="P59" s="19" t="n">
+        <f aca="false">P58+M59*N59/12</f>
+        <v>4430.49911283899</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="18" t="n">
@@ -4096,6 +5103,22 @@
         <f aca="false">L59+((G59+C60)+J59)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>2178.42407489142</v>
       </c>
+      <c r="M60" s="19" t="n">
+        <f aca="false">(O59+C60)*(1+Předpoklady!$B$12)</f>
+        <v>275822.861865771</v>
+      </c>
+      <c r="N60" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M60,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O60" s="19" t="n">
+        <f aca="false">M60*(1-N60/12)</f>
+        <v>275661.96519635</v>
+      </c>
+      <c r="P60" s="19" t="n">
+        <f aca="false">P59+M60*N60/12</f>
+        <v>4591.39578226069</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="18" t="n">
@@ -4145,6 +5168,22 @@
         <f aca="false">L60+((G60+C61)+J60)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>2257.77347459598</v>
       </c>
+      <c r="M61" s="19" t="n">
+        <f aca="false">(O60+C61)*(1+Předpoklady!$B$12)</f>
+        <v>281243.214606897</v>
+      </c>
+      <c r="N61" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M61,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O61" s="19" t="n">
+        <f aca="false">M61*(1-N61/12)</f>
+        <v>281079.156065043</v>
+      </c>
+      <c r="P61" s="19" t="n">
+        <f aca="false">P60+M61*N61/12</f>
+        <v>4755.45432411471</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="18" t="n">
@@ -4194,6 +5233,22 @@
         <f aca="false">L61+((G61+C62)+J61)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>2338.55723197508</v>
       </c>
+      <c r="M62" s="19" t="n">
+        <f aca="false">(O61+C62)*(1+Předpoklady!$B$12)</f>
+        <v>286691.035060354</v>
+      </c>
+      <c r="N62" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M62,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O62" s="19" t="n">
+        <f aca="false">M62*(1-N62/12)</f>
+        <v>286523.798623235</v>
+      </c>
+      <c r="P62" s="19" t="n">
+        <f aca="false">P61+M62*N62/12</f>
+        <v>4922.69076123325</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="18" t="n">
@@ -4243,6 +5298,22 @@
         <f aca="false">L62+((G62+C63)+J62)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>2420.7830964786</v>
       </c>
+      <c r="M63" s="19" t="n">
+        <f aca="false">(O62+C63)*(1+Předpoklady!$B$12)</f>
+        <v>292166.462419152</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M63,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O63" s="19" t="n">
+        <f aca="false">M63*(1-N63/12)</f>
+        <v>291996.031982741</v>
+      </c>
+      <c r="P63" s="19" t="n">
+        <f aca="false">P62+M63*N63/12</f>
+        <v>5093.12119764443</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="18" t="n">
@@ -4292,6 +5363,22 @@
         <f aca="false">L63+((G63+C64)+J63)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>2504.45885942465</v>
       </c>
+      <c r="M64" s="19" t="n">
+        <f aca="false">(O63+C64)*(1+Předpoklady!$B$12)</f>
+        <v>297669.636581667</v>
+      </c>
+      <c r="N64" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M64,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O64" s="19" t="n">
+        <f aca="false">M64*(1-N64/12)</f>
+        <v>297495.995960327</v>
+      </c>
+      <c r="P64" s="19" t="n">
+        <f aca="false">P63+M64*N64/12</f>
+        <v>5266.76181898373</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="18" t="n">
@@ -4341,6 +5428,22 @@
         <f aca="false">L64+((G64+C65)+J64)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>2589.59235422571</v>
       </c>
+      <c r="M65" s="19" t="n">
+        <f aca="false">(O64+C65)*(1+Předpoklady!$B$12)</f>
+        <v>303200.698155208</v>
+      </c>
+      <c r="N65" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M65,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O65" s="19" t="n">
+        <f aca="false">M65*(1-N65/12)</f>
+        <v>303023.831081284</v>
+      </c>
+      <c r="P65" s="19" t="n">
+        <f aca="false">P64+M65*N65/12</f>
+        <v>5443.6288929076</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="18" t="n">
@@ -4390,6 +5493,22 @@
         <f aca="false">L65+((G65+C66)+J65)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>2678.00163407781</v>
       </c>
+      <c r="M66" s="19" t="n">
+        <f aca="false">(O65+C66)*(1+Předpoklady!$B$12)</f>
+        <v>308759.788459615</v>
+      </c>
+      <c r="N66" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M66,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O66" s="19" t="n">
+        <f aca="false">M66*(1-N66/12)</f>
+        <v>308579.678583014</v>
+      </c>
+      <c r="P66" s="19" t="n">
+        <f aca="false">P65+M66*N66/12</f>
+        <v>5623.73876950905</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="18" t="n">
@@ -4439,6 +5558,22 @@
         <f aca="false">L66+((G66+C67)+J66)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>2767.89421970748</v>
       </c>
+      <c r="M67" s="19" t="n">
+        <f aca="false">(O66+C67)*(1+Předpoklady!$B$12)</f>
+        <v>314347.049530871</v>
+      </c>
+      <c r="N67" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M67,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O67" s="19" t="n">
+        <f aca="false">M67*(1-N67/12)</f>
+        <v>314163.680418644</v>
+      </c>
+      <c r="P67" s="19" t="n">
+        <f aca="false">P66+M67*N67/12</f>
+        <v>5807.10788173539</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="18" t="n">
@@ -4488,6 +5623,22 @@
         <f aca="false">L67+((G67+C68)+J67)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>2859.2781250181</v>
       </c>
+      <c r="M68" s="19" t="n">
+        <f aca="false">(O67+C68)*(1+Předpoklady!$B$12)</f>
+        <v>319962.624124723</v>
+      </c>
+      <c r="N68" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M68,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O68" s="19" t="n">
+        <f aca="false">M68*(1-N68/12)</f>
+        <v>319775.979260651</v>
+      </c>
+      <c r="P68" s="19" t="n">
+        <f aca="false">P67+M68*N68/12</f>
+        <v>5993.75274580814</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="18" t="n">
@@ -4537,6 +5688,22 @@
         <f aca="false">L68+((G68+C69)+J68)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>2952.16140721</v>
       </c>
+      <c r="M69" s="19" t="n">
+        <f aca="false">(O68+C69)*(1+Předpoklady!$B$12)</f>
+        <v>325606.65572034</v>
+      </c>
+      <c r="N69" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M69,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O69" s="19" t="n">
+        <f aca="false">M69*(1-N69/12)</f>
+        <v>325416.718504503</v>
+      </c>
+      <c r="P69" s="19" t="n">
+        <f aca="false">P68+M69*N69/12</f>
+        <v>6183.68996164501</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="18" t="n">
@@ -4586,6 +5753,22 @@
         <f aca="false">L69+((G69+C70)+J69)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>3046.55216701442</v>
       </c>
+      <c r="M70" s="19" t="n">
+        <f aca="false">(O69+C70)*(1+Předpoklady!$B$12)</f>
+        <v>331279.288523969</v>
+      </c>
+      <c r="N70" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M70,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O70" s="19" t="n">
+        <f aca="false">M70*(1-N70/12)</f>
+        <v>331086.04227233</v>
+      </c>
+      <c r="P70" s="19" t="n">
+        <f aca="false">P69+M70*N70/12</f>
+        <v>6376.93621328399</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="18" t="n">
@@ -4635,6 +5818,22 @@
         <f aca="false">L70+((G70+C71)+J70)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>3142.45854892866</v>
       </c>
+      <c r="M71" s="19" t="n">
+        <f aca="false">(O70+C71)*(1+Předpoklady!$B$12)</f>
+        <v>336980.667472628</v>
+      </c>
+      <c r="N71" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M71,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O71" s="19" t="n">
+        <f aca="false">M71*(1-N71/12)</f>
+        <v>336784.095416603</v>
+      </c>
+      <c r="P71" s="19" t="n">
+        <f aca="false">P70+M71*N71/12</f>
+        <v>6573.50826930969</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="18" t="n">
@@ -4684,6 +5883,22 @@
         <f aca="false">L71+((G71+C72)+J71)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>3239.88874145258</v>
       </c>
+      <c r="M72" s="19" t="n">
+        <f aca="false">(O71+C72)*(1+Předpoklady!$B$12)</f>
+        <v>342710.938237803</v>
+      </c>
+      <c r="N72" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M72,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O72" s="19" t="n">
+        <f aca="false">M72*(1-N72/12)</f>
+        <v>342511.023523831</v>
+      </c>
+      <c r="P72" s="19" t="n">
+        <f aca="false">P71+M72*N72/12</f>
+        <v>6773.42298328174</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="18" t="n">
@@ -4733,6 +5948,22 @@
         <f aca="false">L72+((G72+C73)+J72)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>3338.85097732629</v>
       </c>
+      <c r="M73" s="19" t="n">
+        <f aca="false">(O72+C73)*(1+Předpoklady!$B$12)</f>
+        <v>348470.247229174</v>
+      </c>
+      <c r="N73" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M73,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O73" s="19" t="n">
+        <f aca="false">M73*(1-N73/12)</f>
+        <v>348266.97291829</v>
+      </c>
+      <c r="P73" s="19" t="n">
+        <f aca="false">P72+M73*N73/12</f>
+        <v>6976.69729416542</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="18" t="n">
@@ -4782,6 +6013,22 @@
         <f aca="false">L73+((G73+C74)+J73)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>3439.3535337692</v>
       </c>
+      <c r="M74" s="19" t="n">
+        <f aca="false">(O73+C74)*(1+Předpoklady!$B$12)</f>
+        <v>354258.741598351</v>
+      </c>
+      <c r="N74" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M74,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O74" s="19" t="n">
+        <f aca="false">M74*(1-N74/12)</f>
+        <v>354052.090665752</v>
+      </c>
+      <c r="P74" s="19" t="n">
+        <f aca="false">P73+M74*N74/12</f>
+        <v>7183.34822676446</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="18" t="n">
@@ -4831,6 +6078,22 @@
         <f aca="false">L74+((G74+C75)+J74)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>3541.4047327203</v>
       </c>
+      <c r="M75" s="19" t="n">
+        <f aca="false">(O74+C75)*(1+Předpoklady!$B$12)</f>
+        <v>360076.569242641</v>
+      </c>
+      <c r="N75" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M75,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O75" s="19" t="n">
+        <f aca="false">M75*(1-N75/12)</f>
+        <v>359866.524577249</v>
+      </c>
+      <c r="P75" s="19" t="n">
+        <f aca="false">P74+M75*N75/12</f>
+        <v>7393.392892156</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="18" t="n">
@@ -4880,6 +6143,22 @@
         <f aca="false">L75+((G75+C76)+J75)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>3645.0129410798</v>
       </c>
+      <c r="M76" s="19" t="n">
+        <f aca="false">(O75+C76)*(1+Předpoklady!$B$12)</f>
+        <v>365923.878808819</v>
+      </c>
+      <c r="N76" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M76,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O76" s="19" t="n">
+        <f aca="false">M76*(1-N76/12)</f>
+        <v>365710.423212847</v>
+      </c>
+      <c r="P76" s="19" t="n">
+        <f aca="false">P75+M76*N76/12</f>
+        <v>7606.84848812781</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="18" t="n">
@@ -4929,6 +6208,22 @@
         <f aca="false">L76+((G76+C77)+J76)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>3750.18657095202</v>
       </c>
+      <c r="M77" s="19" t="n">
+        <f aca="false">(O76+C77)*(1+Předpoklady!$B$12)</f>
+        <v>371800.819696931</v>
+      </c>
+      <c r="N77" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M77,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O77" s="19" t="n">
+        <f aca="false">M77*(1-N77/12)</f>
+        <v>371583.935885441</v>
+      </c>
+      <c r="P77" s="19" t="n">
+        <f aca="false">P76+M77*N77/12</f>
+        <v>7823.73229961769</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="18" t="n">
@@ -4978,6 +6273,22 @@
         <f aca="false">L77+((G77+C78)+J77)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>3858.74425735133</v>
       </c>
+      <c r="M78" s="19" t="n">
+        <f aca="false">(O77+C78)*(1+Předpoklady!$B$12)</f>
+        <v>377707.542064112</v>
+      </c>
+      <c r="N78" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M78,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O78" s="19" t="n">
+        <f aca="false">M78*(1-N78/12)</f>
+        <v>377487.212664574</v>
+      </c>
+      <c r="P78" s="19" t="n">
+        <f aca="false">P77+M78*N78/12</f>
+        <v>8044.06169915509</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="18" t="n">
@@ -5027,6 +6338,22 @@
         <f aca="false">L78+((G78+C79)+J78)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>3968.89410596601</v>
       </c>
+      <c r="M79" s="19" t="n">
+        <f aca="false">(O78+C79)*(1+Předpoklady!$B$12)</f>
+        <v>383644.196828416</v>
+      </c>
+      <c r="N79" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M79,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O79" s="19" t="n">
+        <f aca="false">M79*(1-N79/12)</f>
+        <v>383420.404380266</v>
+      </c>
+      <c r="P79" s="19" t="n">
+        <f aca="false">P78+M79*N79/12</f>
+        <v>8267.854147305</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="18" t="n">
@@ -5076,6 +6403,22 @@
         <f aca="false">L79+((G79+C80)+J79)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>4080.64471882158</v>
       </c>
+      <c r="M80" s="19" t="n">
+        <f aca="false">(O79+C80)*(1+Předpoklady!$B$12)</f>
+        <v>389610.935672679</v>
+      </c>
+      <c r="N80" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M80,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O80" s="19" t="n">
+        <f aca="false">M80*(1-N80/12)</f>
+        <v>389383.66262687</v>
+      </c>
+      <c r="P80" s="19" t="n">
+        <f aca="false">P79+M80*N80/12</f>
+        <v>8495.12719311406</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="18" t="n">
@@ -5125,6 +6468,22 @@
         <f aca="false">L80+((G80+C81)+J80)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>4194.00474441799</v>
       </c>
+      <c r="M81" s="19" t="n">
+        <f aca="false">(O80+C81)*(1+Předpoklady!$B$12)</f>
+        <v>395607.911048392</v>
+      </c>
+      <c r="N81" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M81,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O81" s="19" t="n">
+        <f aca="false">M81*(1-N81/12)</f>
+        <v>395377.139766948</v>
+      </c>
+      <c r="P81" s="19" t="n">
+        <f aca="false">P80+M81*N81/12</f>
+        <v>8725.89847455896</v>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="18" t="n">
@@ -5174,6 +6533,22 @@
         <f aca="false">L81+((G81+C82)+J81)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>4308.98287798071</v>
       </c>
+      <c r="M82" s="19" t="n">
+        <f aca="false">(O81+C82)*(1+Předpoklady!$B$12)</f>
+        <v>401635.276179596</v>
+      </c>
+      <c r="N82" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M82,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O82" s="19" t="n">
+        <f aca="false">M82*(1-N82/12)</f>
+        <v>401400.988935158</v>
+      </c>
+      <c r="P82" s="19" t="n">
+        <f aca="false">P81+M82*N82/12</f>
+        <v>8960.18571899705</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="18" t="n">
@@ -5223,6 +6598,22 @@
         <f aca="false">L82+((G82+C83)+J82)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>4425.58786171319</v>
       </c>
+      <c r="M83" s="19" t="n">
+        <f aca="false">(O82+C83)*(1+Předpoklady!$B$12)</f>
+        <v>407693.185066795</v>
+      </c>
+      <c r="N83" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M83,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O83" s="19" t="n">
+        <f aca="false">M83*(1-N83/12)</f>
+        <v>407455.364042173</v>
+      </c>
+      <c r="P83" s="19" t="n">
+        <f aca="false">P82+M83*N83/12</f>
+        <v>9198.00674361935</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="18" t="n">
@@ -5272,6 +6663,22 @@
         <f aca="false">L83+((G83+C84)+J83)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>4543.82848505067</v>
       </c>
+      <c r="M84" s="19" t="n">
+        <f aca="false">(O83+C84)*(1+Předpoklady!$B$12)</f>
+        <v>413781.792490895</v>
+      </c>
+      <c r="N84" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M84,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O84" s="19" t="n">
+        <f aca="false">M84*(1-N84/12)</f>
+        <v>413540.419778609</v>
+      </c>
+      <c r="P84" s="19" t="n">
+        <f aca="false">P83+M84*N84/12</f>
+        <v>9439.3794559057</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="18" t="n">
@@ -5321,6 +6728,22 @@
         <f aca="false">L84+((G84+C85)+J84)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>4663.71358491532</v>
       </c>
+      <c r="M85" s="19" t="n">
+        <f aca="false">(O84+C85)*(1+Předpoklady!$B$12)</f>
+        <v>419901.254017155</v>
+      </c>
+      <c r="N85" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M85,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O85" s="19" t="n">
+        <f aca="false">M85*(1-N85/12)</f>
+        <v>419656.311618978</v>
+      </c>
+      <c r="P85" s="19" t="n">
+        <f aca="false">P84+M85*N85/12</f>
+        <v>9684.32185408238</v>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="18" t="n">
@@ -5370,6 +6793,22 @@
         <f aca="false">L85+((G85+C86)+J85)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>4785.25204597287</v>
       </c>
+      <c r="M86" s="19" t="n">
+        <f aca="false">(O85+C86)*(1+Předpoklady!$B$12)</f>
+        <v>426051.725999164</v>
+      </c>
+      <c r="N86" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M86,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O86" s="19" t="n">
+        <f aca="false">M86*(1-N86/12)</f>
+        <v>425803.195825664</v>
+      </c>
+      <c r="P86" s="19" t="n">
+        <f aca="false">P85+M86*N86/12</f>
+        <v>9932.85202758189</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="18" t="n">
@@ -5419,6 +6858,22 @@
         <f aca="false">L86+((G86+C87)+J86)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>4908.45280089049</v>
       </c>
+      <c r="M87" s="19" t="n">
+        <f aca="false">(O86+C87)*(1+Předpoklady!$B$12)</f>
+        <v>432233.365582834</v>
+      </c>
+      <c r="N87" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M87,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O87" s="19" t="n">
+        <f aca="false">M87*(1-N87/12)</f>
+        <v>431981.229452911</v>
+      </c>
+      <c r="P87" s="19" t="n">
+        <f aca="false">P86+M87*N87/12</f>
+        <v>10184.9881575052</v>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="18" t="n">
@@ -5468,6 +6923,22 @@
         <f aca="false">L87+((G87+C88)+J87)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>5033.32483059617</v>
       </c>
+      <c r="M88" s="19" t="n">
+        <f aca="false">(O87+C88)*(1+Předpoklady!$B$12)</f>
+        <v>438446.330710417</v>
+      </c>
+      <c r="N88" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M88,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O88" s="19" t="n">
+        <f aca="false">M88*(1-N88/12)</f>
+        <v>438190.570350836</v>
+      </c>
+      <c r="P88" s="19" t="n">
+        <f aca="false">P87+M88*N88/12</f>
+        <v>10440.7485170863</v>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="18" t="n">
@@ -5517,6 +6988,22 @@
         <f aca="false">L88+((G88+C89)+J88)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>5159.87716453943</v>
       </c>
+      <c r="M89" s="19" t="n">
+        <f aca="false">(O88+C89)*(1+Předpoklady!$B$12)</f>
+        <v>444690.78012454</v>
+      </c>
+      <c r="N89" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M89,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O89" s="19" t="n">
+        <f aca="false">M89*(1-N89/12)</f>
+        <v>444431.377169467</v>
+      </c>
+      <c r="P89" s="19" t="n">
+        <f aca="false">P88+M89*N89/12</f>
+        <v>10700.1514721589</v>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="18" t="n">
@@ -5566,6 +7053,22 @@
         <f aca="false">L89+((G89+C90)+J89)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>5289.9290584152</v>
       </c>
+      <c r="M90" s="19" t="n">
+        <f aca="false">(O89+C90)*(1+Předpoklady!$B$12)</f>
+        <v>450966.873372257</v>
+      </c>
+      <c r="N90" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M90,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O90" s="19" t="n">
+        <f aca="false">M90*(1-N90/12)</f>
+        <v>450703.80936279</v>
+      </c>
+      <c r="P90" s="19" t="n">
+        <f aca="false">P89+M90*N90/12</f>
+        <v>10963.2154816261</v>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="18" t="n">
@@ -5615,6 +7118,22 @@
         <f aca="false">L90+((G90+C91)+J90)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>5421.68924194568</v>
       </c>
+      <c r="M91" s="19" t="n">
+        <f aca="false">(O90+C91)*(1+Předpoklady!$B$12)</f>
+        <v>457274.770809134</v>
+      </c>
+      <c r="N91" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M91,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O91" s="19" t="n">
+        <f aca="false">M91*(1-N91/12)</f>
+        <v>457008.027192829</v>
+      </c>
+      <c r="P91" s="19" t="n">
+        <f aca="false">P90+M91*N91/12</f>
+        <v>11229.9590979314</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="18" t="n">
@@ -5664,6 +7183,22 @@
         <f aca="false">L91+((G91+C92)+J91)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>5555.16694456182</v>
       </c>
+      <c r="M92" s="19" t="n">
+        <f aca="false">(O91+C92)*(1+Předpoklady!$B$12)</f>
+        <v>463614.633603338</v>
+      </c>
+      <c r="N92" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M92,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O92" s="19" t="n">
+        <f aca="false">M92*(1-N92/12)</f>
+        <v>463344.191733736</v>
+      </c>
+      <c r="P92" s="19" t="n">
+        <f aca="false">P91+M92*N92/12</f>
+        <v>11500.4009675334</v>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="18" t="n">
@@ -5713,6 +7248,22 @@
         <f aca="false">L92+((G92+C93)+J92)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>5690.37144555867</v>
       </c>
+      <c r="M93" s="19" t="n">
+        <f aca="false">(O92+C93)*(1+Předpoklady!$B$12)</f>
+        <v>469986.623739758</v>
+      </c>
+      <c r="N93" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M93,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O93" s="19" t="n">
+        <f aca="false">M93*(1-N93/12)</f>
+        <v>469712.46487591</v>
+      </c>
+      <c r="P93" s="19" t="n">
+        <f aca="false">P92+M93*N93/12</f>
+        <v>11774.5598313816</v>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="18" t="n">
@@ -5762,6 +7313,22 @@
         <f aca="false">L93+((G93+C94)+J93)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>5827.31207436486</v>
       </c>
+      <c r="M94" s="19" t="n">
+        <f aca="false">(O93+C94)*(1+Předpoklady!$B$12)</f>
+        <v>476390.904024145</v>
+      </c>
+      <c r="N94" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M94,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O94" s="19" t="n">
+        <f aca="false">M94*(1-N94/12)</f>
+        <v>476113.00933013</v>
+      </c>
+      <c r="P94" s="19" t="n">
+        <f aca="false">P93+M94*N94/12</f>
+        <v>12052.4545253956</v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="18" t="n">
@@ -5811,6 +7378,22 @@
         <f aca="false">L94+((G94+C95)+J94)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>5965.99821081338</v>
       </c>
+      <c r="M95" s="19" t="n">
+        <f aca="false">(O94+C95)*(1+Předpoklady!$B$12)</f>
+        <v>482827.638087268</v>
+      </c>
+      <c r="N95" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M95,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O95" s="19" t="n">
+        <f aca="false">M95*(1-N95/12)</f>
+        <v>482545.988631717</v>
+      </c>
+      <c r="P95" s="19" t="n">
+        <f aca="false">P94+M95*N95/12</f>
+        <v>12334.1039809465</v>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="18" t="n">
@@ -5860,6 +7443,22 @@
         <f aca="false">L95+((G95+C96)+J95)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>6106.43928541399</v>
       </c>
+      <c r="M96" s="19" t="n">
+        <f aca="false">(O95+C96)*(1+Předpoklady!$B$12)</f>
+        <v>489296.990389099</v>
+      </c>
+      <c r="N96" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M96,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O96" s="19" t="n">
+        <f aca="false">M96*(1-N96/12)</f>
+        <v>489011.567144706</v>
+      </c>
+      <c r="P96" s="19" t="n">
+        <f aca="false">P95+M96*N96/12</f>
+        <v>12619.5272253402</v>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="18" t="n">
@@ -5909,6 +7508,22 @@
         <f aca="false">L96+((G96+C97)+J96)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>6248.64477962692</v>
       </c>
+      <c r="M97" s="19" t="n">
+        <f aca="false">(O96+C97)*(1+Předpoklady!$B$12)</f>
+        <v>495799.126223014</v>
+      </c>
+      <c r="N97" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M97,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.007</v>
+      </c>
+      <c r="O97" s="19" t="n">
+        <f aca="false">M97*(1-N97/12)</f>
+        <v>495509.910066051</v>
+      </c>
+      <c r="P97" s="19" t="n">
+        <f aca="false">P96+M97*N97/12</f>
+        <v>12908.7433823036</v>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="18" t="n">
@@ -5958,6 +7573,22 @@
         <f aca="false">L97+((G97+C98)+J97)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>6392.62422613822</v>
       </c>
+      <c r="M98" s="19" t="n">
+        <f aca="false">(O97+C98)*(1+Předpoklady!$B$12)</f>
+        <v>502334.211720014</v>
+      </c>
+      <c r="N98" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M98,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O98" s="19" t="n">
+        <f aca="false">M98*(1-N98/12)</f>
+        <v>502099.789087878</v>
+      </c>
+      <c r="P98" s="19" t="n">
+        <f aca="false">P97+M98*N98/12</f>
+        <v>13143.1660144396</v>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="18" t="n">
@@ -6007,6 +7638,22 @@
         <f aca="false">L98+((G98+C99)+J98)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>6538.38720913647</v>
       </c>
+      <c r="M99" s="19" t="n">
+        <f aca="false">(O98+C99)*(1+Předpoklady!$B$12)</f>
+        <v>508961.350875916</v>
+      </c>
+      <c r="N99" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M99,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O99" s="19" t="n">
+        <f aca="false">M99*(1-N99/12)</f>
+        <v>508723.835578841</v>
+      </c>
+      <c r="P99" s="19" t="n">
+        <f aca="false">P98+M99*N99/12</f>
+        <v>13380.681311515</v>
+      </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="18" t="n">
@@ -6056,6 +7703,22 @@
         <f aca="false">L99+((G99+C100)+J99)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>6685.94336459106</v>
       </c>
+      <c r="M100" s="19" t="n">
+        <f aca="false">(O99+C100)*(1+Předpoklady!$B$12)</f>
+        <v>515622.850688792</v>
+      </c>
+      <c r="N100" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M100,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O100" s="19" t="n">
+        <f aca="false">M100*(1-N100/12)</f>
+        <v>515382.226691803</v>
+      </c>
+      <c r="P100" s="19" t="n">
+        <f aca="false">P99+M100*N100/12</f>
+        <v>13621.3053085031</v>
+      </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="18" t="n">
@@ -6105,6 +7768,22 @@
         <f aca="false">L100+((G100+C101)+J100)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>6835.30238053193</v>
       </c>
+      <c r="M101" s="19" t="n">
+        <f aca="false">(O100+C101)*(1+Předpoklady!$B$12)</f>
+        <v>522318.889313153</v>
+      </c>
+      <c r="N101" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M101,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O101" s="19" t="n">
+        <f aca="false">M101*(1-N101/12)</f>
+        <v>522075.14049814</v>
+      </c>
+      <c r="P101" s="19" t="n">
+        <f aca="false">P100+M101*N101/12</f>
+        <v>13865.054123516</v>
+      </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="18" t="n">
@@ -6154,6 +7833,22 @@
         <f aca="false">L101+((G101+C102)+J101)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>6988.28417479255</v>
       </c>
+      <c r="M102" s="19" t="n">
+        <f aca="false">(O101+C102)*(1+Předpoklady!$B$12)</f>
+        <v>529049.645827216</v>
+      </c>
+      <c r="N102" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M102,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O102" s="19" t="n">
+        <f aca="false">M102*(1-N102/12)</f>
+        <v>528802.755992497</v>
+      </c>
+      <c r="P102" s="19" t="n">
+        <f aca="false">P101+M102*N102/12</f>
+        <v>14111.9439582353</v>
+      </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="18" t="n">
@@ -6203,6 +7898,22 @@
         <f aca="false">L102+((G102+C103)+J102)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>7143.09814281105</v>
       </c>
+      <c r="M103" s="19" t="n">
+        <f aca="false">(O102+C103)*(1+Předpoklady!$B$12)</f>
+        <v>535815.300237689</v>
+      </c>
+      <c r="N103" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M103,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O103" s="19" t="n">
+        <f aca="false">M103*(1-N103/12)</f>
+        <v>535565.253097578</v>
+      </c>
+      <c r="P103" s="19" t="n">
+        <f aca="false">P102+M103*N103/12</f>
+        <v>14361.9910983462</v>
+      </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="18" t="n">
@@ -6252,6 +7963,22 @@
         <f aca="false">L103+((G103+C104)+J103)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>7299.75418333093</v>
       </c>
+      <c r="M104" s="19" t="n">
+        <f aca="false">(O103+C104)*(1+Předpoklady!$B$12)</f>
+        <v>542616.033484584</v>
+      </c>
+      <c r="N104" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M104,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O104" s="19" t="n">
+        <f aca="false">M104*(1-N104/12)</f>
+        <v>542362.812668958</v>
+      </c>
+      <c r="P104" s="19" t="n">
+        <f aca="false">P103+M104*N104/12</f>
+        <v>14615.2119139724</v>
+      </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="18" t="n">
@@ -6301,6 +8028,22 @@
         <f aca="false">L104+((G104+C105)+J104)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>7458.26224857598</v>
       </c>
+      <c r="M105" s="19" t="n">
+        <f aca="false">(O104+C105)*(1+Předpoklady!$B$12)</f>
+        <v>549452.02744606</v>
+      </c>
+      <c r="N105" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M105,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O105" s="19" t="n">
+        <f aca="false">M105*(1-N105/12)</f>
+        <v>549195.616499918</v>
+      </c>
+      <c r="P105" s="19" t="n">
+        <f aca="false">P104+M105*N105/12</f>
+        <v>14871.6228601139</v>
+      </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="18" t="n">
@@ -6350,6 +8093,22 @@
         <f aca="false">L105+((G105+C106)+J105)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>7618.63234453916</v>
       </c>
+      <c r="M106" s="19" t="n">
+        <f aca="false">(O105+C106)*(1+Předpoklady!$B$12)</f>
+        <v>556323.464943284</v>
+      </c>
+      <c r="N106" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M106,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O106" s="19" t="n">
+        <f aca="false">M106*(1-N106/12)</f>
+        <v>556063.847326311</v>
+      </c>
+      <c r="P106" s="19" t="n">
+        <f aca="false">P105+M106*N106/12</f>
+        <v>15131.2404770874</v>
+      </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="18" t="n">
@@ -6399,6 +8158,22 @@
         <f aca="false">L106+((G106+C107)+J106)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>7780.87453127315</v>
       </c>
+      <c r="M107" s="19" t="n">
+        <f aca="false">(O106+C107)*(1+Předpoklady!$B$12)</f>
+        <v>563230.529745323</v>
+      </c>
+      <c r="N107" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M107,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O107" s="19" t="n">
+        <f aca="false">M107*(1-N107/12)</f>
+        <v>562967.688831442</v>
+      </c>
+      <c r="P107" s="19" t="n">
+        <f aca="false">P106+M107*N107/12</f>
+        <v>15394.0813909686</v>
+      </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="18" t="n">
@@ -6448,6 +8223,22 @@
         <f aca="false">L107+((G107+C108)+J107)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>7944.99892318238</v>
       </c>
+      <c r="M108" s="19" t="n">
+        <f aca="false">(O107+C108)*(1+Předpoklady!$B$12)</f>
+        <v>570173.406574056</v>
+      </c>
+      <c r="N108" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M108,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O108" s="19" t="n">
+        <f aca="false">M108*(1-N108/12)</f>
+        <v>569907.325650988</v>
+      </c>
+      <c r="P108" s="19" t="n">
+        <f aca="false">P107+M108*N108/12</f>
+        <v>15660.1623140364</v>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="18" t="n">
@@ -6497,6 +8288,22 @@
         <f aca="false">L108+((G108+C109)+J108)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>8111.0156893167</v>
       </c>
+      <c r="M109" s="19" t="n">
+        <f aca="false">(O108+C109)*(1+Předpoklady!$B$12)</f>
+        <v>577152.281109116</v>
+      </c>
+      <c r="N109" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M109,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O109" s="19" t="n">
+        <f aca="false">M109*(1-N109/12)</f>
+        <v>576882.943377932</v>
+      </c>
+      <c r="P109" s="19" t="n">
+        <f aca="false">P108+M109*N109/12</f>
+        <v>15929.5000452207</v>
+      </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="18" t="n">
@@ -6546,6 +8353,22 @@
         <f aca="false">L109+((G109+C110)+J109)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>8278.93505366662</v>
       </c>
+      <c r="M110" s="19" t="n">
+        <f aca="false">(O109+C110)*(1+Předpoklady!$B$12)</f>
+        <v>584167.339992855</v>
+      </c>
+      <c r="N110" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M110,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O110" s="19" t="n">
+        <f aca="false">M110*(1-N110/12)</f>
+        <v>583894.728567525</v>
+      </c>
+      <c r="P110" s="19" t="n">
+        <f aca="false">P109+M110*N110/12</f>
+        <v>16202.1114705507</v>
+      </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="18" t="n">
@@ -6595,6 +8418,22 @@
         <f aca="false">L110+((G110+C111)+J110)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>8448.7672954601</v>
       </c>
+      <c r="M111" s="19" t="n">
+        <f aca="false">(O110+C111)*(1+Předpoklady!$B$12)</f>
+        <v>591218.770835335</v>
+      </c>
+      <c r="N111" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M111,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O111" s="19" t="n">
+        <f aca="false">M111*(1-N111/12)</f>
+        <v>590942.868742278</v>
+      </c>
+      <c r="P111" s="19" t="n">
+        <f aca="false">P110+M111*N111/12</f>
+        <v>16478.0135636072</v>
+      </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="18" t="n">
@@ -6644,6 +8483,22 @@
         <f aca="false">L111+((G111+C112)+J111)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>8620.52274946104</v>
       </c>
+      <c r="M112" s="19" t="n">
+        <f aca="false">(O111+C112)*(1+Předpoklady!$B$12)</f>
+        <v>598306.762219347</v>
+      </c>
+      <c r="N112" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M112,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O112" s="19" t="n">
+        <f aca="false">M112*(1-N112/12)</f>
+        <v>598027.552396978</v>
+      </c>
+      <c r="P112" s="19" t="n">
+        <f aca="false">P111+M112*N112/12</f>
+        <v>16757.2233859762</v>
+      </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="18" t="n">
@@ -6693,6 +8548,22 @@
         <f aca="false">L112+((G112+C113)+J112)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>8794.2118062693</v>
       </c>
+      <c r="M113" s="19" t="n">
+        <f aca="false">(O112+C113)*(1+Předpoklady!$B$12)</f>
+        <v>605431.503705454</v>
+      </c>
+      <c r="N113" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M113,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O113" s="19" t="n">
+        <f aca="false">M113*(1-N113/12)</f>
+        <v>605148.969003725</v>
+      </c>
+      <c r="P113" s="19" t="n">
+        <f aca="false">P112+M113*N113/12</f>
+        <v>17039.7580877054</v>
+      </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="18" t="n">
@@ -6742,6 +8613,22 @@
         <f aca="false">L113+((G113+C114)+J113)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>8971.65509008403</v>
       </c>
+      <c r="M114" s="19" t="n">
+        <f aca="false">(O113+C114)*(1+Předpoklady!$B$12)</f>
+        <v>612593.18583706</v>
+      </c>
+      <c r="N114" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M114,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O114" s="19" t="n">
+        <f aca="false">M114*(1-N114/12)</f>
+        <v>612307.309017003</v>
+      </c>
+      <c r="P114" s="19" t="n">
+        <f aca="false">P113+M114*N114/12</f>
+        <v>17325.6349077627</v>
+      </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="18" t="n">
@@ -6791,6 +8678,22 @@
         <f aca="false">L114+((G114+C115)+J114)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>9151.06270652538</v>
       </c>
+      <c r="M115" s="19" t="n">
+        <f aca="false">(O114+C115)*(1+Předpoklady!$B$12)</f>
+        <v>619792.000145505</v>
+      </c>
+      <c r="N115" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M115,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O115" s="19" t="n">
+        <f aca="false">M115*(1-N115/12)</f>
+        <v>619502.763878771</v>
+      </c>
+      <c r="P115" s="19" t="n">
+        <f aca="false">P114+M115*N115/12</f>
+        <v>17614.8711744973</v>
+      </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="18" t="n">
@@ -6840,6 +8743,22 @@
         <f aca="false">L115+((G115+C116)+J115)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>9332.44526835579</v>
       </c>
+      <c r="M116" s="19" t="n">
+        <f aca="false">(O115+C116)*(1+Předpoklady!$B$12)</f>
+        <v>627028.13915519</v>
+      </c>
+      <c r="N116" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M116,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O116" s="19" t="n">
+        <f aca="false">M116*(1-N116/12)</f>
+        <v>626735.526023585</v>
+      </c>
+      <c r="P116" s="19" t="n">
+        <f aca="false">P115+M116*N116/12</f>
+        <v>17907.4843061031</v>
+      </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="18" t="n">
@@ -6889,6 +8808,22 @@
         <f aca="false">L116+((G116+C117)+J116)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>9515.81344567561</v>
       </c>
+      <c r="M117" s="19" t="n">
+        <f aca="false">(O116+C117)*(1+Předpoklady!$B$12)</f>
+        <v>634301.796388724</v>
+      </c>
+      <c r="N117" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M117,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O117" s="19" t="n">
+        <f aca="false">M117*(1-N117/12)</f>
+        <v>634005.788883742</v>
+      </c>
+      <c r="P117" s="19" t="n">
+        <f aca="false">P116+M117*N117/12</f>
+        <v>18203.4918110845</v>
+      </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="18" t="n">
@@ -6938,6 +8873,22 @@
         <f aca="false">L117+((G117+C118)+J117)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>9701.17796623289</v>
       </c>
+      <c r="M118" s="19" t="n">
+        <f aca="false">(O117+C118)*(1+Předpoklady!$B$12)</f>
+        <v>641613.166372097</v>
+      </c>
+      <c r="N118" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M118,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O118" s="19" t="n">
+        <f aca="false">M118*(1-N118/12)</f>
+        <v>641313.746894457</v>
+      </c>
+      <c r="P118" s="19" t="n">
+        <f aca="false">P117+M118*N118/12</f>
+        <v>18502.9112887248</v>
+      </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="18" t="n">
@@ -6987,6 +8938,22 @@
         <f aca="false">L118+((G118+C119)+J118)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>9888.54961573484</v>
       </c>
+      <c r="M119" s="19" t="n">
+        <f aca="false">(O118+C119)*(1+Předpoklady!$B$12)</f>
+        <v>648962.444639889</v>
+      </c>
+      <c r="N119" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M119,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O119" s="19" t="n">
+        <f aca="false">M119*(1-N119/12)</f>
+        <v>648659.595499057</v>
+      </c>
+      <c r="P119" s="19" t="n">
+        <f aca="false">P118+M119*N119/12</f>
+        <v>18805.7604295567</v>
+      </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="18" t="n">
@@ -7036,6 +9003,22 @@
         <f aca="false">L119+((G119+C120)+J119)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>10077.9392381609</v>
       </c>
+      <c r="M120" s="19" t="n">
+        <f aca="false">(O119+C120)*(1+Předpoklady!$B$12)</f>
+        <v>656349.827740494</v>
+      </c>
+      <c r="N120" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M120,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O120" s="19" t="n">
+        <f aca="false">M120*(1-N120/12)</f>
+        <v>656043.531154216</v>
+      </c>
+      <c r="P120" s="19" t="n">
+        <f aca="false">P119+M120*N120/12</f>
+        <v>19112.0570158356</v>
+      </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="18" t="n">
@@ -7085,6 +9068,22 @@
         <f aca="false">L120+((G120+C121)+J120)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>10269.3577360777</v>
       </c>
+      <c r="M121" s="19" t="n">
+        <f aca="false">(O120+C121)*(1+Předpoklady!$B$12)</f>
+        <v>663775.513241378</v>
+      </c>
+      <c r="N121" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M121,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O121" s="19" t="n">
+        <f aca="false">M121*(1-N121/12)</f>
+        <v>663465.751335199</v>
+      </c>
+      <c r="P121" s="19" t="n">
+        <f aca="false">P120+M121*N121/12</f>
+        <v>19421.8189220149</v>
+      </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="18" t="n">
@@ -7134,6 +9133,22 @@
         <f aca="false">L121+((G121+C122)+J121)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>10462.8160709555</v>
       </c>
+      <c r="M122" s="19" t="n">
+        <f aca="false">(O121+C122)*(1+Předpoklady!$B$12)</f>
+        <v>671239.699734361</v>
+      </c>
+      <c r="N122" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M122,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O122" s="19" t="n">
+        <f aca="false">M122*(1-N122/12)</f>
+        <v>670926.454541152</v>
+      </c>
+      <c r="P122" s="19" t="n">
+        <f aca="false">P121+M122*N122/12</f>
+        <v>19735.0641152243</v>
+      </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="18" t="n">
@@ -7183,6 +9198,22 @@
         <f aca="false">L122+((G122+C123)+J122)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>10658.3252634864</v>
       </c>
+      <c r="M123" s="19" t="n">
+        <f aca="false">(O122+C123)*(1+Předpoklady!$B$12)</f>
+        <v>678742.586840934</v>
+      </c>
+      <c r="N123" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M123,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O123" s="19" t="n">
+        <f aca="false">M123*(1-N123/12)</f>
+        <v>678425.840300408</v>
+      </c>
+      <c r="P123" s="19" t="n">
+        <f aca="false">P122+M123*N123/12</f>
+        <v>20051.8106557501</v>
+      </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="18" t="n">
@@ -7232,6 +9263,22 @@
         <f aca="false">L123+((G123+C124)+J123)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>10855.8963939043</v>
       </c>
+      <c r="M124" s="19" t="n">
+        <f aca="false">(O123+C124)*(1+Předpoklady!$B$12)</f>
+        <v>686284.375217589</v>
+      </c>
+      <c r="N124" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M124,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O124" s="19" t="n">
+        <f aca="false">M124*(1-N124/12)</f>
+        <v>685964.109175821</v>
+      </c>
+      <c r="P124" s="19" t="n">
+        <f aca="false">P123+M124*N124/12</f>
+        <v>20372.0766975183</v>
+      </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="18" t="n">
@@ -7281,6 +9328,22 @@
         <f aca="false">L124+((G124+C125)+J124)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>11055.5406023067</v>
       </c>
+      <c r="M125" s="19" t="n">
+        <f aca="false">(O124+C125)*(1+Předpoklady!$B$12)</f>
+        <v>693865.266561192</v>
+      </c>
+      <c r="N125" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M125,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O125" s="19" t="n">
+        <f aca="false">M125*(1-N125/12)</f>
+        <v>693541.46277013</v>
+      </c>
+      <c r="P125" s="19" t="n">
+        <f aca="false">P124+M125*N125/12</f>
+        <v>20695.8804885802</v>
+      </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="18" t="n">
@@ -7330,6 +9393,22 @@
         <f aca="false">L125+((G125+C126)+J125)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>11259.0792664399</v>
       </c>
+      <c r="M126" s="19" t="n">
+        <f aca="false">(O125+C126)*(1+Předpoklady!$B$12)</f>
+        <v>701485.463614376</v>
+      </c>
+      <c r="N126" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M126,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O126" s="19" t="n">
+        <f aca="false">M126*(1-N126/12)</f>
+        <v>701158.103731356</v>
+      </c>
+      <c r="P126" s="19" t="n">
+        <f aca="false">P125+M126*N126/12</f>
+        <v>21023.2403716002</v>
+      </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="18" t="n">
@@ -7379,6 +9458,22 @@
         <f aca="false">L126+((G126+C127)+J126)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>11464.723249542</v>
       </c>
+      <c r="M127" s="19" t="n">
+        <f aca="false">(O126+C127)*(1+Předpoklady!$B$12)</f>
+        <v>709145.17017096</v>
+      </c>
+      <c r="N127" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M127,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O127" s="19" t="n">
+        <f aca="false">M127*(1-N127/12)</f>
+        <v>708814.235758214</v>
+      </c>
+      <c r="P127" s="19" t="n">
+        <f aca="false">P126+M127*N127/12</f>
+        <v>21354.1747843467</v>
+      </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="18" t="n">
@@ -7428,6 +9523,22 @@
         <f aca="false">L127+((G127+C128)+J127)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>11672.4839260871</v>
       </c>
+      <c r="M128" s="19" t="n">
+        <f aca="false">(O127+C128)*(1+Předpoklady!$B$12)</f>
+        <v>716844.591081403</v>
+      </c>
+      <c r="N128" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M128,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O128" s="19" t="n">
+        <f aca="false">M128*(1-N128/12)</f>
+        <v>716510.063605565</v>
+      </c>
+      <c r="P128" s="19" t="n">
+        <f aca="false">P127+M128*N128/12</f>
+        <v>21688.7022601846</v>
+      </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="18" t="n">
@@ -7477,6 +9588,22 @@
         <f aca="false">L128+((G128+C129)+J128)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>11882.3727320021</v>
       </c>
+      <c r="M129" s="19" t="n">
+        <f aca="false">(O128+C129)*(1+Předpoklady!$B$12)</f>
+        <v>724583.932258279</v>
+      </c>
+      <c r="N129" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M129,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O129" s="19" t="n">
+        <f aca="false">M129*(1-N129/12)</f>
+        <v>724245.793089892</v>
+      </c>
+      <c r="P129" s="19" t="n">
+        <f aca="false">P128+M129*N129/12</f>
+        <v>22026.8414285718</v>
+      </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="18" t="n">
@@ -7526,6 +9653,22 @@
         <f aca="false">L129+((G129+C130)+J129)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>12094.4011649994</v>
       </c>
+      <c r="M130" s="19" t="n">
+        <f aca="false">(O129+C130)*(1+Předpoklady!$B$12)</f>
+        <v>732363.400681789</v>
+      </c>
+      <c r="N130" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M130,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O130" s="19" t="n">
+        <f aca="false">M130*(1-N130/12)</f>
+        <v>732021.631094804</v>
+      </c>
+      <c r="P130" s="19" t="n">
+        <f aca="false">P129+M130*N130/12</f>
+        <v>22368.6110155567</v>
+      </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="18" t="n">
@@ -7575,6 +9718,22 @@
         <f aca="false">L130+((G130+C131)+J130)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>12308.5807849103</v>
       </c>
+      <c r="M131" s="19" t="n">
+        <f aca="false">(O130+C131)*(1+Předpoklady!$B$12)</f>
+        <v>740183.204405289</v>
+      </c>
+      <c r="N131" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M131,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O131" s="19" t="n">
+        <f aca="false">M131*(1-N131/12)</f>
+        <v>739837.785576567</v>
+      </c>
+      <c r="P131" s="19" t="n">
+        <f aca="false">P130+M131*N131/12</f>
+        <v>22714.0298442791</v>
+      </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="18" t="n">
@@ -7624,6 +9783,22 @@
         <f aca="false">L131+((G131+C132)+J131)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>12524.923214021</v>
       </c>
+      <c r="M132" s="19" t="n">
+        <f aca="false">(O131+C132)*(1+Předpoklady!$B$12)</f>
+        <v>748043.552560862</v>
+      </c>
+      <c r="N132" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M132,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O132" s="19" t="n">
+        <f aca="false">M132*(1-N132/12)</f>
+        <v>747694.465569667</v>
+      </c>
+      <c r="P132" s="19" t="n">
+        <f aca="false">P131+M132*N132/12</f>
+        <v>23063.1168354742</v>
+      </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="18" t="n">
@@ -7673,6 +9848,22 @@
         <f aca="false">L132+((G132+C133)+J132)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>12743.4401374096</v>
       </c>
+      <c r="M133" s="19" t="n">
+        <f aca="false">(O132+C133)*(1+Předpoklady!$B$12)</f>
+        <v>755944.655364906</v>
+      </c>
+      <c r="N133" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M133,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O133" s="19" t="n">
+        <f aca="false">M133*(1-N133/12)</f>
+        <v>755591.881192402</v>
+      </c>
+      <c r="P133" s="19" t="n">
+        <f aca="false">P132+M133*N133/12</f>
+        <v>23415.8910079778</v>
+      </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="18" t="n">
@@ -7722,6 +9913,22 @@
         <f aca="false">L133+((G133+C134)+J133)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>12964.1433032855</v>
       </c>
+      <c r="M134" s="19" t="n">
+        <f aca="false">(O133+C134)*(1+Předpoklady!$B$12)</f>
+        <v>763886.724123757</v>
+      </c>
+      <c r="N134" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M134,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O134" s="19" t="n">
+        <f aca="false">M134*(1-N134/12)</f>
+        <v>763530.243652499</v>
+      </c>
+      <c r="P134" s="19" t="n">
+        <f aca="false">P133+M134*N134/12</f>
+        <v>23772.3714792356</v>
+      </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="18" t="n">
@@ -7771,6 +9978,22 @@
         <f aca="false">L134+((G134+C135)+J134)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>13187.0445233307</v>
       </c>
+      <c r="M135" s="19" t="n">
+        <f aca="false">(O134+C135)*(1+Předpoklady!$B$12)</f>
+        <v>771869.971239341</v>
+      </c>
+      <c r="N135" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M135,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O135" s="19" t="n">
+        <f aca="false">M135*(1-N135/12)</f>
+        <v>771509.765252763</v>
+      </c>
+      <c r="P135" s="19" t="n">
+        <f aca="false">P134+M135*N135/12</f>
+        <v>24132.5774658139</v>
+      </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="18" t="n">
@@ -7820,6 +10043,22 @@
         <f aca="false">L135+((G135+C136)+J135)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>13412.1556730425</v>
       </c>
+      <c r="M136" s="19" t="n">
+        <f aca="false">(O135+C136)*(1+Předpoklady!$B$12)</f>
+        <v>779894.610214854</v>
+      </c>
+      <c r="N136" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M136,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O136" s="19" t="n">
+        <f aca="false">M136*(1-N136/12)</f>
+        <v>779530.659396754</v>
+      </c>
+      <c r="P136" s="19" t="n">
+        <f aca="false">P135+M136*N136/12</f>
+        <v>24496.5282839142</v>
+      </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="18" t="n">
@@ -7869,6 +10108,22 @@
         <f aca="false">L136+((G136+C137)+J136)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>13639.4886920783</v>
       </c>
+      <c r="M137" s="19" t="n">
+        <f aca="false">(O136+C137)*(1+Předpoklady!$B$12)</f>
+        <v>787960.855660473</v>
+      </c>
+      <c r="N137" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M137,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O137" s="19" t="n">
+        <f aca="false">M137*(1-N137/12)</f>
+        <v>787593.140594498</v>
+      </c>
+      <c r="P137" s="19" t="n">
+        <f aca="false">P136+M137*N137/12</f>
+        <v>24864.2433498891</v>
+      </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="18" t="n">
@@ -7918,6 +10173,22 @@
         <f aca="false">L137+((G137+C138)+J137)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>13870.8657620639</v>
       </c>
+      <c r="M138" s="19" t="n">
+        <f aca="false">(O137+C138)*(1+Předpoklady!$B$12)</f>
+        <v>796068.923299092</v>
+      </c>
+      <c r="N138" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M138,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O138" s="19" t="n">
+        <f aca="false">M138*(1-N138/12)</f>
+        <v>795697.424468219</v>
+      </c>
+      <c r="P138" s="19" t="n">
+        <f aca="false">P137+M138*N138/12</f>
+        <v>25235.742180762</v>
+      </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="18" t="n">
@@ -7967,6 +10238,22 @@
         <f aca="false">L138+((G138+C139)+J138)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>14104.4985544605</v>
       </c>
+      <c r="M139" s="19" t="n">
+        <f aca="false">(O138+C139)*(1+Předpoklady!$B$12)</f>
+        <v>804219.029972096</v>
+      </c>
+      <c r="N139" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M139,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O139" s="19" t="n">
+        <f aca="false">M139*(1-N139/12)</f>
+        <v>803843.727758109</v>
+      </c>
+      <c r="P139" s="19" t="n">
+        <f aca="false">P138+M139*N139/12</f>
+        <v>25611.044394749</v>
+      </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="18" t="n">
@@ -8016,6 +10303,22 @@
         <f aca="false">L139+((G139+C140)+J139)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>14340.3992563314</v>
       </c>
+      <c r="M140" s="19" t="n">
+        <f aca="false">(O139+C140)*(1+Předpoklady!$B$12)</f>
+        <v>812411.393645157</v>
+      </c>
+      <c r="N140" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M140,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O140" s="19" t="n">
+        <f aca="false">M140*(1-N140/12)</f>
+        <v>812032.268328123</v>
+      </c>
+      <c r="P140" s="19" t="n">
+        <f aca="false">P139+M140*N140/12</f>
+        <v>25990.1697117834</v>
+      </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="18" t="n">
@@ -8065,6 +10368,22 @@
         <f aca="false">L140+((G140+C141)+J140)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>14578.5801205834</v>
       </c>
+      <c r="M141" s="19" t="n">
+        <f aca="false">(O140+C141)*(1+Předpoklady!$B$12)</f>
+        <v>820646.233414064</v>
+      </c>
+      <c r="N141" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M141,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O141" s="19" t="n">
+        <f aca="false">M141*(1-N141/12)</f>
+        <v>820263.265171804</v>
+      </c>
+      <c r="P141" s="19" t="n">
+        <f aca="false">P140+M141*N141/12</f>
+        <v>26373.1379540433</v>
+      </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="18" t="n">
@@ -8114,6 +10433,22 @@
         <f aca="false">L141+((G141+C142)+J141)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>14819.0534663223</v>
       </c>
+      <c r="M142" s="19" t="n">
+        <f aca="false">(O141+C142)*(1+Předpoklady!$B$12)</f>
+        <v>828923.769510583</v>
+      </c>
+      <c r="N142" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M142,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O142" s="19" t="n">
+        <f aca="false">M142*(1-N142/12)</f>
+        <v>828536.938418145</v>
+      </c>
+      <c r="P142" s="19" t="n">
+        <f aca="false">P141+M142*N142/12</f>
+        <v>26759.9690464816</v>
+      </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="18" t="n">
@@ -8163,6 +10498,22 @@
         <f aca="false">L142+((G142+C143)+J142)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>15061.8316792111</v>
       </c>
+      <c r="M143" s="19" t="n">
+        <f aca="false">(O142+C143)*(1+Předpoklady!$B$12)</f>
+        <v>837244.223308346</v>
+      </c>
+      <c r="N143" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M143,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O143" s="19" t="n">
+        <f aca="false">M143*(1-N143/12)</f>
+        <v>836853.509337469</v>
+      </c>
+      <c r="P143" s="19" t="n">
+        <f aca="false">P142+M143*N143/12</f>
+        <v>27150.6830173588</v>
+      </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="18" t="n">
@@ -8212,6 +10563,22 @@
         <f aca="false">L143+((G143+C144)+J143)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>15306.9272118287</v>
       </c>
+      <c r="M144" s="19" t="n">
+        <f aca="false">(O143+C144)*(1+Předpoklady!$B$12)</f>
+        <v>845607.817328773</v>
+      </c>
+      <c r="N144" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M144,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O144" s="19" t="n">
+        <f aca="false">M144*(1-N144/12)</f>
+        <v>845213.200347353</v>
+      </c>
+      <c r="P144" s="19" t="n">
+        <f aca="false">P143+M144*N144/12</f>
+        <v>27545.2999987789</v>
+      </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="18" t="n">
@@ -8261,6 +10628,22 @@
         <f aca="false">L144+((G144+C145)+J144)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>15554.3525840323</v>
       </c>
+      <c r="M145" s="19" t="n">
+        <f aca="false">(O144+C145)*(1+Předpoklady!$B$12)</f>
+        <v>854014.77524702</v>
+      </c>
+      <c r="N145" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M145,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O145" s="19" t="n">
+        <f aca="false">M145*(1-N145/12)</f>
+        <v>853616.235018572</v>
+      </c>
+      <c r="P145" s="19" t="n">
+        <f aca="false">P144+M145*N145/12</f>
+        <v>27943.8402272275</v>
+      </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="18" t="n">
@@ -8310,6 +10693,22 @@
         <f aca="false">L145+((G145+C146)+J145)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>15804.1203833205</v>
       </c>
+      <c r="M146" s="19" t="n">
+        <f aca="false">(O145+C146)*(1+Předpoklady!$B$12)</f>
+        <v>862465.321897966</v>
+      </c>
+      <c r="N146" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M146,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O146" s="19" t="n">
+        <f aca="false">M146*(1-N146/12)</f>
+        <v>862062.83808108</v>
+      </c>
+      <c r="P146" s="19" t="n">
+        <f aca="false">P145+M146*N146/12</f>
+        <v>28346.3240441132</v>
+      </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="18" t="n">
@@ -8359,6 +10758,22 @@
         <f aca="false">L146+((G146+C147)+J146)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>16056.2432651987</v>
       </c>
+      <c r="M147" s="19" t="n">
+        <f aca="false">(O146+C147)*(1+Předpoklady!$B$12)</f>
+        <v>870959.68328222</v>
+      </c>
+      <c r="N147" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M147,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O147" s="19" t="n">
+        <f aca="false">M147*(1-N147/12)</f>
+        <v>870553.235430021</v>
+      </c>
+      <c r="P147" s="19" t="n">
+        <f aca="false">P146+M147*N147/12</f>
+        <v>28752.7718963116</v>
+      </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="18" t="n">
@@ -8408,6 +10823,22 @@
         <f aca="false">L147+((G147+C148)+J147)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>16310.7339535465</v>
       </c>
+      <c r="M148" s="19" t="n">
+        <f aca="false">(O147+C148)*(1+Předpoklady!$B$12)</f>
+        <v>879498.086572168</v>
+      </c>
+      <c r="N148" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M148,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O148" s="19" t="n">
+        <f aca="false">M148*(1-N148/12)</f>
+        <v>879087.654131768</v>
+      </c>
+      <c r="P148" s="19" t="n">
+        <f aca="false">P147+M148*N148/12</f>
+        <v>29163.2043367119</v>
+      </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="18" t="n">
@@ -8457,6 +10888,22 @@
         <f aca="false">L148+((G148+C149)+J148)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>16567.6052409875</v>
       </c>
+      <c r="M149" s="19" t="n">
+        <f aca="false">(O148+C149)*(1+Předpoklady!$B$12)</f>
+        <v>888080.760118052</v>
+      </c>
+      <c r="N149" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M149,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O149" s="19" t="n">
+        <f aca="false">M149*(1-N149/12)</f>
+        <v>887666.322429996</v>
+      </c>
+      <c r="P149" s="19" t="n">
+        <f aca="false">P148+M149*N149/12</f>
+        <v>29577.642024767</v>
+      </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="18" t="n">
@@ -8506,6 +10953,22 @@
         <f aca="false">L149+((G149+C150)+J149)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>16828.6801667218</v>
       </c>
+      <c r="M150" s="19" t="n">
+        <f aca="false">(O149+C150)*(1+Předpoklady!$B$12)</f>
+        <v>896707.933454069</v>
+      </c>
+      <c r="N150" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M150,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O150" s="19" t="n">
+        <f aca="false">M150*(1-N150/12)</f>
+        <v>896289.46975179</v>
+      </c>
+      <c r="P150" s="19" t="n">
+        <f aca="false">P149+M150*N150/12</f>
+        <v>29996.1057270456</v>
+      </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="18" t="n">
@@ -8555,6 +11018,22 @@
         <f aca="false">L150+((G150+C151)+J150)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>17092.1712644183</v>
       </c>
+      <c r="M151" s="19" t="n">
+        <f aca="false">(O150+C151)*(1+Předpoklady!$B$12)</f>
+        <v>905379.837304517</v>
+      </c>
+      <c r="N151" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M151,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O151" s="19" t="n">
+        <f aca="false">M151*(1-N151/12)</f>
+        <v>904957.326713775</v>
+      </c>
+      <c r="P151" s="19" t="n">
+        <f aca="false">P150+M151*N151/12</f>
+        <v>30418.6163177877</v>
+      </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="18" t="n">
@@ -8604,6 +11083,22 @@
         <f aca="false">L151+((G151+C152)+J151)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>17358.0915880062</v>
       </c>
+      <c r="M152" s="19" t="n">
+        <f aca="false">(O151+C152)*(1+Předpoklady!$B$12)</f>
+        <v>914096.703589962</v>
+      </c>
+      <c r="N152" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M152,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O152" s="19" t="n">
+        <f aca="false">M152*(1-N152/12)</f>
+        <v>913670.125128286</v>
+      </c>
+      <c r="P152" s="19" t="n">
+        <f aca="false">P151+M152*N152/12</f>
+        <v>30845.194779463</v>
+      </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="18" t="n">
@@ -8653,6 +11148,22 @@
         <f aca="false">L152+((G152+C153)+J152)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>17626.4542619416</v>
       </c>
+      <c r="M153" s="19" t="n">
+        <f aca="false">(O152+C153)*(1+Předpoklady!$B$12)</f>
+        <v>922858.76543344</v>
+      </c>
+      <c r="N153" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M153,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O153" s="19" t="n">
+        <f aca="false">M153*(1-N153/12)</f>
+        <v>922428.098009571</v>
+      </c>
+      <c r="P153" s="19" t="n">
+        <f aca="false">P152+M153*N153/12</f>
+        <v>31275.8622033319</v>
+      </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="18" t="n">
@@ -8702,6 +11213,22 @@
         <f aca="false">L153+((G153+C154)+J153)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>17897.2724815884</v>
       </c>
+      <c r="M154" s="19" t="n">
+        <f aca="false">(O153+C154)*(1+Předpoklady!$B$12)</f>
+        <v>931666.257166694</v>
+      </c>
+      <c r="N154" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M154,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O154" s="19" t="n">
+        <f aca="false">M154*(1-N154/12)</f>
+        <v>931231.479580017</v>
+      </c>
+      <c r="P154" s="19" t="n">
+        <f aca="false">P153+M154*N154/12</f>
+        <v>31710.6397900097</v>
+      </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="18" t="n">
@@ -8751,6 +11278,22 @@
         <f aca="false">L154+((G154+C155)+J154)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>18170.5595136018</v>
       </c>
+      <c r="M155" s="19" t="n">
+        <f aca="false">(O154+C155)*(1+Předpoklady!$B$12)</f>
+        <v>940519.41433644</v>
+      </c>
+      <c r="N155" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M155,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O155" s="19" t="n">
+        <f aca="false">M155*(1-N155/12)</f>
+        <v>940080.505276417</v>
+      </c>
+      <c r="P155" s="19" t="n">
+        <f aca="false">P154+M155*N155/12</f>
+        <v>32149.5488500334</v>
+      </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="18" t="n">
@@ -8800,6 +11343,22 @@
         <f aca="false">L155+((G155+C156)+J155)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>18446.3286963129</v>
       </c>
+      <c r="M156" s="19" t="n">
+        <f aca="false">(O155+C156)*(1+Předpoklady!$B$12)</f>
+        <v>949418.473710665</v>
+      </c>
+      <c r="N156" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M156,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O156" s="19" t="n">
+        <f aca="false">M156*(1-N156/12)</f>
+        <v>948975.411756266</v>
+      </c>
+      <c r="P156" s="19" t="n">
+        <f aca="false">P155+M156*N156/12</f>
+        <v>32592.6108044317</v>
+      </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="18" t="n">
@@ -8849,6 +11408,22 @@
         <f aca="false">L156+((G156+C157)+J156)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>18724.5934401164</v>
       </c>
+      <c r="M157" s="19" t="n">
+        <f aca="false">(O156+C157)*(1+Předpoklady!$B$12)</f>
+        <v>958363.673284959</v>
+      </c>
+      <c r="N157" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M157,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O157" s="19" t="n">
+        <f aca="false">M157*(1-N157/12)</f>
+        <v>957916.436904092</v>
+      </c>
+      <c r="P157" s="19" t="n">
+        <f aca="false">P156+M157*N157/12</f>
+        <v>33039.847185298</v>
+      </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="18" t="n">
@@ -8898,6 +11473,22 @@
         <f aca="false">L157+((G157+C158)+J157)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>19005.3672278596</v>
       </c>
+      <c r="M158" s="19" t="n">
+        <f aca="false">(O157+C158)*(1+Předpoklady!$B$12)</f>
+        <v>967355.252288883</v>
+      </c>
+      <c r="N158" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M158,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O158" s="19" t="n">
+        <f aca="false">M158*(1-N158/12)</f>
+        <v>966903.819837815</v>
+      </c>
+      <c r="P158" s="19" t="n">
+        <f aca="false">P157+M158*N158/12</f>
+        <v>33491.2796363662</v>
+      </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="18" t="n">
@@ -8947,6 +11538,22 @@
         <f aca="false">L158+((G158+C159)+J158)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>19288.6636152342</v>
       </c>
+      <c r="M159" s="19" t="n">
+        <f aca="false">(O158+C159)*(1+Předpoklady!$B$12)</f>
+        <v>976393.451192365</v>
+      </c>
+      <c r="N159" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M159,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O159" s="19" t="n">
+        <f aca="false">M159*(1-N159/12)</f>
+        <v>975937.800915142</v>
+      </c>
+      <c r="P159" s="19" t="n">
+        <f aca="false">P158+M159*N159/12</f>
+        <v>33946.9299135893</v>
+      </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="18" t="n">
@@ -8996,6 +11603,22 @@
         <f aca="false">L159+((G159+C160)+J159)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>19574.4962311696</v>
       </c>
+      <c r="M160" s="19" t="n">
+        <f aca="false">(O159+C160)*(1+Předpoklady!$B$12)</f>
+        <v>985478.51171213</v>
+      </c>
+      <c r="N160" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M160,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O160" s="19" t="n">
+        <f aca="false">M160*(1-N160/12)</f>
+        <v>985018.621739998</v>
+      </c>
+      <c r="P160" s="19" t="n">
+        <f aca="false">P159+M160*N160/12</f>
+        <v>34406.8198857216</v>
+      </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="18" t="n">
@@ -9045,6 +11668,22 @@
         <f aca="false">L160+((G160+C161)+J160)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>19862.8787782285</v>
       </c>
+      <c r="M161" s="19" t="n">
+        <f aca="false">(O160+C161)*(1+Předpoklady!$B$12)</f>
+        <v>994610.676818167</v>
+      </c>
+      <c r="N161" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M161,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0056</v>
+      </c>
+      <c r="O161" s="19" t="n">
+        <f aca="false">M161*(1-N161/12)</f>
+        <v>994146.525168985</v>
+      </c>
+      <c r="P161" s="19" t="n">
+        <f aca="false">P160+M161*N161/12</f>
+        <v>34870.9715349034</v>
+      </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="18" t="n">
@@ -9094,6 +11733,22 @@
         <f aca="false">L161+((G161+C162)+J161)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>20155.6352104668</v>
       </c>
+      <c r="M162" s="19" t="n">
+        <f aca="false">(O161+C162)*(1+Předpoklady!$B$12)</f>
+        <v>1003790.19074022</v>
+      </c>
+      <c r="N162" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M162,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O162" s="19" t="n">
+        <f aca="false">M162*(1-N162/12)</f>
+        <v>1003438.86417347</v>
+      </c>
+      <c r="P162" s="19" t="n">
+        <f aca="false">P161+M162*N162/12</f>
+        <v>35222.2981016625</v>
+      </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="18" t="n">
@@ -9143,6 +11798,22 @@
         <f aca="false">L162+((G162+C163)+J162)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>20450.9789813515</v>
       </c>
+      <c r="M163" s="19" t="n">
+        <f aca="false">(O162+C163)*(1+Předpoklady!$B$12)</f>
+        <v>1013135.06998042</v>
+      </c>
+      <c r="N163" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M163,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O163" s="19" t="n">
+        <f aca="false">M163*(1-N163/12)</f>
+        <v>1012780.47270593</v>
+      </c>
+      <c r="P163" s="19" t="n">
+        <f aca="false">P162+M163*N163/12</f>
+        <v>35576.8953761556</v>
+      </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="18" t="n">
@@ -9192,6 +11863,22 @@
         <f aca="false">L163+((G163+C164)+J163)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>20748.9240695796</v>
       </c>
+      <c r="M164" s="19" t="n">
+        <f aca="false">(O163+C164)*(1+Předpoklady!$B$12)</f>
+        <v>1022529.49732569</v>
+      </c>
+      <c r="N164" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M164,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O164" s="19" t="n">
+        <f aca="false">M164*(1-N164/12)</f>
+        <v>1022171.61200162</v>
+      </c>
+      <c r="P164" s="19" t="n">
+        <f aca="false">P163+M164*N164/12</f>
+        <v>35934.7807002196</v>
+      </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="18" t="n">
@@ -9241,6 +11928,22 @@
         <f aca="false">L164+((G164+C165)+J164)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>21049.4845293711</v>
       </c>
+      <c r="M165" s="19" t="n">
+        <f aca="false">(O164+C165)*(1+Předpoklady!$B$12)</f>
+        <v>1031973.73548831</v>
+      </c>
+      <c r="N165" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M165,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O165" s="19" t="n">
+        <f aca="false">M165*(1-N165/12)</f>
+        <v>1031612.54468089</v>
+      </c>
+      <c r="P165" s="19" t="n">
+        <f aca="false">P164+M165*N165/12</f>
+        <v>36295.9715076405</v>
+      </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="18" t="n">
@@ -9290,6 +11993,22 @@
         <f aca="false">L165+((G165+C166)+J165)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>21352.6744908773</v>
       </c>
+      <c r="M166" s="19" t="n">
+        <f aca="false">(O165+C166)*(1+Předpoklady!$B$12)</f>
+        <v>1041468.04857353</v>
+      </c>
+      <c r="N166" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M166,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O166" s="19" t="n">
+        <f aca="false">M166*(1-N166/12)</f>
+        <v>1041103.53475653</v>
+      </c>
+      <c r="P166" s="19" t="n">
+        <f aca="false">P165+M166*N166/12</f>
+        <v>36660.4853246413</v>
+      </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="18" t="n">
@@ -9339,6 +12058,22 @@
         <f aca="false">L166+((G166+C167)+J166)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>21658.5081605908</v>
       </c>
+      <c r="M167" s="19" t="n">
+        <f aca="false">(O166+C167)*(1+Předpoklady!$B$12)</f>
+        <v>1051012.70208694</v>
+      </c>
+      <c r="N167" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M167,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O167" s="19" t="n">
+        <f aca="false">M167*(1-N167/12)</f>
+        <v>1050644.84764121</v>
+      </c>
+      <c r="P167" s="19" t="n">
+        <f aca="false">P166+M167*N167/12</f>
+        <v>37028.3397703717</v>
+      </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="18" t="n">
@@ -9388,6 +12123,22 @@
         <f aca="false">L167+((G167+C168)+J167)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>21966.9998217582</v>
       </c>
+      <c r="M168" s="19" t="n">
+        <f aca="false">(O167+C168)*(1+Předpoklady!$B$12)</f>
+        <v>1060607.96294185</v>
+      </c>
+      <c r="N168" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M168,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O168" s="19" t="n">
+        <f aca="false">M168*(1-N168/12)</f>
+        <v>1060236.75015482</v>
+      </c>
+      <c r="P168" s="19" t="n">
+        <f aca="false">P167+M168*N168/12</f>
+        <v>37399.5525574013</v>
+      </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="18" t="n">
@@ -9437,6 +12188,22 @@
         <f aca="false">L168+((G168+C169)+J168)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>22278.1638347945</v>
       </c>
+      <c r="M169" s="19" t="n">
+        <f aca="false">(O168+C169)*(1+Předpoklady!$B$12)</f>
+        <v>1070254.09946681</v>
+      </c>
+      <c r="N169" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M169,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O169" s="19" t="n">
+        <f aca="false">M169*(1-N169/12)</f>
+        <v>1069879.510532</v>
+      </c>
+      <c r="P169" s="19" t="n">
+        <f aca="false">P168+M169*N169/12</f>
+        <v>37774.1414922147</v>
+      </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="18" t="n">
@@ -9486,6 +12253,22 @@
         <f aca="false">L169+((G169+C170)+J169)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>22592.0146377004</v>
       </c>
+      <c r="M170" s="19" t="n">
+        <f aca="false">(O169+C170)*(1+Předpoklady!$B$12)</f>
+        <v>1079951.3814131</v>
+      </c>
+      <c r="N170" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M170,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O170" s="19" t="n">
+        <f aca="false">M170*(1-N170/12)</f>
+        <v>1079573.39842961</v>
+      </c>
+      <c r="P170" s="19" t="n">
+        <f aca="false">P169+M170*N170/12</f>
+        <v>38152.1244757093</v>
+      </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="18" t="n">
@@ -9535,6 +12318,22 @@
         <f aca="false">L170+((G170+C171)+J170)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>22908.566746481</v>
       </c>
+      <c r="M171" s="19" t="n">
+        <f aca="false">(O170+C171)*(1+Předpoklady!$B$12)</f>
+        <v>1089700.07996225</v>
+      </c>
+      <c r="N171" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M171,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O171" s="19" t="n">
+        <f aca="false">M171*(1-N171/12)</f>
+        <v>1089318.68493427</v>
+      </c>
+      <c r="P171" s="19" t="n">
+        <f aca="false">P170+M171*N171/12</f>
+        <v>38533.5195036961</v>
+      </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="18" t="n">
@@ -9584,6 +12383,22 @@
         <f aca="false">L171+((G171+C172)+J171)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>23227.8347555677</v>
       </c>
+      <c r="M172" s="19" t="n">
+        <f aca="false">(O171+C172)*(1+Předpoklady!$B$12)</f>
+        <v>1099500.46773365</v>
+      </c>
+      <c r="N172" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M172,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O172" s="19" t="n">
+        <f aca="false">M172*(1-N172/12)</f>
+        <v>1099115.64256995</v>
+      </c>
+      <c r="P172" s="19" t="n">
+        <f aca="false">P171+M172*N172/12</f>
+        <v>38918.3446674029</v>
+      </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="18" t="n">
@@ -9633,6 +12448,22 @@
         <f aca="false">L172+((G172+C173)+J172)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>23549.8333382414</v>
       </c>
+      <c r="M173" s="19" t="n">
+        <f aca="false">(O172+C173)*(1+Předpoklady!$B$12)</f>
+        <v>1109352.81879216</v>
+      </c>
+      <c r="N173" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M173,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O173" s="19" t="n">
+        <f aca="false">M173*(1-N173/12)</f>
+        <v>1108964.54530558</v>
+      </c>
+      <c r="P173" s="19" t="n">
+        <f aca="false">P172+M173*N173/12</f>
+        <v>39306.6181539801</v>
+      </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="18" t="n">
@@ -9682,6 +12513,22 @@
         <f aca="false">L173+((G173+C174)+J173)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>23876.3874245208</v>
       </c>
+      <c r="M174" s="19" t="n">
+        <f aca="false">(O173+C174)*(1+Předpoklady!$B$12)</f>
+        <v>1119257.40865576</v>
+      </c>
+      <c r="N174" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M174,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O174" s="19" t="n">
+        <f aca="false">M174*(1-N174/12)</f>
+        <v>1118865.66856274</v>
+      </c>
+      <c r="P174" s="19" t="n">
+        <f aca="false">P173+M174*N174/12</f>
+        <v>39698.3582470097</v>
+      </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="18" t="n">
@@ -9731,6 +12578,22 @@
         <f aca="false">L174+((G174+C175)+J174)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>24205.7114491086</v>
       </c>
+      <c r="M175" s="19" t="n">
+        <f aca="false">(O174+C175)*(1+Předpoklady!$B$12)</f>
+        <v>1129214.51430331</v>
+      </c>
+      <c r="N175" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M175,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O175" s="19" t="n">
+        <f aca="false">M175*(1-N175/12)</f>
+        <v>1128819.28922331</v>
+      </c>
+      <c r="P175" s="19" t="n">
+        <f aca="false">P174+M175*N175/12</f>
+        <v>40093.5833270158</v>
+      </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="18" t="n">
@@ -9780,6 +12643,22 @@
         <f aca="false">L175+((G175+C176)+J175)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>24537.8203772388</v>
       </c>
+      <c r="M176" s="19" t="n">
+        <f aca="false">(O175+C176)*(1+Předpoklady!$B$12)</f>
+        <v>1139224.41418223</v>
+      </c>
+      <c r="N176" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M176,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O176" s="19" t="n">
+        <f aca="false">M176*(1-N176/12)</f>
+        <v>1138825.68563727</v>
+      </c>
+      <c r="P176" s="19" t="n">
+        <f aca="false">P175+M176*N176/12</f>
+        <v>40492.3118719796</v>
+      </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="18" t="n">
@@ -9829,6 +12708,22 @@
         <f aca="false">L176+((G176+C177)+J176)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>24872.7292549984</v>
       </c>
+      <c r="M177" s="19" t="n">
+        <f aca="false">(O176+C177)*(1+Předpoklady!$B$12)</f>
+        <v>1149287.38821632</v>
+      </c>
+      <c r="N177" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M177,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O177" s="19" t="n">
+        <f aca="false">M177*(1-N177/12)</f>
+        <v>1148885.13763045</v>
+      </c>
+      <c r="P177" s="19" t="n">
+        <f aca="false">P176+M177*N177/12</f>
+        <v>40894.5624578553</v>
+      </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="18" t="n">
@@ -9878,6 +12773,22 @@
         <f aca="false">L177+((G177+C178)+J177)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>25210.4532097645</v>
       </c>
+      <c r="M178" s="19" t="n">
+        <f aca="false">(O177+C178)*(1+Předpoklady!$B$12)</f>
+        <v>1159403.71781359</v>
+      </c>
+      <c r="N178" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M178,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O178" s="19" t="n">
+        <f aca="false">M178*(1-N178/12)</f>
+        <v>1158997.92651236</v>
+      </c>
+      <c r="P178" s="19" t="n">
+        <f aca="false">P177+M178*N178/12</f>
+        <v>41300.3537590901</v>
+      </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="18" t="n">
@@ -9927,6 +12838,22 @@
         <f aca="false">L178+((G178+C179)+J178)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>25551.0074506432</v>
       </c>
+      <c r="M179" s="19" t="n">
+        <f aca="false">(O178+C179)*(1+Předpoklady!$B$12)</f>
+        <v>1169573.68587411</v>
+      </c>
+      <c r="N179" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M179,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O179" s="19" t="n">
+        <f aca="false">M179*(1-N179/12)</f>
+        <v>1169164.33508405</v>
+      </c>
+      <c r="P179" s="19" t="n">
+        <f aca="false">P178+M179*N179/12</f>
+        <v>41709.704549146</v>
+      </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="18" t="n">
@@ -9976,6 +12903,22 @@
         <f aca="false">L179+((G179+C180)+J179)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>25894.4072689116</v>
       </c>
+      <c r="M180" s="19" t="n">
+        <f aca="false">(O179+C180)*(1+Předpoklady!$B$12)</f>
+        <v>1179797.57679794</v>
+      </c>
+      <c r="N180" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M180,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O180" s="19" t="n">
+        <f aca="false">M180*(1-N180/12)</f>
+        <v>1179384.64764606</v>
+      </c>
+      <c r="P180" s="19" t="n">
+        <f aca="false">P179+M180*N180/12</f>
+        <v>42122.6337010253</v>
+      </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="18" t="n">
@@ -10025,6 +12968,22 @@
         <f aca="false">L180+((G180+C181)+J180)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>26240.6680384611</v>
       </c>
+      <c r="M181" s="19" t="n">
+        <f aca="false">(O180+C181)*(1+Předpoklady!$B$12)</f>
+        <v>1190075.67649307</v>
+      </c>
+      <c r="N181" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M181,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O181" s="19" t="n">
+        <f aca="false">M181*(1-N181/12)</f>
+        <v>1189659.1500063</v>
+      </c>
+      <c r="P181" s="19" t="n">
+        <f aca="false">P180+M181*N181/12</f>
+        <v>42539.1601877979</v>
+      </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="18" t="n">
@@ -10074,6 +13033,22 @@
         <f aca="false">L181+((G181+C182)+J181)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>26589.8052162444</v>
       </c>
+      <c r="M182" s="19" t="n">
+        <f aca="false">(O181+C182)*(1+Předpoklady!$B$12)</f>
+        <v>1200408.27238344</v>
+      </c>
+      <c r="N182" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M182,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O182" s="19" t="n">
+        <f aca="false">M182*(1-N182/12)</f>
+        <v>1199988.12948811</v>
+      </c>
+      <c r="P182" s="19" t="n">
+        <f aca="false">P181+M182*N182/12</f>
+        <v>42959.3030831321</v>
+      </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="18" t="n">
@@ -10123,6 +13098,22 @@
         <f aca="false">L182+((G182+C183)+J182)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>26941.8343427239</v>
       </c>
+      <c r="M183" s="19" t="n">
+        <f aca="false">(O182+C183)*(1+Předpoklady!$B$12)</f>
+        <v>1210795.65341694</v>
+      </c>
+      <c r="N183" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M183,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O183" s="19" t="n">
+        <f aca="false">M183*(1-N183/12)</f>
+        <v>1210371.87493825</v>
+      </c>
+      <c r="P183" s="19" t="n">
+        <f aca="false">P182+M183*N183/12</f>
+        <v>43383.081561828</v>
+      </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="18" t="n">
@@ -10172,6 +13163,22 @@
         <f aca="false">L183+((G183+C184)+J183)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>27296.771042323</v>
       </c>
+      <c r="M184" s="19" t="n">
+        <f aca="false">(O183+C184)*(1+Předpoklady!$B$12)</f>
+        <v>1221238.11007352</v>
+      </c>
+      <c r="N184" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M184,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O184" s="19" t="n">
+        <f aca="false">M184*(1-N184/12)</f>
+        <v>1220810.676735</v>
+      </c>
+      <c r="P184" s="19" t="n">
+        <f aca="false">P183+M184*N184/12</f>
+        <v>43810.5149003537</v>
+      </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="18" t="n">
@@ -10221,6 +13228,22 @@
         <f aca="false">L184+((G184+C185)+J184)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>27654.6310238794</v>
       </c>
+      <c r="M185" s="19" t="n">
+        <f aca="false">(O184+C185)*(1+Předpoklady!$B$12)</f>
+        <v>1231735.9343733</v>
+      </c>
+      <c r="N185" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M185,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O185" s="19" t="n">
+        <f aca="false">M185*(1-N185/12)</f>
+        <v>1231304.82679627</v>
+      </c>
+      <c r="P185" s="19" t="n">
+        <f aca="false">P184+M185*N185/12</f>
+        <v>44241.6224773844</v>
+      </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="18" t="n">
@@ -10270,6 +13293,22 @@
         <f aca="false">L185+((G185+C186)+J185)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>28017.2402585635</v>
       </c>
+      <c r="M186" s="19" t="n">
+        <f aca="false">(O185+C186)*(1+Předpoklady!$B$12)</f>
+        <v>1242289.41988474</v>
+      </c>
+      <c r="N186" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M186,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O186" s="19" t="n">
+        <f aca="false">M186*(1-N186/12)</f>
+        <v>1241854.61858778</v>
+      </c>
+      <c r="P186" s="19" t="n">
+        <f aca="false">P185+M186*N186/12</f>
+        <v>44676.423774344</v>
+      </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="18" t="n">
@@ -10319,6 +13358,22 @@
         <f aca="false">L186+((G186+C187)+J186)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>28382.8142278548</v>
       </c>
+      <c r="M187" s="19" t="n">
+        <f aca="false">(O186+C187)*(1+Předpoklady!$B$12)</f>
+        <v>1252898.86173285</v>
+      </c>
+      <c r="N187" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M187,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O187" s="19" t="n">
+        <f aca="false">M187*(1-N187/12)</f>
+        <v>1252460.34713124</v>
+      </c>
+      <c r="P187" s="19" t="n">
+        <f aca="false">P186+M187*N187/12</f>
+        <v>45114.9383759505</v>
+      </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="18" t="n">
@@ -10368,6 +13423,22 @@
         <f aca="false">L187+((G187+C188)+J187)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>28751.3689494192</v>
       </c>
+      <c r="M188" s="19" t="n">
+        <f aca="false">(O187+C188)*(1+Předpoklady!$B$12)</f>
+        <v>1263564.55660743</v>
+      </c>
+      <c r="N188" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M188,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O188" s="19" t="n">
+        <f aca="false">M188*(1-N188/12)</f>
+        <v>1263122.30901262</v>
+      </c>
+      <c r="P188" s="19" t="n">
+        <f aca="false">P187+M188*N188/12</f>
+        <v>45557.1859707631</v>
+      </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="18" t="n">
@@ -10417,6 +13488,22 @@
         <f aca="false">L188+((G188+C189)+J188)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>29122.920527462</v>
       </c>
+      <c r="M189" s="19" t="n">
+        <f aca="false">(O188+C189)*(1+Předpoklady!$B$12)</f>
+        <v>1274286.8027714</v>
+      </c>
+      <c r="N189" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M189,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O189" s="19" t="n">
+        <f aca="false">M189*(1-N189/12)</f>
+        <v>1273840.80239043</v>
+      </c>
+      <c r="P189" s="19" t="n">
+        <f aca="false">P188+M189*N189/12</f>
+        <v>46003.1863517331</v>
+      </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="18" t="n">
@@ -10466,6 +13553,22 @@
         <f aca="false">L189+((G189+C190)+J189)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>29497.4851531953</v>
       </c>
+      <c r="M190" s="19" t="n">
+        <f aca="false">(O189+C190)*(1+Předpoklady!$B$12)</f>
+        <v>1285065.90006911</v>
+      </c>
+      <c r="N190" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M190,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O190" s="19" t="n">
+        <f aca="false">M190*(1-N190/12)</f>
+        <v>1284616.12700408</v>
+      </c>
+      <c r="P190" s="19" t="n">
+        <f aca="false">P189+M190*N190/12</f>
+        <v>46452.9594167573</v>
+      </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="18" t="n">
@@ -10515,6 +13618,22 @@
         <f aca="false">L190+((G190+C191)+J190)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>29875.0791053076</v>
       </c>
+      <c r="M191" s="19" t="n">
+        <f aca="false">(O190+C191)*(1+Předpoklady!$B$12)</f>
+        <v>1295902.14993472</v>
+      </c>
+      <c r="N191" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M191,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O191" s="19" t="n">
+        <f aca="false">M191*(1-N191/12)</f>
+        <v>1295448.58418224</v>
+      </c>
+      <c r="P191" s="19" t="n">
+        <f aca="false">P190+M191*N191/12</f>
+        <v>46906.5251692345</v>
+      </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="18" t="n">
@@ -10564,6 +13683,22 @@
         <f aca="false">L191+((G191+C192)+J191)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>30255.7187504372</v>
       </c>
+      <c r="M192" s="19" t="n">
+        <f aca="false">(O191+C192)*(1+Předpoklady!$B$12)</f>
+        <v>1306795.85540066</v>
+      </c>
+      <c r="N192" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M192,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O192" s="19" t="n">
+        <f aca="false">M192*(1-N192/12)</f>
+        <v>1306338.47685127</v>
+      </c>
+      <c r="P192" s="19" t="n">
+        <f aca="false">P191+M192*N192/12</f>
+        <v>47363.9037186247</v>
+      </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="18" t="n">
@@ -10613,6 +13748,22 @@
         <f aca="false">L192+((G192+C193)+J192)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>30639.4205436467</v>
       </c>
+      <c r="M193" s="19" t="n">
+        <f aca="false">(O192+C193)*(1+Předpoklady!$B$12)</f>
+        <v>1317747.3211061</v>
+      </c>
+      <c r="N193" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M193,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O193" s="19" t="n">
+        <f aca="false">M193*(1-N193/12)</f>
+        <v>1317286.10954372</v>
+      </c>
+      <c r="P193" s="19" t="n">
+        <f aca="false">P192+M193*N193/12</f>
+        <v>47825.1152810118</v>
+      </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="18" t="n">
@@ -10662,6 +13813,22 @@
         <f aca="false">L193+((G193+C194)+J193)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>31026.2010289011</v>
       </c>
+      <c r="M194" s="19" t="n">
+        <f aca="false">(O193+C194)*(1+Předpoklady!$B$12)</f>
+        <v>1328756.85330543</v>
+      </c>
+      <c r="N194" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M194,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O194" s="19" t="n">
+        <f aca="false">M194*(1-N194/12)</f>
+        <v>1328291.78840678</v>
+      </c>
+      <c r="P194" s="19" t="n">
+        <f aca="false">P193+M194*N194/12</f>
+        <v>48290.1801796687</v>
+      </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="18" t="n">
@@ -10711,6 +13878,22 @@
         <f aca="false">L194+((G194+C195)+J194)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>31416.0768395479</v>
       </c>
+      <c r="M195" s="19" t="n">
+        <f aca="false">(O194+C195)*(1+Předpoklady!$B$12)</f>
+        <v>1339824.75987688</v>
+      </c>
+      <c r="N195" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M195,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O195" s="19" t="n">
+        <f aca="false">M195*(1-N195/12)</f>
+        <v>1339355.82121092</v>
+      </c>
+      <c r="P195" s="19" t="n">
+        <f aca="false">P194+M195*N195/12</f>
+        <v>48759.1188456256</v>
+      </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="18" t="n">
@@ -10760,6 +13943,22 @@
         <f aca="false">L195+((G195+C196)+J195)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>31809.0646988002</v>
       </c>
+      <c r="M196" s="19" t="n">
+        <f aca="false">(O195+C196)*(1+Předpoklady!$B$12)</f>
+        <v>1350951.35033106</v>
+      </c>
+      <c r="N196" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M196,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O196" s="19" t="n">
+        <f aca="false">M196*(1-N196/12)</f>
+        <v>1350478.51735845</v>
+      </c>
+      <c r="P196" s="19" t="n">
+        <f aca="false">P195+M196*N196/12</f>
+        <v>49231.9518182415</v>
+      </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="18" t="n">
@@ -10809,6 +14008,22 @@
         <f aca="false">L196+((G196+C197)+J196)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>32205.1814202222</v>
       </c>
+      <c r="M197" s="19" t="n">
+        <f aca="false">(O196+C197)*(1+Předpoklady!$B$12)</f>
+        <v>1362136.93581971</v>
+      </c>
+      <c r="N197" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M197,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O197" s="19" t="n">
+        <f aca="false">M197*(1-N197/12)</f>
+        <v>1361660.18789217</v>
+      </c>
+      <c r="P197" s="19" t="n">
+        <f aca="false">P196+M197*N197/12</f>
+        <v>49708.6997457784</v>
+      </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="18" t="n">
@@ -10858,6 +14073,22 @@
         <f aca="false">L197+((G197+C198)+J197)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>32606.2540856788</v>
       </c>
+      <c r="M198" s="19" t="n">
+        <f aca="false">(O197+C198)*(1+Předpoklady!$B$12)</f>
+        <v>1373381.82914431</v>
+      </c>
+      <c r="N198" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M198,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O198" s="19" t="n">
+        <f aca="false">M198*(1-N198/12)</f>
+        <v>1372901.14550411</v>
+      </c>
+      <c r="P198" s="19" t="n">
+        <f aca="false">P197+M198*N198/12</f>
+        <v>50189.3833859789</v>
+      </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="18" t="n">
@@ -10907,6 +14138,22 @@
         <f aca="false">L198+((G198+C199)+J198)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>33010.4992933451</v>
       </c>
+      <c r="M199" s="19" t="n">
+        <f aca="false">(O198+C199)*(1+Předpoklady!$B$12)</f>
+        <v>1384686.34476487</v>
+      </c>
+      <c r="N199" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M199,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O199" s="19" t="n">
+        <f aca="false">M199*(1-N199/12)</f>
+        <v>1384201.7045442</v>
+      </c>
+      <c r="P199" s="19" t="n">
+        <f aca="false">P198+M199*N199/12</f>
+        <v>50674.0236066466</v>
+      </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="18" t="n">
@@ -10956,6 +14203,22 @@
         <f aca="false">L199+((G199+C200)+J199)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>33417.9341836158</v>
       </c>
+      <c r="M200" s="19" t="n">
+        <f aca="false">(O199+C200)*(1+Předpoklady!$B$12)</f>
+        <v>1396050.79880874</v>
+      </c>
+      <c r="N200" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M200,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O200" s="19" t="n">
+        <f aca="false">M200*(1-N200/12)</f>
+        <v>1395562.18102916</v>
+      </c>
+      <c r="P200" s="19" t="n">
+        <f aca="false">P199+M200*N200/12</f>
+        <v>51162.6413862297</v>
+      </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="18" t="n">
@@ -11005,6 +14268,22 @@
         <f aca="false">L200+((G200+C201)+J200)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>33828.5759894909</v>
       </c>
+      <c r="M201" s="19" t="n">
+        <f aca="false">(O200+C201)*(1+Předpoklady!$B$12)</f>
+        <v>1407475.50907941</v>
+      </c>
+      <c r="N201" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M201,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O201" s="19" t="n">
+        <f aca="false">M201*(1-N201/12)</f>
+        <v>1406982.89265123</v>
+      </c>
+      <c r="P201" s="19" t="n">
+        <f aca="false">P200+M201*N201/12</f>
+        <v>51655.2578144075</v>
+      </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="18" t="n">
@@ -11054,6 +14333,22 @@
         <f aca="false">L201+((G201+C202)+J201)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>34242.4420370753</v>
       </c>
+      <c r="M202" s="19" t="n">
+        <f aca="false">(O201+C202)*(1+Předpoklady!$B$12)</f>
+        <v>1418960.79506542</v>
+      </c>
+      <c r="N202" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M202,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O202" s="19" t="n">
+        <f aca="false">M202*(1-N202/12)</f>
+        <v>1418464.15878715</v>
+      </c>
+      <c r="P202" s="19" t="n">
+        <f aca="false">P201+M202*N202/12</f>
+        <v>52151.8940926804</v>
+      </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="18" t="n">
@@ -11103,6 +14398,22 @@
         <f aca="false">L202+((G202+C203)+J202)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>34659.5497460824</v>
       </c>
+      <c r="M203" s="19" t="n">
+        <f aca="false">(O202+C203)*(1+Předpoklady!$B$12)</f>
+        <v>1430506.97794931</v>
+      </c>
+      <c r="N203" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M203,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O203" s="19" t="n">
+        <f aca="false">M203*(1-N203/12)</f>
+        <v>1430006.30050702</v>
+      </c>
+      <c r="P203" s="19" t="n">
+        <f aca="false">P202+M203*N203/12</f>
+        <v>52652.5715349626</v>
+      </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="18" t="n">
@@ -11152,6 +14463,22 @@
         <f aca="false">L203+((G203+C204)+J203)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>35079.9166303397</v>
       </c>
+      <c r="M204" s="19" t="n">
+        <f aca="false">(O203+C204)*(1+Předpoklady!$B$12)</f>
+        <v>1442114.38061655</v>
+      </c>
+      <c r="N204" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M204,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O204" s="19" t="n">
+        <f aca="false">M204*(1-N204/12)</f>
+        <v>1441609.64058333</v>
+      </c>
+      <c r="P204" s="19" t="n">
+        <f aca="false">P203+M204*N204/12</f>
+        <v>53157.3115681784</v>
+      </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="18" t="n">
@@ -11201,6 +14528,22 @@
         <f aca="false">L204+((G204+C205)+J204)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>35503.5602982971</v>
       </c>
+      <c r="M205" s="19" t="n">
+        <f aca="false">(O204+C205)*(1+Předpoklady!$B$12)</f>
+        <v>1453783.32766462</v>
+      </c>
+      <c r="N205" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M205,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O205" s="19" t="n">
+        <f aca="false">M205*(1-N205/12)</f>
+        <v>1453274.50349994</v>
+      </c>
+      <c r="P205" s="19" t="n">
+        <f aca="false">P204+M205*N205/12</f>
+        <v>53666.135732861</v>
+      </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="18" t="n">
@@ -11250,6 +14593,22 @@
         <f aca="false">L205+((G205+C206)+J205)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>35930.4984535383</v>
       </c>
+      <c r="M206" s="19" t="n">
+        <f aca="false">(O205+C206)*(1+Předpoklady!$B$12)</f>
+        <v>1465514.14541209</v>
+      </c>
+      <c r="N206" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M206,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O206" s="19" t="n">
+        <f aca="false">M206*(1-N206/12)</f>
+        <v>1465001.21546119</v>
+      </c>
+      <c r="P206" s="19" t="n">
+        <f aca="false">P205+M206*N206/12</f>
+        <v>54179.0656837553</v>
+      </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="18" t="n">
@@ -11299,6 +14658,22 @@
         <f aca="false">L206+((G206+C207)+J206)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>36360.7488952946</v>
       </c>
+      <c r="M207" s="19" t="n">
+        <f aca="false">(O206+C207)*(1+Předpoklady!$B$12)</f>
+        <v>1477307.16190769</v>
+      </c>
+      <c r="N207" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M207,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O207" s="19" t="n">
+        <f aca="false">M207*(1-N207/12)</f>
+        <v>1476790.10440102</v>
+      </c>
+      <c r="P207" s="19" t="n">
+        <f aca="false">P206+M207*N207/12</f>
+        <v>54696.123190423</v>
+      </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="18" t="n">
@@ -11348,6 +14723,22 @@
         <f aca="false">L207+((G207+C208)+J207)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>36794.3295189618</v>
       </c>
+      <c r="M208" s="19" t="n">
+        <f aca="false">(O207+C208)*(1+Předpoklady!$B$12)</f>
+        <v>1489162.70693953</v>
+      </c>
+      <c r="N208" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M208,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O208" s="19" t="n">
+        <f aca="false">M208*(1-N208/12)</f>
+        <v>1488641.4999921</v>
+      </c>
+      <c r="P208" s="19" t="n">
+        <f aca="false">P207+M208*N208/12</f>
+        <v>55217.3301378518</v>
+      </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="18" t="n">
@@ -11397,6 +14788,22 @@
         <f aca="false">L208+((G208+C209)+J208)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>37231.25831662</v>
       </c>
+      <c r="M209" s="19" t="n">
+        <f aca="false">(O208+C209)*(1+Předpoklady!$B$12)</f>
+        <v>1501081.11204433</v>
+      </c>
+      <c r="N209" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M209,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O209" s="19" t="n">
+        <f aca="false">M209*(1-N209/12)</f>
+        <v>1500555.73365512</v>
+      </c>
+      <c r="P209" s="19" t="n">
+        <f aca="false">P208+M209*N209/12</f>
+        <v>55742.7085270673</v>
+      </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="18" t="n">
@@ -11446,6 +14853,22 @@
         <f aca="false">L209+((G209+C210)+J209)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>37673.363555017</v>
       </c>
+      <c r="M210" s="19" t="n">
+        <f aca="false">(O209+C210)*(1+Předpoklady!$B$12)</f>
+        <v>1513062.71051666</v>
+      </c>
+      <c r="N210" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M210,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O210" s="19" t="n">
+        <f aca="false">M210*(1-N210/12)</f>
+        <v>1512533.13856798</v>
+      </c>
+      <c r="P210" s="19" t="n">
+        <f aca="false">P209+M210*N210/12</f>
+        <v>56272.2804757481</v>
+      </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="18" t="n">
@@ -11495,6 +14918,22 @@
         <f aca="false">L210+((G210+C211)+J210)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>38118.8630236124</v>
       </c>
+      <c r="M211" s="19" t="n">
+        <f aca="false">(O210+C211)*(1+Předpoklady!$B$12)</f>
+        <v>1525107.83741826</v>
+      </c>
+      <c r="N211" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M211,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O211" s="19" t="n">
+        <f aca="false">M211*(1-N211/12)</f>
+        <v>1524574.04967516</v>
+      </c>
+      <c r="P211" s="19" t="n">
+        <f aca="false">P210+M211*N211/12</f>
+        <v>56806.0682188445</v>
+      </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="18" t="n">
@@ -11544,6 +14983,22 @@
         <f aca="false">L211+((G211+C212)+J211)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>38567.7750605218</v>
       </c>
+      <c r="M212" s="19" t="n">
+        <f aca="false">(O211+C212)*(1+Předpoklady!$B$12)</f>
+        <v>1537216.82958744</v>
+      </c>
+      <c r="N212" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M212,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O212" s="19" t="n">
+        <f aca="false">M212*(1-N212/12)</f>
+        <v>1536678.80369709</v>
+      </c>
+      <c r="P212" s="19" t="n">
+        <f aca="false">P211+M212*N212/12</f>
+        <v>57344.0941092001</v>
+      </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="18" t="n">
@@ -11593,6 +15048,22 @@
         <f aca="false">L212+((G212+C213)+J212)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>39020.1181029368</v>
       </c>
+      <c r="M213" s="19" t="n">
+        <f aca="false">(O212+C213)*(1+Předpoklady!$B$12)</f>
+        <v>1549390.02564848</v>
+      </c>
+      <c r="N213" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M213,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O213" s="19" t="n">
+        <f aca="false">M213*(1-N213/12)</f>
+        <v>1548847.73913951</v>
+      </c>
+      <c r="P213" s="19" t="n">
+        <f aca="false">P212+M213*N213/12</f>
+        <v>57886.3806181771</v>
+      </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="18" t="n">
@@ -11642,6 +15113,22 @@
         <f aca="false">L213+((G213+C214)+J213)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>39475.9106876599</v>
       </c>
+      <c r="M214" s="19" t="n">
+        <f aca="false">(O213+C214)*(1+Předpoklady!$B$12)</f>
+        <v>1561627.7660211</v>
+      </c>
+      <c r="N214" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M214,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O214" s="19" t="n">
+        <f aca="false">M214*(1-N214/12)</f>
+        <v>1561081.196303</v>
+      </c>
+      <c r="P214" s="19" t="n">
+        <f aca="false">P213+M214*N214/12</f>
+        <v>58432.9503362845</v>
+      </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="18" t="n">
@@ -11691,6 +15178,22 @@
         <f aca="false">L214+((G214+C215)+J214)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>39935.1714516435</v>
       </c>
+      <c r="M215" s="19" t="n">
+        <f aca="false">(O214+C215)*(1+Předpoklady!$B$12)</f>
+        <v>1573930.39292999</v>
+      </c>
+      <c r="N215" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M215,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O215" s="19" t="n">
+        <f aca="false">M215*(1-N215/12)</f>
+        <v>1573379.51729246</v>
+      </c>
+      <c r="P215" s="19" t="n">
+        <f aca="false">P214+M215*N215/12</f>
+        <v>58983.82597381</v>
+      </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="18" t="n">
@@ -11740,6 +15243,22 @@
         <f aca="false">L215+((G215+C216)+J215)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>40397.9191325299</v>
       </c>
+      <c r="M216" s="19" t="n">
+        <f aca="false">(O215+C216)*(1+Předpoklady!$B$12)</f>
+        <v>1586298.25041435</v>
+      </c>
+      <c r="N216" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M216,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O216" s="19" t="n">
+        <f aca="false">M216*(1-N216/12)</f>
+        <v>1585743.0460267</v>
+      </c>
+      <c r="P216" s="19" t="n">
+        <f aca="false">P215+M216*N216/12</f>
+        <v>59539.030361455</v>
+      </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="18" t="n">
@@ -11789,6 +15308,22 @@
         <f aca="false">L216+((G216+C217)+J216)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>40864.1725691962</v>
       </c>
+      <c r="M217" s="19" t="n">
+        <f aca="false">(O216+C217)*(1+Předpoklady!$B$12)</f>
+        <v>1598731.68433756</v>
+      </c>
+      <c r="N217" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M217,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O217" s="19" t="n">
+        <f aca="false">M217*(1-N217/12)</f>
+        <v>1598172.12824804</v>
+      </c>
+      <c r="P217" s="19" t="n">
+        <f aca="false">P216+M217*N217/12</f>
+        <v>60098.5864509732</v>
+      </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="18" t="n">
@@ -11838,6 +15373,22 @@
         <f aca="false">L217+((G217+C218)+J217)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>41333.9507023009</v>
       </c>
+      <c r="M218" s="19" t="n">
+        <f aca="false">(O217+C218)*(1+Předpoklady!$B$12)</f>
+        <v>1611231.0423968</v>
+      </c>
+      <c r="N218" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M218,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O218" s="19" t="n">
+        <f aca="false">M218*(1-N218/12)</f>
+        <v>1610667.11153196</v>
+      </c>
+      <c r="P218" s="19" t="n">
+        <f aca="false">P217+M218*N218/12</f>
+        <v>60662.517315812</v>
+      </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="18" t="n">
@@ -11887,6 +15438,22 @@
         <f aca="false">L218+((G218+C219)+J218)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>41807.2725748336</v>
       </c>
+      <c r="M219" s="19" t="n">
+        <f aca="false">(O218+C219)*(1+Předpoklady!$B$12)</f>
+        <v>1623796.67413282</v>
+      </c>
+      <c r="N219" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M219,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O219" s="19" t="n">
+        <f aca="false">M219*(1-N219/12)</f>
+        <v>1623228.34529688</v>
+      </c>
+      <c r="P219" s="19" t="n">
+        <f aca="false">P218+M219*N219/12</f>
+        <v>61230.8461517585</v>
+      </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="18" t="n">
@@ -11936,6 +15503,22 @@
         <f aca="false">L219+((G219+C220)+J219)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>42284.1573326682</v>
       </c>
+      <c r="M220" s="19" t="n">
+        <f aca="false">(O219+C220)*(1+Předpoklady!$B$12)</f>
+        <v>1636428.93093969</v>
+      </c>
+      <c r="N220" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M220,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O220" s="19" t="n">
+        <f aca="false">M220*(1-N220/12)</f>
+        <v>1635856.18081386</v>
+      </c>
+      <c r="P220" s="19" t="n">
+        <f aca="false">P219+M220*N220/12</f>
+        <v>61803.5962775874</v>
+      </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="18" t="n">
@@ -11985,6 +15568,22 @@
         <f aca="false">L220+((G220+C221)+J220)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>42764.6242251187</v>
       </c>
+      <c r="M221" s="19" t="n">
+        <f aca="false">(O220+C221)*(1+Předpoklady!$B$12)</f>
+        <v>1649128.16607462</v>
+      </c>
+      <c r="N221" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M221,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O221" s="19" t="n">
+        <f aca="false">M221*(1-N221/12)</f>
+        <v>1648550.9712165</v>
+      </c>
+      <c r="P221" s="19" t="n">
+        <f aca="false">P220+M221*N221/12</f>
+        <v>62380.7911357135</v>
+      </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="18" t="n">
@@ -12034,6 +15633,22 @@
         <f aca="false">L221+((G221+C222)+J221)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>43250.5027829595</v>
       </c>
+      <c r="M222" s="19" t="n">
+        <f aca="false">(O221+C222)*(1+Předpoklady!$B$12)</f>
+        <v>1661894.73466785</v>
+      </c>
+      <c r="N222" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M222,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O222" s="19" t="n">
+        <f aca="false">M222*(1-N222/12)</f>
+        <v>1661313.07151072</v>
+      </c>
+      <c r="P222" s="19" t="n">
+        <f aca="false">P221+M222*N222/12</f>
+        <v>62962.4542928473</v>
+      </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="18" t="n">
@@ -12083,6 +15698,22 @@
         <f aca="false">L222+((G222+C223)+J222)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>43740.0120665058</v>
       </c>
+      <c r="M223" s="19" t="n">
+        <f aca="false">(O222+C223)*(1+Předpoklady!$B$12)</f>
+        <v>1674728.99373259</v>
+      </c>
+      <c r="N223" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M223,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O223" s="19" t="n">
+        <f aca="false">M223*(1-N223/12)</f>
+        <v>1674142.83858478</v>
+      </c>
+      <c r="P223" s="19" t="n">
+        <f aca="false">P222+M223*N223/12</f>
+        <v>63548.6094406537</v>
+      </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="18" t="n">
@@ -12132,6 +15763,22 @@
         <f aca="false">L223+((G223+C224)+J223)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>44233.1716915951</v>
       </c>
+      <c r="M224" s="19" t="n">
+        <f aca="false">(O223+C224)*(1+Předpoklady!$B$12)</f>
+        <v>1687631.30217497</v>
+      </c>
+      <c r="N224" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M224,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O224" s="19" t="n">
+        <f aca="false">M224*(1-N224/12)</f>
+        <v>1687040.63121921</v>
+      </c>
+      <c r="P224" s="19" t="n">
+        <f aca="false">P223+M224*N224/12</f>
+        <v>64139.2803964149</v>
+      </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="18" t="n">
@@ -12181,6 +15828,22 @@
         <f aca="false">L224+((G224+C225)+J224)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>44730.001380044</v>
       </c>
+      <c r="M225" s="19" t="n">
+        <f aca="false">(O224+C225)*(1+Předpoklady!$B$12)</f>
+        <v>1700602.02080413</v>
+      </c>
+      <c r="N225" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M225,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O225" s="19" t="n">
+        <f aca="false">M225*(1-N225/12)</f>
+        <v>1700006.81009685</v>
+      </c>
+      <c r="P225" s="19" t="n">
+        <f aca="false">P224+M225*N225/12</f>
+        <v>64734.4911036964</v>
+      </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="18" t="n">
@@ -12230,6 +15893,22 @@
         <f aca="false">L225+((G225+C226)+J225)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>45230.5209602206</v>
       </c>
+      <c r="M226" s="19" t="n">
+        <f aca="false">(O225+C226)*(1+Předpoklady!$B$12)</f>
+        <v>1713641.51234227</v>
+      </c>
+      <c r="N226" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M226,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O226" s="19" t="n">
+        <f aca="false">M226*(1-N226/12)</f>
+        <v>1713041.73781295</v>
+      </c>
+      <c r="P226" s="19" t="n">
+        <f aca="false">P225+M226*N226/12</f>
+        <v>65334.2656330162</v>
+      </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="18" t="n">
@@ -12279,6 +15958,22 @@
         <f aca="false">L226+((G226+C227)+J226)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>45734.7503676204</v>
       </c>
+      <c r="M227" s="19" t="n">
+        <f aca="false">(O226+C227)*(1+Předpoklady!$B$12)</f>
+        <v>1726750.14143478</v>
+      </c>
+      <c r="N227" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M227,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O227" s="19" t="n">
+        <f aca="false">M227*(1-N227/12)</f>
+        <v>1726145.77888528</v>
+      </c>
+      <c r="P227" s="19" t="n">
+        <f aca="false">P226+M227*N227/12</f>
+        <v>65938.6281825183</v>
+      </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="18" t="n">
@@ -12328,6 +16023,22 @@
         <f aca="false">L227+((G227+C228)+J227)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>46242.7096454453</v>
       </c>
+      <c r="M228" s="19" t="n">
+        <f aca="false">(O227+C228)*(1+Předpoklady!$B$12)</f>
+        <v>1739928.27466051</v>
+      </c>
+      <c r="N228" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M228,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O228" s="19" t="n">
+        <f aca="false">M228*(1-N228/12)</f>
+        <v>1739319.29976437</v>
+      </c>
+      <c r="P228" s="19" t="n">
+        <f aca="false">P227+M228*N228/12</f>
+        <v>66547.6030786495</v>
+      </c>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="18" t="n">
@@ -12377,6 +16088,22 @@
         <f aca="false">L228+((G228+C229)+J228)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>46754.4189451848</v>
       </c>
+      <c r="M229" s="19" t="n">
+        <f aca="false">(O228+C229)*(1+Předpoklady!$B$12)</f>
+        <v>1753176.28054191</v>
+      </c>
+      <c r="N229" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M229,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O229" s="19" t="n">
+        <f aca="false">M229*(1-N229/12)</f>
+        <v>1752562.66884372</v>
+      </c>
+      <c r="P229" s="19" t="n">
+        <f aca="false">P228+M229*N229/12</f>
+        <v>67161.2147768392</v>
+      </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="18" t="n">
@@ -12426,6 +16153,22 @@
         <f aca="false">L229+((G229+C230)+J229)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>47269.898527202</v>
       </c>
+      <c r="M230" s="19" t="n">
+        <f aca="false">(O229+C230)*(1+Předpoklady!$B$12)</f>
+        <v>1766494.52955545</v>
+      </c>
+      <c r="N230" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M230,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O230" s="19" t="n">
+        <f aca="false">M230*(1-N230/12)</f>
+        <v>1765876.25647011</v>
+      </c>
+      <c r="P230" s="19" t="n">
+        <f aca="false">P229+M230*N230/12</f>
+        <v>67779.4878621836</v>
+      </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="18" t="n">
@@ -12475,6 +16218,22 @@
         <f aca="false">L230+((G230+C231)+J230)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>47789.1687613208</v>
       </c>
+      <c r="M231" s="19" t="n">
+        <f aca="false">(O230+C231)*(1+Předpoklady!$B$12)</f>
+        <v>1779883.39414191</v>
+      </c>
+      <c r="N231" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M231,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O231" s="19" t="n">
+        <f aca="false">M231*(1-N231/12)</f>
+        <v>1779260.43495396</v>
+      </c>
+      <c r="P231" s="19" t="n">
+        <f aca="false">P230+M231*N231/12</f>
+        <v>68402.4470501333</v>
+      </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="18" t="n">
@@ -12524,6 +16283,22 @@
         <f aca="false">L231+((G231+C232)+J231)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>48312.2501274183</v>
       </c>
+      <c r="M232" s="19" t="n">
+        <f aca="false">(O231+C232)*(1+Předpoklady!$B$12)</f>
+        <v>1793343.2487168</v>
+      </c>
+      <c r="N232" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M232,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O232" s="19" t="n">
+        <f aca="false">M232*(1-N232/12)</f>
+        <v>1792715.57857974</v>
+      </c>
+      <c r="P232" s="19" t="n">
+        <f aca="false">P231+M232*N232/12</f>
+        <v>69030.1171871841</v>
+      </c>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="18" t="n">
@@ -12573,6 +16348,22 @@
         <f aca="false">L232+((G232+C233)+J232)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>48839.1632160184</v>
       </c>
+      <c r="M233" s="19" t="n">
+        <f aca="false">(O232+C233)*(1+Předpoklady!$B$12)</f>
+        <v>1806874.46968085</v>
+      </c>
+      <c r="N233" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M233,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O233" s="19" t="n">
+        <f aca="false">M233*(1-N233/12)</f>
+        <v>1806242.06361646</v>
+      </c>
+      <c r="P233" s="19" t="n">
+        <f aca="false">P232+M233*N233/12</f>
+        <v>69662.5232515724</v>
+      </c>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="18" t="n">
@@ -12622,6 +16413,22 @@
         <f aca="false">L233+((G233+C234)+J233)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>49371.7389063522</v>
       </c>
+      <c r="M234" s="19" t="n">
+        <f aca="false">(O233+C234)*(1+Předpoklady!$B$12)</f>
+        <v>1820477.43543055</v>
+      </c>
+      <c r="N234" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M234,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O234" s="19" t="n">
+        <f aca="false">M234*(1-N234/12)</f>
+        <v>1819840.26832815</v>
+      </c>
+      <c r="P234" s="19" t="n">
+        <f aca="false">P233+M234*N234/12</f>
+        <v>70299.6903539731</v>
+      </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="18" t="n">
@@ -12671,6 +16478,22 @@
         <f aca="false">L234+((G234+C235)+J234)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>49908.1976144766</v>
       </c>
+      <c r="M235" s="19" t="n">
+        <f aca="false">(O234+C235)*(1+Předpoklady!$B$12)</f>
+        <v>1834152.52636868</v>
+      </c>
+      <c r="N235" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M235,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O235" s="19" t="n">
+        <f aca="false">M235*(1-N235/12)</f>
+        <v>1833510.57298445</v>
+      </c>
+      <c r="P235" s="19" t="n">
+        <f aca="false">P234+M235*N235/12</f>
+        <v>70941.6437382022</v>
+      </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="18" t="n">
@@ -12720,6 +16543,22 @@
         <f aca="false">L235+((G235+C236)+J235)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>50448.5603192955</v>
       </c>
+      <c r="M236" s="19" t="n">
+        <f aca="false">(O235+C236)*(1+Předpoklady!$B$12)</f>
+        <v>1847900.124915</v>
+      </c>
+      <c r="N236" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M236,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O236" s="19" t="n">
+        <f aca="false">M236*(1-N236/12)</f>
+        <v>1847253.35987128</v>
+      </c>
+      <c r="P236" s="19" t="n">
+        <f aca="false">P235+M236*N236/12</f>
+        <v>71588.4087819224</v>
+      </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="18" t="n">
@@ -12769,6 +16608,22 @@
         <f aca="false">L236+((G236+C237)+J236)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>50992.8481130563</v>
       </c>
+      <c r="M237" s="19" t="n">
+        <f aca="false">(O236+C237)*(1+Předpoklady!$B$12)</f>
+        <v>1861720.61551691</v>
+      </c>
+      <c r="N237" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M237,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O237" s="19" t="n">
+        <f aca="false">M237*(1-N237/12)</f>
+        <v>1861069.01330148</v>
+      </c>
+      <c r="P237" s="19" t="n">
+        <f aca="false">P236+M237*N237/12</f>
+        <v>72240.0109973533</v>
+      </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="18" t="n">
@@ -12818,6 +16673,22 @@
         <f aca="false">L237+((G237+C238)+J237)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>51541.0822019619</v>
       </c>
+      <c r="M238" s="19" t="n">
+        <f aca="false">(O237+C238)*(1+Předpoklady!$B$12)</f>
+        <v>1875614.38466023</v>
+      </c>
+      <c r="N238" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M238,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O238" s="19" t="n">
+        <f aca="false">M238*(1-N238/12)</f>
+        <v>1874957.9196256</v>
+      </c>
+      <c r="P238" s="19" t="n">
+        <f aca="false">P237+M238*N238/12</f>
+        <v>72896.4760319844</v>
+      </c>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="18" t="n">
@@ -12867,6 +16738,22 @@
         <f aca="false">L238+((G238+C239)+J238)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>52093.2839067869</v>
       </c>
+      <c r="M239" s="19" t="n">
+        <f aca="false">(O238+C239)*(1+Předpoklady!$B$12)</f>
+        <v>1889581.82087998</v>
+      </c>
+      <c r="N239" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M239,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O239" s="19" t="n">
+        <f aca="false">M239*(1-N239/12)</f>
+        <v>1888920.46724267</v>
+      </c>
+      <c r="P239" s="19" t="n">
+        <f aca="false">P238+M239*N239/12</f>
+        <v>73557.8296692924</v>
+      </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="18" t="n">
@@ -12916,6 +16803,22 @@
         <f aca="false">L239+((G239+C240)+J239)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>52649.4746634962</v>
       </c>
+      <c r="M240" s="19" t="n">
+        <f aca="false">(O239+C240)*(1+Předpoklady!$B$12)</f>
+        <v>1903623.31477126</v>
+      </c>
+      <c r="N240" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M240,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O240" s="19" t="n">
+        <f aca="false">M240*(1-N240/12)</f>
+        <v>1902957.04661109</v>
+      </c>
+      <c r="P240" s="19" t="n">
+        <f aca="false">P239+M240*N240/12</f>
+        <v>74224.0978294624</v>
+      </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="18" t="n">
@@ -12965,6 +16868,22 @@
         <f aca="false">L240+((G240+C241)+J240)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>53209.6760238674</v>
       </c>
+      <c r="M241" s="19" t="n">
+        <f aca="false">(O240+C241)*(1+Předpoklady!$B$12)</f>
+        <v>1917739.25900016</v>
+      </c>
+      <c r="N241" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M241,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O241" s="19" t="n">
+        <f aca="false">M241*(1-N241/12)</f>
+        <v>1917068.05025951</v>
+      </c>
+      <c r="P241" s="19" t="n">
+        <f aca="false">P240+M241*N241/12</f>
+        <v>74895.3065701124</v>
+      </c>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="18" t="n">
@@ -13014,6 +16933,22 @@
         <f aca="false">L241+((G241+C242)+J241)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>53773.9096561167</v>
       </c>
+      <c r="M242" s="19" t="n">
+        <f aca="false">(O241+C242)*(1+Předpoklady!$B$12)</f>
+        <v>1931930.04831478</v>
+      </c>
+      <c r="N242" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M242,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O242" s="19" t="n">
+        <f aca="false">M242*(1-N242/12)</f>
+        <v>1931253.87279787</v>
+      </c>
+      <c r="P242" s="19" t="n">
+        <f aca="false">P241+M242*N242/12</f>
+        <v>75571.4820870226</v>
+      </c>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="18" t="n">
@@ -13063,6 +16998,22 @@
         <f aca="false">L242+((G242+C243)+J242)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>54342.1973455277</v>
       </c>
+      <c r="M243" s="19" t="n">
+        <f aca="false">(O242+C243)*(1+Předpoklady!$B$12)</f>
+        <v>1946196.07955621</v>
+      </c>
+      <c r="N243" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M243,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O243" s="19" t="n">
+        <f aca="false">M243*(1-N243/12)</f>
+        <v>1945514.91092836</v>
+      </c>
+      <c r="P243" s="19" t="n">
+        <f aca="false">P242+M243*N243/12</f>
+        <v>76252.6507148673</v>
+      </c>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="18" t="n">
@@ -13112,6 +17063,22 @@
         <f aca="false">L243+((G243+C244)+J243)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>54914.5609950843</v>
       </c>
+      <c r="M244" s="19" t="n">
+        <f aca="false">(O243+C244)*(1+Předpoklady!$B$12)</f>
+        <v>1960537.75166967</v>
+      </c>
+      <c r="N244" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M244,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O244" s="19" t="n">
+        <f aca="false">M244*(1-N244/12)</f>
+        <v>1959851.56345658</v>
+      </c>
+      <c r="P244" s="19" t="n">
+        <f aca="false">P243+M244*N244/12</f>
+        <v>76938.8389279516</v>
+      </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="18" t="n">
@@ -13161,6 +17128,22 @@
         <f aca="false">L244+((G244+C245)+J244)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>55491.0226261061</v>
       </c>
+      <c r="M245" s="19" t="n">
+        <f aca="false">(O244+C245)*(1+Předpoklady!$B$12)</f>
+        <v>1974955.46571565</v>
+      </c>
+      <c r="N245" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M245,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O245" s="19" t="n">
+        <f aca="false">M245*(1-N245/12)</f>
+        <v>1974264.23130265</v>
+      </c>
+      <c r="P245" s="19" t="n">
+        <f aca="false">P244+M245*N245/12</f>
+        <v>77630.0733409521</v>
+      </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="18" t="n">
@@ -13210,6 +17193,22 @@
         <f aca="false">L245+((G245+C246)+J245)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>56073.4145563498</v>
       </c>
+      <c r="M246" s="19" t="n">
+        <f aca="false">(O245+C246)*(1+Předpoklady!$B$12)</f>
+        <v>1989449.62488114</v>
+      </c>
+      <c r="N246" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M246,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O246" s="19" t="n">
+        <f aca="false">M246*(1-N246/12)</f>
+        <v>1988753.31751243</v>
+      </c>
+      <c r="P246" s="19" t="n">
+        <f aca="false">P245+M246*N246/12</f>
+        <v>78326.3807096605</v>
+      </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="18" t="n">
@@ -13259,6 +17258,22 @@
         <f aca="false">L246+((G246+C247)+J246)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>56659.9586481703</v>
       </c>
+      <c r="M247" s="19" t="n">
+        <f aca="false">(O246+C247)*(1+Předpoklady!$B$12)</f>
+        <v>2004020.63449088</v>
+      </c>
+      <c r="N247" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M247,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O247" s="19" t="n">
+        <f aca="false">M247*(1-N247/12)</f>
+        <v>2003319.22726881</v>
+      </c>
+      <c r="P247" s="19" t="n">
+        <f aca="false">P246+M247*N247/12</f>
+        <v>79027.7879317323</v>
+      </c>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="18" t="n">
@@ -13308,6 +17323,22 @@
         <f aca="false">L247+((G247+C248)+J247)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>57250.677334583</v>
       </c>
+      <c r="M248" s="19" t="n">
+        <f aca="false">(O247+C248)*(1+Předpoklady!$B$12)</f>
+        <v>2018668.90201872</v>
+      </c>
+      <c r="N248" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M248,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O248" s="19" t="n">
+        <f aca="false">M248*(1-N248/12)</f>
+        <v>2017962.36790301</v>
+      </c>
+      <c r="P248" s="19" t="n">
+        <f aca="false">P247+M248*N248/12</f>
+        <v>79734.3220474389</v>
+      </c>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="18" t="n">
@@ -13357,6 +17388,22 @@
         <f aca="false">L248+((G248+C249)+J248)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>57845.5931698033</v>
       </c>
+      <c r="M249" s="19" t="n">
+        <f aca="false">(O248+C249)*(1+Předpoklady!$B$12)</f>
+        <v>2033394.837099</v>
+      </c>
+      <c r="N249" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M249,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O249" s="19" t="n">
+        <f aca="false">M249*(1-N249/12)</f>
+        <v>2032683.14890601</v>
+      </c>
+      <c r="P249" s="19" t="n">
+        <f aca="false">P248+M249*N249/12</f>
+        <v>80446.0102404235</v>
+      </c>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="18" t="n">
@@ -13406,6 +17453,22 @@
         <f aca="false">L249+((G249+C250)+J249)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>58444.7288299006</v>
       </c>
+      <c r="M250" s="19" t="n">
+        <f aca="false">(O249+C250)*(1+Předpoklady!$B$12)</f>
+        <v>2048198.85153801</v>
+      </c>
+      <c r="N250" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M250,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O250" s="19" t="n">
+        <f aca="false">M250*(1-N250/12)</f>
+        <v>2047481.98193997</v>
+      </c>
+      <c r="P250" s="19" t="n">
+        <f aca="false">P249+M250*N250/12</f>
+        <v>81162.8798384618</v>
+      </c>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="18" t="n">
@@ -13455,6 +17518,22 @@
         <f aca="false">L250+((G250+C251)+J250)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>59048.1071134571</v>
       </c>
+      <c r="M251" s="19" t="n">
+        <f aca="false">(O250+C251)*(1+Předpoklady!$B$12)</f>
+        <v>2063081.3593255</v>
+      </c>
+      <c r="N251" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M251,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O251" s="19" t="n">
+        <f aca="false">M251*(1-N251/12)</f>
+        <v>2062359.28084973</v>
+      </c>
+      <c r="P251" s="19" t="n">
+        <f aca="false">P250+M251*N251/12</f>
+        <v>81884.9583142258</v>
+      </c>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="18" t="n">
@@ -13504,6 +17583,22 @@
         <f aca="false">L251+((G251+C252)+J251)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>59655.7509422299</v>
       </c>
+      <c r="M252" s="19" t="n">
+        <f aca="false">(O251+C252)*(1+Předpoklady!$B$12)</f>
+        <v>2078042.77664627</v>
+      </c>
+      <c r="N252" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M252,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O252" s="19" t="n">
+        <f aca="false">M252*(1-N252/12)</f>
+        <v>2077315.46167445</v>
+      </c>
+      <c r="P252" s="19" t="n">
+        <f aca="false">P251+M252*N252/12</f>
+        <v>82612.273286052</v>
+      </c>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="18" t="n">
@@ -13553,6 +17648,22 @@
         <f aca="false">L252+((G252+C253)+J252)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>60267.6833618159</v>
       </c>
+      <c r="M253" s="19" t="n">
+        <f aca="false">(O252+C253)*(1+Předpoklady!$B$12)</f>
+        <v>2093083.52189181</v>
+      </c>
+      <c r="N253" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M253,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O253" s="19" t="n">
+        <f aca="false">M253*(1-N253/12)</f>
+        <v>2092350.94265915</v>
+      </c>
+      <c r="P253" s="19" t="n">
+        <f aca="false">P252+M253*N253/12</f>
+        <v>83344.8525187141</v>
+      </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="18" t="n">
@@ -13602,6 +17713,22 @@
         <f aca="false">L253+((G253+C254)+J253)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>60883.9275423212</v>
       </c>
+      <c r="M254" s="19" t="n">
+        <f aca="false">(O253+C254)*(1+Předpoklady!$B$12)</f>
+        <v>2108204.01567197</v>
+      </c>
+      <c r="N254" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M254,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O254" s="19" t="n">
+        <f aca="false">M254*(1-N254/12)</f>
+        <v>2107466.14426648</v>
+      </c>
+      <c r="P254" s="19" t="n">
+        <f aca="false">P253+M254*N254/12</f>
+        <v>84082.7239241993</v>
+      </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="18" t="n">
@@ -13651,6 +17778,22 @@
         <f aca="false">L254+((G254+C255)+J254)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>61504.506779034</v>
       </c>
+      <c r="M255" s="19" t="n">
+        <f aca="false">(O254+C255)*(1+Předpoklady!$B$12)</f>
+        <v>2123404.68082675</v>
+      </c>
+      <c r="N255" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M255,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O255" s="19" t="n">
+        <f aca="false">M255*(1-N255/12)</f>
+        <v>2122661.48918846</v>
+      </c>
+      <c r="P255" s="19" t="n">
+        <f aca="false">P254+M255*N255/12</f>
+        <v>84825.9155624886</v>
+      </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="18" t="n">
@@ -13700,6 +17843,22 @@
         <f aca="false">L255+((G255+C256)+J255)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>62129.4444931005</v>
       </c>
+      <c r="M256" s="19" t="n">
+        <f aca="false">(O255+C256)*(1+Předpoklady!$B$12)</f>
+        <v>2138685.94243813</v>
+      </c>
+      <c r="N256" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M256,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O256" s="19" t="n">
+        <f aca="false">M256*(1-N256/12)</f>
+        <v>2137937.40235827</v>
+      </c>
+      <c r="P256" s="19" t="n">
+        <f aca="false">P255+M256*N256/12</f>
+        <v>85574.455642342</v>
+      </c>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="18" t="n">
@@ -13749,6 +17908,22 @@
         <f aca="false">L256+((G256+C257)+J256)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>62758.764232205</v>
       </c>
+      <c r="M257" s="19" t="n">
+        <f aca="false">(O256+C257)*(1+Předpoklady!$B$12)</f>
+        <v>2154048.22784193</v>
+      </c>
+      <c r="N257" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M257,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O257" s="19" t="n">
+        <f aca="false">M257*(1-N257/12)</f>
+        <v>2153294.31096218</v>
+      </c>
+      <c r="P257" s="19" t="n">
+        <f aca="false">P256+M257*N257/12</f>
+        <v>86328.3725220867</v>
+      </c>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="18" t="n">
@@ -13798,6 +17973,22 @@
         <f aca="false">L257+((G257+C258)+J257)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>63394.2998487156</v>
       </c>
+      <c r="M258" s="19" t="n">
+        <f aca="false">(O257+C258)*(1+Předpoklady!$B$12)</f>
+        <v>2169491.96663979</v>
+      </c>
+      <c r="N258" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M258,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O258" s="19" t="n">
+        <f aca="false">M258*(1-N258/12)</f>
+        <v>2168732.64445146</v>
+      </c>
+      <c r="P258" s="19" t="n">
+        <f aca="false">P257+M258*N258/12</f>
+        <v>87087.6947104106</v>
+      </c>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="18" t="n">
@@ -13847,6 +18038,22 @@
         <f aca="false">L258+((G258+C259)+J258)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>64034.2747478894</v>
       </c>
+      <c r="M259" s="19" t="n">
+        <f aca="false">(O258+C259)*(1+Předpoklady!$B$12)</f>
+        <v>2185017.59071115</v>
+      </c>
+      <c r="N259" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M259,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O259" s="19" t="n">
+        <f aca="false">M259*(1-N259/12)</f>
+        <v>2184252.8345544</v>
+      </c>
+      <c r="P259" s="19" t="n">
+        <f aca="false">P258+M259*N259/12</f>
+        <v>87852.4508671595</v>
+      </c>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="18" t="n">
@@ -13896,6 +18103,22 @@
         <f aca="false">L259+((G259+C260)+J259)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>64678.7129139803</v>
       </c>
+      <c r="M260" s="19" t="n">
+        <f aca="false">(O259+C260)*(1+Předpoklady!$B$12)</f>
+        <v>2200625.53422538</v>
+      </c>
+      <c r="N260" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M260,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O260" s="19" t="n">
+        <f aca="false">M260*(1-N260/12)</f>
+        <v>2199855.3152884</v>
+      </c>
+      <c r="P260" s="19" t="n">
+        <f aca="false">P259+M260*N260/12</f>
+        <v>88622.6698041384</v>
+      </c>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="18" t="n">
@@ -13945,6 +18168,22 @@
         <f aca="false">L260+((G260+C261)+J260)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>65327.6384608225</v>
       </c>
+      <c r="M261" s="19" t="n">
+        <f aca="false">(O260+C261)*(1+Předpoklady!$B$12)</f>
+        <v>2216316.23365384</v>
+      </c>
+      <c r="N261" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M261,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O261" s="19" t="n">
+        <f aca="false">M261*(1-N261/12)</f>
+        <v>2215540.52297206</v>
+      </c>
+      <c r="P261" s="19" t="n">
+        <f aca="false">P260+M261*N261/12</f>
+        <v>89398.3804859172</v>
+      </c>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="18" t="n">
@@ -13994,6 +18233,22 @@
         <f aca="false">L261+((G261+C262)+J261)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>65981.0756325309</v>
       </c>
+      <c r="M262" s="19" t="n">
+        <f aca="false">(O261+C262)*(1+Předpoklady!$B$12)</f>
+        <v>2232090.12778219</v>
+      </c>
+      <c r="N262" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M262,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O262" s="19" t="n">
+        <f aca="false">M262*(1-N262/12)</f>
+        <v>2231308.89623746</v>
+      </c>
+      <c r="P262" s="19" t="n">
+        <f aca="false">P261+M262*N262/12</f>
+        <v>90179.612030641</v>
+      </c>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="18" t="n">
@@ -14043,6 +18298,22 @@
         <f aca="false">L262+((G262+C263)+J262)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>66639.0488042051</v>
       </c>
+      <c r="M263" s="19" t="n">
+        <f aca="false">(O262+C263)*(1+Předpoklady!$B$12)</f>
+        <v>2247947.65772255</v>
+      </c>
+      <c r="N263" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M263,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O263" s="19" t="n">
+        <f aca="false">M263*(1-N263/12)</f>
+        <v>2247160.87604235</v>
+      </c>
+      <c r="P263" s="19" t="n">
+        <f aca="false">P262+M263*N263/12</f>
+        <v>90966.3937108439</v>
+      </c>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="18" t="n">
@@ -14092,6 +18363,22 @@
         <f aca="false">L263+((G263+C264)+J263)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>67301.5824826363</v>
       </c>
+      <c r="M264" s="19" t="n">
+        <f aca="false">(O263+C264)*(1+Předpoklady!$B$12)</f>
+        <v>2263889.26692593</v>
+      </c>
+      <c r="N264" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M264,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O264" s="19" t="n">
+        <f aca="false">M264*(1-N264/12)</f>
+        <v>2263096.9056825</v>
+      </c>
+      <c r="P264" s="19" t="n">
+        <f aca="false">P263+M264*N264/12</f>
+        <v>91758.754954268</v>
+      </c>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="18" t="n">
@@ -14141,6 +18428,22 @@
         <f aca="false">L264+((G264+C265)+J264)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>67968.7013070198</v>
       </c>
+      <c r="M265" s="19" t="n">
+        <f aca="false">(O264+C265)*(1+Předpoklady!$B$12)</f>
+        <v>2279915.40119457</v>
+      </c>
+      <c r="N265" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M265,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O265" s="19" t="n">
+        <f aca="false">M265*(1-N265/12)</f>
+        <v>2279117.43080415</v>
+      </c>
+      <c r="P265" s="19" t="n">
+        <f aca="false">P264+M265*N265/12</f>
+        <v>92556.725344686</v>
+      </c>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="18" t="n">
@@ -14190,6 +18493,22 @@
         <f aca="false">L265+((G265+C266)+J265)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>68640.4300496696</v>
       </c>
+      <c r="M266" s="19" t="n">
+        <f aca="false">(O265+C266)*(1+Předpoklady!$B$12)</f>
+        <v>2296026.50869444</v>
+      </c>
+      <c r="N266" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M266,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O266" s="19" t="n">
+        <f aca="false">M266*(1-N266/12)</f>
+        <v>2295222.8994164</v>
+      </c>
+      <c r="P266" s="19" t="n">
+        <f aca="false">P265+M266*N266/12</f>
+        <v>93360.3346227291</v>
+      </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="18" t="n">
@@ -14239,6 +18558,22 @@
         <f aca="false">L266+((G266+C267)+J266)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>69316.793616738</v>
       </c>
+      <c r="M267" s="19" t="n">
+        <f aca="false">(O266+C267)*(1+Předpoklady!$B$12)</f>
+        <v>2312223.03996775</v>
+      </c>
+      <c r="N267" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M267,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O267" s="19" t="n">
+        <f aca="false">M267*(1-N267/12)</f>
+        <v>2311413.76190376</v>
+      </c>
+      <c r="P267" s="19" t="n">
+        <f aca="false">P266+M267*N267/12</f>
+        <v>94169.6126867178</v>
+      </c>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="18" t="n">
@@ -14288,6 +18623,22 @@
         <f aca="false">L267+((G267+C268)+J267)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>69997.8170489385</v>
       </c>
+      <c r="M268" s="19" t="n">
+        <f aca="false">(O267+C268)*(1+Předpoklady!$B$12)</f>
+        <v>2328505.44794556</v>
+      </c>
+      <c r="N268" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M268,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O268" s="19" t="n">
+        <f aca="false">M268*(1-N268/12)</f>
+        <v>2327690.47103878</v>
+      </c>
+      <c r="P268" s="19" t="n">
+        <f aca="false">P267+M268*N268/12</f>
+        <v>94984.5895934987</v>
+      </c>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="18" t="n">
@@ -14337,6 +18688,22 @@
         <f aca="false">L268+((G268+C269)+J268)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>70683.5255222728</v>
       </c>
+      <c r="M269" s="19" t="n">
+        <f aca="false">(O268+C269)*(1+Předpoklady!$B$12)</f>
+        <v>2344874.18796046</v>
+      </c>
+      <c r="N269" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M269,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O269" s="19" t="n">
+        <f aca="false">M269*(1-N269/12)</f>
+        <v>2344053.48199467</v>
+      </c>
+      <c r="P269" s="19" t="n">
+        <f aca="false">P268+M269*N269/12</f>
+        <v>95805.2955592849</v>
+      </c>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="18" t="n">
@@ -14386,6 +18753,22 @@
         <f aca="false">L269+((G269+C270)+J269)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>71375.7545262237</v>
       </c>
+      <c r="M270" s="19" t="n">
+        <f aca="false">(O269+C270)*(1+Předpoklady!$B$12)</f>
+        <v>2361329.71775928</v>
+      </c>
+      <c r="N270" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M270,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O270" s="19" t="n">
+        <f aca="false">M270*(1-N270/12)</f>
+        <v>2360503.25235806</v>
+      </c>
+      <c r="P270" s="19" t="n">
+        <f aca="false">P269+M270*N270/12</f>
+        <v>96631.7609605006</v>
+      </c>
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="18" t="n">
@@ -14435,6 +18818,22 @@
         <f aca="false">L270+((G270+C271)+J270)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>72072.7291120078</v>
       </c>
+      <c r="M271" s="19" t="n">
+        <f aca="false">(O270+C271)*(1+Předpoklady!$B$12)</f>
+        <v>2377872.49751589</v>
+      </c>
+      <c r="N271" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M271,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O271" s="19" t="n">
+        <f aca="false">M271*(1-N271/12)</f>
+        <v>2377040.24214176</v>
+      </c>
+      <c r="P271" s="19" t="n">
+        <f aca="false">P270+M271*N271/12</f>
+        <v>97464.0163346312</v>
+      </c>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="18" t="n">
@@ -14484,6 +18883,22 @@
         <f aca="false">L271+((G271+C272)+J271)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>72774.4749187313</v>
       </c>
+      <c r="M272" s="19" t="n">
+        <f aca="false">(O271+C272)*(1+Předpoklady!$B$12)</f>
+        <v>2394502.98984409</v>
+      </c>
+      <c r="N272" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M272,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O272" s="19" t="n">
+        <f aca="false">M272*(1-N272/12)</f>
+        <v>2393664.91379764</v>
+      </c>
+      <c r="P272" s="19" t="n">
+        <f aca="false">P271+M272*N272/12</f>
+        <v>98302.0923810766</v>
+      </c>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="18" t="n">
@@ -14533,6 +18948,22 @@
         <f aca="false">L272+((G272+C273)+J272)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>73481.0177240215</v>
       </c>
+      <c r="M273" s="19" t="n">
+        <f aca="false">(O272+C273)*(1+Předpoklady!$B$12)</f>
+        <v>2411221.65981053</v>
+      </c>
+      <c r="N273" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M273,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O273" s="19" t="n">
+        <f aca="false">M273*(1-N273/12)</f>
+        <v>2410377.7322296</v>
+      </c>
+      <c r="P273" s="19" t="n">
+        <f aca="false">P272+M273*N273/12</f>
+        <v>99146.0199620103</v>
+      </c>
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="18" t="n">
@@ -14582,6 +19013,22 @@
         <f aca="false">L273+((G273+C274)+J273)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>74192.3834447753</v>
       </c>
+      <c r="M274" s="19" t="n">
+        <f aca="false">(O273+C274)*(1+Předpoklady!$B$12)</f>
+        <v>2428028.97494774</v>
+      </c>
+      <c r="N274" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M274,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O274" s="19" t="n">
+        <f aca="false">M274*(1-N274/12)</f>
+        <v>2427179.16480651</v>
+      </c>
+      <c r="P274" s="19" t="n">
+        <f aca="false">P273+M274*N274/12</f>
+        <v>99995.830103242</v>
+      </c>
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="18" t="n">
@@ -14631,6 +19078,22 @@
         <f aca="false">L274+((G274+C275)+J274)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>74908.5981379118</v>
       </c>
+      <c r="M275" s="19" t="n">
+        <f aca="false">(O274+C275)*(1+Předpoklady!$B$12)</f>
+        <v>2444925.40526716</v>
+      </c>
+      <c r="N275" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M275,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O275" s="19" t="n">
+        <f aca="false">M275*(1-N275/12)</f>
+        <v>2444069.68137531</v>
+      </c>
+      <c r="P275" s="19" t="n">
+        <f aca="false">P274+M275*N275/12</f>
+        <v>100851.553995086</v>
+      </c>
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="18" t="n">
@@ -14680,6 +19143,22 @@
         <f aca="false">L275+((G275+C276)+J275)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>75629.6880011285</v>
       </c>
+      <c r="M276" s="19" t="n">
+        <f aca="false">(O275+C276)*(1+Předpoklady!$B$12)</f>
+        <v>2461911.42327231</v>
+      </c>
+      <c r="N276" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M276,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O276" s="19" t="n">
+        <f aca="false">M276*(1-N276/12)</f>
+        <v>2461049.75427416</v>
+      </c>
+      <c r="P276" s="19" t="n">
+        <f aca="false">P275+M276*N276/12</f>
+        <v>101713.222993231</v>
+      </c>
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="18" t="n">
@@ -14729,6 +19208,22 @@
         <f aca="false">L276+((G276+C277)+J276)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>76355.6793736621</v>
       </c>
+      <c r="M277" s="19" t="n">
+        <f aca="false">(O276+C277)*(1+Předpoklady!$B$12)</f>
+        <v>2478987.50397202</v>
+      </c>
+      <c r="N277" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M277,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O277" s="19" t="n">
+        <f aca="false">M277*(1-N277/12)</f>
+        <v>2478119.85834563</v>
+      </c>
+      <c r="P277" s="19" t="n">
+        <f aca="false">P276+M277*N277/12</f>
+        <v>102580.868619621</v>
+      </c>
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="18" t="n">
@@ -14778,6 +19273,22 @@
         <f aca="false">L277+((G277+C278)+J277)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>77086.5987370531</v>
       </c>
+      <c r="M278" s="19" t="n">
+        <f aca="false">(O277+C278)*(1+Předpoklady!$B$12)</f>
+        <v>2496154.12489368</v>
+      </c>
+      <c r="N278" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M278,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O278" s="19" t="n">
+        <f aca="false">M278*(1-N278/12)</f>
+        <v>2495280.47094997</v>
+      </c>
+      <c r="P278" s="19" t="n">
+        <f aca="false">P277+M278*N278/12</f>
+        <v>103454.522563334</v>
+      </c>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="18" t="n">
@@ -14827,6 +19338,22 @@
         <f aca="false">L278+((G278+C279)+J278)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>77822.4727159145</v>
       </c>
+      <c r="M279" s="19" t="n">
+        <f aca="false">(O278+C279)*(1+Předpoklady!$B$12)</f>
+        <v>2513411.76609662</v>
+      </c>
+      <c r="N279" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M279,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O279" s="19" t="n">
+        <f aca="false">M279*(1-N279/12)</f>
+        <v>2512532.07197849</v>
+      </c>
+      <c r="P279" s="19" t="n">
+        <f aca="false">P278+M279*N279/12</f>
+        <v>104334.216681468</v>
+      </c>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="18" t="n">
@@ -14876,6 +19403,22 @@
         <f aca="false">L279+((G279+C280)+J279)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>78563.3280787054</v>
       </c>
+      <c r="M280" s="19" t="n">
+        <f aca="false">(O279+C280)*(1+Předpoklady!$B$12)</f>
+        <v>2530760.91018552</v>
+      </c>
+      <c r="N280" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M280,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O280" s="19" t="n">
+        <f aca="false">M280*(1-N280/12)</f>
+        <v>2529875.14386696</v>
+      </c>
+      <c r="P280" s="19" t="n">
+        <f aca="false">P279+M280*N280/12</f>
+        <v>105219.983000033</v>
+      </c>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="18" t="n">
@@ -14925,6 +19468,22 @@
         <f aca="false">L280+((G280+C281)+J280)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>79309.1917385072</v>
       </c>
+      <c r="M281" s="19" t="n">
+        <f aca="false">(O280+C281)*(1+Předpoklady!$B$12)</f>
+        <v>2548202.04232391</v>
+      </c>
+      <c r="N281" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M281,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O281" s="19" t="n">
+        <f aca="false">M281*(1-N281/12)</f>
+        <v>2547310.1716091</v>
+      </c>
+      <c r="P281" s="19" t="n">
+        <f aca="false">P280+M281*N281/12</f>
+        <v>106111.853714846</v>
+      </c>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="18" t="n">
@@ -14974,6 +19533,22 @@
         <f aca="false">L281+((G281+C282)+J281)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>80061.9009312674</v>
       </c>
+      <c r="M282" s="19" t="n">
+        <f aca="false">(O281+C282)*(1+Předpoklady!$B$12)</f>
+        <v>2565735.65024774</v>
+      </c>
+      <c r="N282" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M282,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O282" s="19" t="n">
+        <f aca="false">M282*(1-N282/12)</f>
+        <v>2564837.64277016</v>
+      </c>
+      <c r="P282" s="19" t="n">
+        <f aca="false">P281+M282*N282/12</f>
+        <v>107009.861192433</v>
+      </c>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="18" t="n">
@@ -15023,6 +19598,22 @@
         <f aca="false">L282+((G282+C283)+J282)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>80819.6824641033</v>
       </c>
+      <c r="M283" s="19" t="n">
+        <f aca="false">(O282+C283)*(1+Předpoklady!$B$12)</f>
+        <v>2583362.22427902</v>
+      </c>
+      <c r="N283" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M283,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O283" s="19" t="n">
+        <f aca="false">M283*(1-N283/12)</f>
+        <v>2582458.04750052</v>
+      </c>
+      <c r="P283" s="19" t="n">
+        <f aca="false">P282+M283*N283/12</f>
+        <v>107914.03797093</v>
+      </c>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="18" t="n">
@@ -15072,6 +19663,22 @@
         <f aca="false">L283+((G283+C284)+J283)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>81582.5637415082</v>
       </c>
+      <c r="M284" s="19" t="n">
+        <f aca="false">(O283+C284)*(1+Předpoklady!$B$12)</f>
+        <v>2601082.25733951</v>
+      </c>
+      <c r="N284" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M284,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O284" s="19" t="n">
+        <f aca="false">M284*(1-N284/12)</f>
+        <v>2600171.87854944</v>
+      </c>
+      <c r="P284" s="19" t="n">
+        <f aca="false">P283+M284*N284/12</f>
+        <v>108824.416760999</v>
+      </c>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="18" t="n">
@@ -15121,6 +19728,22 @@
         <f aca="false">L284+((G284+C285)+J284)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>82350.5723160346</v>
       </c>
+      <c r="M285" s="19" t="n">
+        <f aca="false">(O284+C285)*(1+Předpoklady!$B$12)</f>
+        <v>2618896.24496455</v>
+      </c>
+      <c r="N285" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M285,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O285" s="19" t="n">
+        <f aca="false">M285*(1-N285/12)</f>
+        <v>2617979.63127882</v>
+      </c>
+      <c r="P285" s="19" t="n">
+        <f aca="false">P284+M285*N285/12</f>
+        <v>109741.030446737</v>
+      </c>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="18" t="n">
@@ -15170,6 +19793,22 @@
         <f aca="false">L285+((G285+C286)+J285)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>83123.7358890937</v>
       </c>
+      <c r="M286" s="19" t="n">
+        <f aca="false">(O285+C286)*(1+Předpoklady!$B$12)</f>
+        <v>2636804.68531688</v>
+      </c>
+      <c r="N286" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M286,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O286" s="19" t="n">
+        <f aca="false">M286*(1-N286/12)</f>
+        <v>2635881.80367702</v>
+      </c>
+      <c r="P286" s="19" t="n">
+        <f aca="false">P285+M286*N286/12</f>
+        <v>110663.912086598</v>
+      </c>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="18" t="n">
@@ -15219,6 +19858,22 @@
         <f aca="false">L286+((G286+C287)+J286)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>83902.0823117606</v>
       </c>
+      <c r="M287" s="19" t="n">
+        <f aca="false">(O286+C287)*(1+Předpoklady!$B$12)</f>
+        <v>2654808.07920058</v>
+      </c>
+      <c r="N287" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M287,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O287" s="19" t="n">
+        <f aca="false">M287*(1-N287/12)</f>
+        <v>2653878.89637286</v>
+      </c>
+      <c r="P287" s="19" t="n">
+        <f aca="false">P286+M287*N287/12</f>
+        <v>111593.094914318</v>
+      </c>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="18" t="n">
@@ -15268,6 +19923,22 @@
         <f aca="false">L287+((G287+C288)+J287)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>84685.6395855817</v>
       </c>
+      <c r="M288" s="19" t="n">
+        <f aca="false">(O287+C288)*(1+Předpoklady!$B$12)</f>
+        <v>2672906.93007506</v>
+      </c>
+      <c r="N288" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M288,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O288" s="19" t="n">
+        <f aca="false">M288*(1-N288/12)</f>
+        <v>2671971.41264954</v>
+      </c>
+      <c r="P288" s="19" t="n">
+        <f aca="false">P287+M288*N288/12</f>
+        <v>112528.612339844</v>
+      </c>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="18" t="n">
@@ -15317,6 +19988,22 @@
         <f aca="false">L288+((G288+C289)+J288)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>85474.4358633885</v>
       </c>
+      <c r="M289" s="19" t="n">
+        <f aca="false">(O288+C289)*(1+Předpoklady!$B$12)</f>
+        <v>2691101.7440692</v>
+      </c>
+      <c r="N289" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M289,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O289" s="19" t="n">
+        <f aca="false">M289*(1-N289/12)</f>
+        <v>2690159.85845877</v>
+      </c>
+      <c r="P289" s="19" t="n">
+        <f aca="false">P288+M289*N289/12</f>
+        <v>113470.497950268</v>
+      </c>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="18" t="n">
@@ -15366,6 +20053,22 @@
         <f aca="false">L289+((G289+C290)+J289)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>86268.4994501149</v>
       </c>
+      <c r="M290" s="19" t="n">
+        <f aca="false">(O289+C290)*(1+Předpoklady!$B$12)</f>
+        <v>2709393.02999541</v>
+      </c>
+      <c r="N290" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M290,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O290" s="19" t="n">
+        <f aca="false">M290*(1-N290/12)</f>
+        <v>2708444.74243491</v>
+      </c>
+      <c r="P290" s="19" t="n">
+        <f aca="false">P289+M290*N290/12</f>
+        <v>114418.785510767</v>
+      </c>
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="18" t="n">
@@ -15415,6 +20118,22 @@
         <f aca="false">L290+((G290+C291)+J290)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>87067.8588036185</v>
       </c>
+      <c r="M291" s="19" t="n">
+        <f aca="false">(O290+C291)*(1+Předpoklady!$B$12)</f>
+        <v>2727781.29936394</v>
+      </c>
+      <c r="N291" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M291,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O291" s="19" t="n">
+        <f aca="false">M291*(1-N291/12)</f>
+        <v>2726826.57590917</v>
+      </c>
+      <c r="P291" s="19" t="n">
+        <f aca="false">P290+M291*N291/12</f>
+        <v>115373.508965544</v>
+      </c>
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="18" t="n">
@@ -15464,6 +20183,22 @@
         <f aca="false">L291+((G291+C292)+J291)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>87872.542535507</v>
       </c>
+      <c r="M292" s="19" t="n">
+        <f aca="false">(O291+C292)*(1+Předpoklady!$B$12)</f>
+        <v>2746267.06639715</v>
+      </c>
+      <c r="N292" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M292,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O292" s="19" t="n">
+        <f aca="false">M292*(1-N292/12)</f>
+        <v>2745305.87292391</v>
+      </c>
+      <c r="P292" s="19" t="n">
+        <f aca="false">P291+M292*N292/12</f>
+        <v>116334.702438783</v>
+      </c>
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="18" t="n">
@@ -15513,6 +20248,22 @@
         <f aca="false">L292+((G292+C293)+J292)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>88682.5794119692</v>
       </c>
+      <c r="M293" s="19" t="n">
+        <f aca="false">(O292+C293)*(1+Předpoklady!$B$12)</f>
+        <v>2764850.84804387</v>
+      </c>
+      <c r="N293" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M293,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O293" s="19" t="n">
+        <f aca="false">M293*(1-N293/12)</f>
+        <v>2763883.15024705</v>
+      </c>
+      <c r="P293" s="19" t="n">
+        <f aca="false">P292+M293*N293/12</f>
+        <v>117302.400235598</v>
+      </c>
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="18" t="n">
@@ -15562,6 +20313,22 @@
         <f aca="false">L293+((G293+C294)+J293)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>89499.8085320716</v>
       </c>
+      <c r="M294" s="19" t="n">
+        <f aca="false">(O293+C294)*(1+Předpoklady!$B$12)</f>
+        <v>2783533.1639939</v>
+      </c>
+      <c r="N294" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M294,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O294" s="19" t="n">
+        <f aca="false">M294*(1-N294/12)</f>
+        <v>2782558.9273865</v>
+      </c>
+      <c r="P294" s="19" t="n">
+        <f aca="false">P293+M294*N294/12</f>
+        <v>118276.636842996</v>
+      </c>
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="18" t="n">
@@ -15611,6 +20378,22 @@
         <f aca="false">L294+((G294+C295)+J294)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>90322.4585761161</v>
       </c>
+      <c r="M295" s="19" t="n">
+        <f aca="false">(O294+C295)*(1+Předpoklady!$B$12)</f>
+        <v>2802314.53669252</v>
+      </c>
+      <c r="N295" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M295,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O295" s="19" t="n">
+        <f aca="false">M295*(1-N295/12)</f>
+        <v>2801333.72660467</v>
+      </c>
+      <c r="P295" s="19" t="n">
+        <f aca="false">P294+M295*N295/12</f>
+        <v>119257.446930839</v>
+      </c>
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="18" t="n">
@@ -15660,6 +20443,22 @@
         <f aca="false">L295+((G295+C296)+J295)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>91150.5588319012</v>
       </c>
+      <c r="M296" s="19" t="n">
+        <f aca="false">(O295+C296)*(1+Předpoklady!$B$12)</f>
+        <v>2821195.49135509</v>
+      </c>
+      <c r="N296" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M296,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O296" s="19" t="n">
+        <f aca="false">M296*(1-N296/12)</f>
+        <v>2820208.07293311</v>
+      </c>
+      <c r="P296" s="19" t="n">
+        <f aca="false">P295+M296*N296/12</f>
+        <v>120244.865352813</v>
+      </c>
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="18" t="n">
@@ -15709,6 +20508,22 @@
         <f aca="false">L296+((G296+C297)+J296)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>91984.1387454595</v>
       </c>
+      <c r="M297" s="19" t="n">
+        <f aca="false">(O296+C297)*(1+Předpoklady!$B$12)</f>
+        <v>2840176.55598176</v>
+      </c>
+      <c r="N297" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M297,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O297" s="19" t="n">
+        <f aca="false">M297*(1-N297/12)</f>
+        <v>2839182.49418717</v>
+      </c>
+      <c r="P297" s="19" t="n">
+        <f aca="false">P296+M297*N297/12</f>
+        <v>121238.927147407</v>
+      </c>
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="18" t="n">
@@ -15758,6 +20573,22 @@
         <f aca="false">L297+((G297+C298)+J297)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>92823.2279219125</v>
       </c>
+      <c r="M298" s="19" t="n">
+        <f aca="false">(O297+C298)*(1+Předpoklady!$B$12)</f>
+        <v>2859258.26137223</v>
+      </c>
+      <c r="N298" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M298,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O298" s="19" t="n">
+        <f aca="false">M298*(1-N298/12)</f>
+        <v>2858257.52098075</v>
+      </c>
+      <c r="P298" s="19" t="n">
+        <f aca="false">P297+M298*N298/12</f>
+        <v>122239.667538887</v>
+      </c>
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="18" t="n">
@@ -15807,6 +20638,22 @@
         <f aca="false">L298+((G298+C299)+J298)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>93667.8561263305</v>
       </c>
+      <c r="M299" s="19" t="n">
+        <f aca="false">(O298+C299)*(1+Předpoklady!$B$12)</f>
+        <v>2878441.14114057</v>
+      </c>
+      <c r="N299" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M299,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O299" s="19" t="n">
+        <f aca="false">M299*(1-N299/12)</f>
+        <v>2877433.68674117</v>
+      </c>
+      <c r="P299" s="19" t="n">
+        <f aca="false">P298+M299*N299/12</f>
+        <v>123247.121938286</v>
+      </c>
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="18" t="n">
@@ -15856,6 +20703,22 @@
         <f aca="false">L299+((G299+C300)+J299)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>94518.0532845961</v>
       </c>
+      <c r="M300" s="19" t="n">
+        <f aca="false">(O299+C300)*(1+Předpoklady!$B$12)</f>
+        <v>2897725.73173017</v>
+      </c>
+      <c r="N300" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M300,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O300" s="19" t="n">
+        <f aca="false">M300*(1-N300/12)</f>
+        <v>2896711.52772406</v>
+      </c>
+      <c r="P300" s="19" t="n">
+        <f aca="false">P299+M300*N300/12</f>
+        <v>124261.325944392</v>
+      </c>
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="18" t="n">
@@ -15905,6 +20768,22 @@
         <f aca="false">L300+((G300+C301)+J300)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>95373.8494842738</v>
       </c>
+      <c r="M301" s="19" t="n">
+        <f aca="false">(O300+C301)*(1+Předpoklady!$B$12)</f>
+        <v>2917112.57242874</v>
+      </c>
+      <c r="N301" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M301,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O301" s="19" t="n">
+        <f aca="false">M301*(1-N301/12)</f>
+        <v>2916091.58302839</v>
+      </c>
+      <c r="P301" s="19" t="n">
+        <f aca="false">P300+M301*N301/12</f>
+        <v>125282.315344742</v>
+      </c>
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="18" t="n">
@@ -15954,6 +20833,22 @@
         <f aca="false">L301+((G301+C302)+J301)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>96235.2749754829</v>
       </c>
+      <c r="M302" s="19" t="n">
+        <f aca="false">(O301+C302)*(1+Předpoklady!$B$12)</f>
+        <v>2936602.20538337</v>
+      </c>
+      <c r="N302" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M302,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O302" s="19" t="n">
+        <f aca="false">M302*(1-N302/12)</f>
+        <v>2935574.39461149</v>
+      </c>
+      <c r="P302" s="19" t="n">
+        <f aca="false">P301+M302*N302/12</f>
+        <v>126310.126116626</v>
+      </c>
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="18" t="n">
@@ -16003,6 +20898,22 @@
         <f aca="false">L302+((G302+C303)+J302)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>97102.3601717761</v>
       </c>
+      <c r="M303" s="19" t="n">
+        <f aca="false">(O302+C303)*(1+Předpoklady!$B$12)</f>
+        <v>2956195.17561571</v>
+      </c>
+      <c r="N303" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M303,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O303" s="19" t="n">
+        <f aca="false">M303*(1-N303/12)</f>
+        <v>2955160.50730425</v>
+      </c>
+      <c r="P303" s="19" t="n">
+        <f aca="false">P302+M303*N303/12</f>
+        <v>127344.794428091</v>
+      </c>
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="18" t="n">
@@ -16052,6 +20963,22 @@
         <f aca="false">L303+((G303+C304)+J303)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>97975.1356510222</v>
       </c>
+      <c r="M304" s="19" t="n">
+        <f aca="false">(O303+C304)*(1+Předpoklady!$B$12)</f>
+        <v>2975892.03103721</v>
+      </c>
+      <c r="N304" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M304,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O304" s="19" t="n">
+        <f aca="false">M304*(1-N304/12)</f>
+        <v>2974850.46882635</v>
+      </c>
+      <c r="P304" s="19" t="n">
+        <f aca="false">P303+M304*N304/12</f>
+        <v>128386.356638954</v>
+      </c>
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="18" t="n">
@@ -16101,6 +21028,22 @@
         <f aca="false">L304+((G304+C305)+J304)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>98853.6321562942</v>
       </c>
+      <c r="M305" s="19" t="n">
+        <f aca="false">(O304+C305)*(1+Předpoklady!$B$12)</f>
+        <v>2995693.32246443</v>
+      </c>
+      <c r="N305" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M305,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O305" s="19" t="n">
+        <f aca="false">M305*(1-N305/12)</f>
+        <v>2994644.82980157</v>
+      </c>
+      <c r="P305" s="19" t="n">
+        <f aca="false">P304+M305*N305/12</f>
+        <v>129434.849301817</v>
+      </c>
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="18" t="n">
@@ -16150,6 +21093,22 @@
         <f aca="false">L305+((G305+C306)+J305)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>99739.6907742235</v>
       </c>
+      <c r="M306" s="19" t="n">
+        <f aca="false">(O305+C306)*(1+Předpoklady!$B$12)</f>
+        <v>3015599.60363446</v>
+      </c>
+      <c r="N306" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M306,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O306" s="19" t="n">
+        <f aca="false">M306*(1-N306/12)</f>
+        <v>3014544.14377319</v>
+      </c>
+      <c r="P306" s="19" t="n">
+        <f aca="false">P305+M306*N306/12</f>
+        <v>130490.309163089</v>
+      </c>
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="18" t="n">
@@ -16199,6 +21158,22 @@
         <f aca="false">L306+((G306+C307)+J306)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>100631.542183415</v>
       </c>
+      <c r="M307" s="19" t="n">
+        <f aca="false">(O306+C307)*(1+Předpoklady!$B$12)</f>
+        <v>3035611.43122038</v>
+      </c>
+      <c r="N307" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M307,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O307" s="19" t="n">
+        <f aca="false">M307*(1-N307/12)</f>
+        <v>3034548.96721946</v>
+      </c>
+      <c r="P307" s="19" t="n">
+        <f aca="false">P306+M307*N307/12</f>
+        <v>131552.773164016</v>
+      </c>
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="18" t="n">
@@ -16248,6 +21223,22 @@
         <f aca="false">L307+((G307+C308)+J307)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>101529.217680767</v>
       </c>
+      <c r="M308" s="19" t="n">
+        <f aca="false">(O307+C308)*(1+Předpoklady!$B$12)</f>
+        <v>3055729.36484687</v>
+      </c>
+      <c r="N308" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M308,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O308" s="19" t="n">
+        <f aca="false">M308*(1-N308/12)</f>
+        <v>3054659.85956917</v>
+      </c>
+      <c r="P308" s="19" t="n">
+        <f aca="false">P307+M308*N308/12</f>
+        <v>132622.278441713</v>
+      </c>
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="18" t="n">
@@ -16297,6 +21288,22 @@
         <f aca="false">L308+((G308+C309)+J308)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>102432.748732266</v>
       </c>
+      <c r="M309" s="19" t="n">
+        <f aca="false">(O308+C309)*(1+Předpoklady!$B$12)</f>
+        <v>3075953.96710579</v>
+      </c>
+      <c r="N309" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M309,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O309" s="19" t="n">
+        <f aca="false">M309*(1-N309/12)</f>
+        <v>3074877.38321731</v>
+      </c>
+      <c r="P309" s="19" t="n">
+        <f aca="false">P308+M309*N309/12</f>
+        <v>133698.8623302</v>
+      </c>
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="18" t="n">
@@ -16346,6 +21353,22 @@
         <f aca="false">L309+((G309+C310)+J309)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>103342.1669739</v>
       </c>
+      <c r="M310" s="19" t="n">
+        <f aca="false">(O309+C310)*(1+Předpoklady!$B$12)</f>
+        <v>3096285.80357201</v>
+      </c>
+      <c r="N310" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M310,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O310" s="19" t="n">
+        <f aca="false">M310*(1-N310/12)</f>
+        <v>3095202.10354076</v>
+      </c>
+      <c r="P310" s="19" t="n">
+        <f aca="false">P309+M310*N310/12</f>
+        <v>134782.56236145</v>
+      </c>
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="18" t="n">
@@ -16395,6 +21418,22 @@
         <f aca="false">L310+((G310+C311)+J310)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>104257.50421258</v>
       </c>
+      <c r="M311" s="19" t="n">
+        <f aca="false">(O310+C311)*(1+Předpoklady!$B$12)</f>
+        <v>3116725.44281913</v>
+      </c>
+      <c r="N311" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M311,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O311" s="19" t="n">
+        <f aca="false">M311*(1-N311/12)</f>
+        <v>3115634.58891415</v>
+      </c>
+      <c r="P311" s="19" t="n">
+        <f aca="false">P310+M311*N311/12</f>
+        <v>135873.416266436</v>
+      </c>
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="18" t="n">
@@ -16444,6 +21483,22 @@
         <f aca="false">L311+((G311+C312)+J311)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>105178.792427059</v>
       </c>
+      <c r="M312" s="19" t="n">
+        <f aca="false">(O311+C312)*(1+Předpoklady!$B$12)</f>
+        <v>3137273.45643545</v>
+      </c>
+      <c r="N312" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M312,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O312" s="19" t="n">
+        <f aca="false">M312*(1-N312/12)</f>
+        <v>3136175.41072569</v>
+      </c>
+      <c r="P312" s="19" t="n">
+        <f aca="false">P311+M312*N312/12</f>
+        <v>136971.461976189</v>
+      </c>
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="18" t="n">
@@ -16493,6 +21548,22 @@
         <f aca="false">L312+((G312+C313)+J312)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>106106.063768864</v>
       </c>
+      <c r="M313" s="19" t="n">
+        <f aca="false">(O312+C313)*(1+Předpoklady!$B$12)</f>
+        <v>3157930.41903989</v>
+      </c>
+      <c r="N313" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M313,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O313" s="19" t="n">
+        <f aca="false">M313*(1-N313/12)</f>
+        <v>3156825.14339323</v>
+      </c>
+      <c r="P313" s="19" t="n">
+        <f aca="false">P312+M313*N313/12</f>
+        <v>138076.737622853</v>
+      </c>
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="18" t="n">
@@ -16542,6 +21613,22 @@
         <f aca="false">L313+((G313+C314)+J313)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>107039.350563227</v>
       </c>
+      <c r="M314" s="19" t="n">
+        <f aca="false">(O313+C314)*(1+Předpoklady!$B$12)</f>
+        <v>3178696.90829814</v>
+      </c>
+      <c r="N314" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M314,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O314" s="19" t="n">
+        <f aca="false">M314*(1-N314/12)</f>
+        <v>3177584.36438024</v>
+      </c>
+      <c r="P314" s="19" t="n">
+        <f aca="false">P313+M314*N314/12</f>
+        <v>139189.281540757</v>
+      </c>
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="18" t="n">
@@ -16591,6 +21678,22 @@
         <f aca="false">L314+((G314+C315)+J314)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>107978.685310026</v>
       </c>
+      <c r="M315" s="19" t="n">
+        <f aca="false">(O314+C315)*(1+Předpoklady!$B$12)</f>
+        <v>3199573.50493874</v>
+      </c>
+      <c r="N315" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M315,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O315" s="19" t="n">
+        <f aca="false">M315*(1-N315/12)</f>
+        <v>3198453.65421201</v>
+      </c>
+      <c r="P315" s="19" t="n">
+        <f aca="false">P314+M315*N315/12</f>
+        <v>140309.132267486</v>
+      </c>
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="18" t="n">
@@ -16640,6 +21743,22 @@
         <f aca="false">L315+((G315+C316)+J315)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>108924.100684725</v>
       </c>
+      <c r="M316" s="19" t="n">
+        <f aca="false">(O315+C316)*(1+Předpoklady!$B$12)</f>
+        <v>3220560.79276935</v>
+      </c>
+      <c r="N316" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M316,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O316" s="19" t="n">
+        <f aca="false">M316*(1-N316/12)</f>
+        <v>3219433.59649188</v>
+      </c>
+      <c r="P316" s="19" t="n">
+        <f aca="false">P315+M316*N316/12</f>
+        <v>141436.328544955</v>
+      </c>
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="18" t="n">
@@ -16689,6 +21808,22 @@
         <f aca="false">L316+((G316+C317)+J316)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>109875.629539327</v>
       </c>
+      <c r="M317" s="19" t="n">
+        <f aca="false">(O316+C317)*(1+Předpoklady!$B$12)</f>
+        <v>3241659.35869309</v>
+      </c>
+      <c r="N317" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M317,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O317" s="19" t="n">
+        <f aca="false">M317*(1-N317/12)</f>
+        <v>3240524.77791755</v>
+      </c>
+      <c r="P317" s="19" t="n">
+        <f aca="false">P316+M317*N317/12</f>
+        <v>142570.909320498</v>
+      </c>
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="18" t="n">
@@ -16738,6 +21873,22 @@
         <f aca="false">L317+((G317+C318)+J317)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>110835.115080786</v>
       </c>
+      <c r="M318" s="19" t="n">
+        <f aca="false">(O317+C318)*(1+Předpoklady!$B$12)</f>
+        <v>3262869.79272494</v>
+      </c>
+      <c r="N318" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M318,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O318" s="19" t="n">
+        <f aca="false">M318*(1-N318/12)</f>
+        <v>3261727.78829748</v>
+      </c>
+      <c r="P318" s="19" t="n">
+        <f aca="false">P317+M318*N318/12</f>
+        <v>143712.913747951</v>
+      </c>
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="18" t="n">
@@ -16787,6 +21938,22 @@
         <f aca="false">L318+((G318+C319)+J318)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>111800.790119486</v>
       </c>
+      <c r="M319" s="19" t="n">
+        <f aca="false">(O318+C319)*(1+Předpoklady!$B$12)</f>
+        <v>3284192.6880082</v>
+      </c>
+      <c r="N319" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M319,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O319" s="19" t="n">
+        <f aca="false">M319*(1-N319/12)</f>
+        <v>3283043.2205674</v>
+      </c>
+      <c r="P319" s="19" t="n">
+        <f aca="false">P318+M319*N319/12</f>
+        <v>144862.381188754</v>
+      </c>
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="18" t="n">
@@ -16836,6 +22003,22 @@
         <f aca="false">L319+((G319+C320)+J319)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>112772.688095621</v>
       </c>
+      <c r="M320" s="19" t="n">
+        <f aca="false">(O319+C320)*(1+Předpoklady!$B$12)</f>
+        <v>3305628.64083118</v>
+      </c>
+      <c r="N320" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M320,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O320" s="19" t="n">
+        <f aca="false">M320*(1-N320/12)</f>
+        <v>3304471.67080688</v>
+      </c>
+      <c r="P320" s="19" t="n">
+        <f aca="false">P319+M320*N320/12</f>
+        <v>146019.351213045</v>
+      </c>
     </row>
     <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="18" t="n">
@@ -16885,6 +22068,22 @@
         <f aca="false">L320+((G320+C321)+J320)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>113750.842630053</v>
       </c>
+      <c r="M321" s="19" t="n">
+        <f aca="false">(O320+C321)*(1+Předpoklady!$B$12)</f>
+        <v>3327178.25064374</v>
+      </c>
+      <c r="N321" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M321,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O321" s="19" t="n">
+        <f aca="false">M321*(1-N321/12)</f>
+        <v>3326013.73825601</v>
+      </c>
+      <c r="P321" s="19" t="n">
+        <f aca="false">P320+M321*N321/12</f>
+        <v>147183.86360077</v>
+      </c>
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="18" t="n">
@@ -16934,6 +22133,22 @@
         <f aca="false">L321+((G321+C322)+J321)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>114735.287525288</v>
       </c>
+      <c r="M322" s="19" t="n">
+        <f aca="false">(O321+C322)*(1+Předpoklady!$B$12)</f>
+        <v>3348842.12007417</v>
+      </c>
+      <c r="N322" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M322,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O322" s="19" t="n">
+        <f aca="false">M322*(1-N322/12)</f>
+        <v>3347670.02533214</v>
+      </c>
+      <c r="P322" s="19" t="n">
+        <f aca="false">P321+M322*N322/12</f>
+        <v>148355.958342796</v>
+      </c>
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="18" t="n">
@@ -16983,6 +22198,22 @@
         <f aca="false">L322+((G322+C323)+J322)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>115726.05676646</v>
       </c>
+      <c r="M323" s="19" t="n">
+        <f aca="false">(O322+C323)*(1+Předpoklady!$B$12)</f>
+        <v>3370620.85494598</v>
+      </c>
+      <c r="N323" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M323,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O323" s="19" t="n">
+        <f aca="false">M323*(1-N323/12)</f>
+        <v>3369441.13764675</v>
+      </c>
+      <c r="P323" s="19" t="n">
+        <f aca="false">P322+M323*N323/12</f>
+        <v>149535.675642028</v>
+      </c>
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="18" t="n">
@@ -17032,6 +22263,22 @@
         <f aca="false">L323+((G323+C324)+J323)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>116723.184522314</v>
       </c>
+      <c r="M324" s="19" t="n">
+        <f aca="false">(O323+C324)*(1+Předpoklady!$B$12)</f>
+        <v>3392515.06429486</v>
+      </c>
+      <c r="N324" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M324,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O324" s="19" t="n">
+        <f aca="false">M324*(1-N324/12)</f>
+        <v>3391327.68402235</v>
+      </c>
+      <c r="P324" s="19" t="n">
+        <f aca="false">P323+M324*N324/12</f>
+        <v>150723.055914531</v>
+      </c>
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="18" t="n">
@@ -17081,6 +22328,22 @@
         <f aca="false">L324+((G324+C325)+J324)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>117726.7051462</v>
       </c>
+      <c r="M325" s="19" t="n">
+        <f aca="false">(O324+C325)*(1+Předpoklady!$B$12)</f>
+        <v>3414525.3603857</v>
+      </c>
+      <c r="N325" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M325,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O325" s="19" t="n">
+        <f aca="false">M325*(1-N325/12)</f>
+        <v>3413330.27650956</v>
+      </c>
+      <c r="P325" s="19" t="n">
+        <f aca="false">P324+M325*N325/12</f>
+        <v>151918.139790666</v>
+      </c>
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="18" t="n">
@@ -17130,6 +22393,22 @@
         <f aca="false">L325+((G325+C326)+J325)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>118736.653177068</v>
       </c>
+      <c r="M326" s="19" t="n">
+        <f aca="false">(O325+C326)*(1+Předpoklady!$B$12)</f>
+        <v>3436652.35872973</v>
+      </c>
+      <c r="N326" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M326,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O326" s="19" t="n">
+        <f aca="false">M326*(1-N326/12)</f>
+        <v>3435449.53040418</v>
+      </c>
+      <c r="P326" s="19" t="n">
+        <f aca="false">P325+M326*N326/12</f>
+        <v>153120.968116221</v>
+      </c>
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="18" t="n">
@@ -17179,6 +22458,22 @@
         <f aca="false">L326+((G326+C327)+J326)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>119753.063340476</v>
       </c>
+      <c r="M327" s="19" t="n">
+        <f aca="false">(O326+C327)*(1+Předpoklady!$B$12)</f>
+        <v>3458896.67810172</v>
+      </c>
+      <c r="N327" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M327,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O327" s="19" t="n">
+        <f aca="false">M327*(1-N327/12)</f>
+        <v>3457686.06426439</v>
+      </c>
+      <c r="P327" s="19" t="n">
+        <f aca="false">P326+M327*N327/12</f>
+        <v>154331.581953557</v>
+      </c>
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="18" t="n">
@@ -17228,6 +22523,22 @@
         <f aca="false">L327+((G327+C328)+J327)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>120775.970549594</v>
       </c>
+      <c r="M328" s="19" t="n">
+        <f aca="false">(O327+C328)*(1+Předpoklady!$B$12)</f>
+        <v>3481258.94055729</v>
+      </c>
+      <c r="N328" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M328,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O328" s="19" t="n">
+        <f aca="false">M328*(1-N328/12)</f>
+        <v>3480040.4999281</v>
+      </c>
+      <c r="P328" s="19" t="n">
+        <f aca="false">P327+M328*N328/12</f>
+        <v>155550.022582752</v>
+      </c>
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="18" t="n">
@@ -17277,6 +22588,22 @@
         <f aca="false">L328+((G328+C329)+J328)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>121805.409906216</v>
       </c>
+      <c r="M329" s="19" t="n">
+        <f aca="false">(O328+C329)*(1+Předpoklady!$B$12)</f>
+        <v>3503739.7714503</v>
+      </c>
+      <c r="N329" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M329,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O329" s="19" t="n">
+        <f aca="false">M329*(1-N329/12)</f>
+        <v>3502513.46253029</v>
+      </c>
+      <c r="P329" s="19" t="n">
+        <f aca="false">P328+M329*N329/12</f>
+        <v>156776.331502759</v>
+      </c>
     </row>
     <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="18" t="n">
@@ -17326,6 +22653,22 @@
         <f aca="false">L329+((G329+C330)+J329)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>122843.226879245</v>
       </c>
+      <c r="M330" s="19" t="n">
+        <f aca="false">(O329+C330)*(1+Předpoklady!$B$12)</f>
+        <v>3526339.79945033</v>
+      </c>
+      <c r="N330" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M330,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O330" s="19" t="n">
+        <f aca="false">M330*(1-N330/12)</f>
+        <v>3525105.58052053</v>
+      </c>
+      <c r="P330" s="19" t="n">
+        <f aca="false">P329+M330*N330/12</f>
+        <v>158010.550432567</v>
+      </c>
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="18" t="n">
@@ -17375,6 +22718,22 @@
         <f aca="false">L330+((G330+C331)+J330)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>123887.656553236</v>
       </c>
+      <c r="M331" s="19" t="n">
+        <f aca="false">(O330+C331)*(1+Předpoklady!$B$12)</f>
+        <v>3549059.65656029</v>
+      </c>
+      <c r="N331" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M331,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O331" s="19" t="n">
+        <f aca="false">M331*(1-N331/12)</f>
+        <v>3547817.4856805</v>
+      </c>
+      <c r="P331" s="19" t="n">
+        <f aca="false">P330+M331*N331/12</f>
+        <v>159252.721312363</v>
+      </c>
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="18" t="n">
@@ -17424,6 +22783,22 @@
         <f aca="false">L331+((G331+C332)+J331)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>124938.734654839</v>
       </c>
+      <c r="M332" s="19" t="n">
+        <f aca="false">(O331+C332)*(1+Předpoklady!$B$12)</f>
+        <v>3571899.97813406</v>
+      </c>
+      <c r="N332" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M332,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O332" s="19" t="n">
+        <f aca="false">M332*(1-N332/12)</f>
+        <v>3570649.81314172</v>
+      </c>
+      <c r="P332" s="19" t="n">
+        <f aca="false">P331+M332*N332/12</f>
+        <v>160502.88630471</v>
+      </c>
     </row>
     <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="18" t="n">
@@ -17473,6 +22848,22 @@
         <f aca="false">L332+((G332+C333)+J332)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>125996.497103724</v>
       </c>
+      <c r="M333" s="19" t="n">
+        <f aca="false">(O332+C333)*(1+Předpoklady!$B$12)</f>
+        <v>3594861.40289428</v>
+      </c>
+      <c r="N333" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M333,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O333" s="19" t="n">
+        <f aca="false">M333*(1-N333/12)</f>
+        <v>3593603.20140327</v>
+      </c>
+      <c r="P333" s="19" t="n">
+        <f aca="false">P332+M333*N333/12</f>
+        <v>161761.087795723</v>
+      </c>
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="18" t="n">
@@ -17522,6 +22913,22 @@
         <f aca="false">L333+((G333+C334)+J333)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>127060.980013628</v>
       </c>
+      <c r="M334" s="19" t="n">
+        <f aca="false">(O333+C334)*(1+Předpoklady!$B$12)</f>
+        <v>3617944.5729502</v>
+      </c>
+      <c r="N334" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M334,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O334" s="19" t="n">
+        <f aca="false">M334*(1-N334/12)</f>
+        <v>3616678.29234966</v>
+      </c>
+      <c r="P334" s="19" t="n">
+        <f aca="false">P333+M334*N334/12</f>
+        <v>163027.368396256</v>
+      </c>
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="18" t="n">
@@ -17571,6 +22978,22 @@
         <f aca="false">L334+((G334+C335)+J334)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>128132.219693399</v>
       </c>
+      <c r="M335" s="19" t="n">
+        <f aca="false">(O334+C335)*(1+Předpoklady!$B$12)</f>
+        <v>3641150.13381563</v>
+      </c>
+      <c r="N335" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M335,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O335" s="19" t="n">
+        <f aca="false">M335*(1-N335/12)</f>
+        <v>3639875.73126879</v>
+      </c>
+      <c r="P335" s="19" t="n">
+        <f aca="false">P334+M335*N335/12</f>
+        <v>164301.770943091</v>
+      </c>
     </row>
     <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="18" t="n">
@@ -17620,6 +23043,22 @@
         <f aca="false">L335+((G335+C336)+J335)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>129210.252648054</v>
       </c>
+      <c r="M336" s="19" t="n">
+        <f aca="false">(O335+C336)*(1+Předpoklady!$B$12)</f>
+        <v>3664478.73442703</v>
+      </c>
+      <c r="N336" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M336,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O336" s="19" t="n">
+        <f aca="false">M336*(1-N336/12)</f>
+        <v>3663196.16686998</v>
+      </c>
+      <c r="P336" s="19" t="n">
+        <f aca="false">P335+M336*N336/12</f>
+        <v>165584.338500141</v>
+      </c>
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="18" t="n">
@@ -17669,6 +23108,22 @@
         <f aca="false">L336+((G336+C337)+J336)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>130295.115579835</v>
       </c>
+      <c r="M337" s="19" t="n">
+        <f aca="false">(O336+C337)*(1+Předpoklady!$B$12)</f>
+        <v>3687931.0271616</v>
+      </c>
+      <c r="N337" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M337,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O337" s="19" t="n">
+        <f aca="false">M337*(1-N337/12)</f>
+        <v>3686640.25130209</v>
+      </c>
+      <c r="P337" s="19" t="n">
+        <f aca="false">P336+M337*N337/12</f>
+        <v>166875.114359647</v>
+      </c>
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="18" t="n">
@@ -17718,6 +23173,22 @@
         <f aca="false">L337+((G337+C338)+J337)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>131386.845389277</v>
       </c>
+      <c r="M338" s="19" t="n">
+        <f aca="false">(O337+C338)*(1+Předpoklady!$B$12)</f>
+        <v>3711507.66785556</v>
+      </c>
+      <c r="N338" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M338,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O338" s="19" t="n">
+        <f aca="false">M338*(1-N338/12)</f>
+        <v>3710208.64017181</v>
+      </c>
+      <c r="P338" s="19" t="n">
+        <f aca="false">P337+M338*N338/12</f>
+        <v>168174.142043397</v>
+      </c>
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="18" t="n">
@@ -17767,6 +23238,22 @@
         <f aca="false">L338+((G338+C339)+J338)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>132485.479176279</v>
       </c>
+      <c r="M339" s="19" t="n">
+        <f aca="false">(O338+C339)*(1+Předpoklady!$B$12)</f>
+        <v>3735209.3158225</v>
+      </c>
+      <c r="N339" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M339,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O339" s="19" t="n">
+        <f aca="false">M339*(1-N339/12)</f>
+        <v>3733901.99256196</v>
+      </c>
+      <c r="P339" s="19" t="n">
+        <f aca="false">P338+M339*N339/12</f>
+        <v>169481.465303934</v>
+      </c>
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="18" t="n">
@@ -17816,6 +23303,22 @@
         <f aca="false">L339+((G339+C340)+J339)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>133591.054241179</v>
       </c>
+      <c r="M340" s="19" t="n">
+        <f aca="false">(O339+C340)*(1+Předpoklady!$B$12)</f>
+        <v>3759036.63387178</v>
+      </c>
+      <c r="N340" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M340,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O340" s="19" t="n">
+        <f aca="false">M340*(1-N340/12)</f>
+        <v>3757720.97104992</v>
+      </c>
+      <c r="P340" s="19" t="n">
+        <f aca="false">P339+M340*N340/12</f>
+        <v>170797.12812579</v>
+      </c>
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="18" t="n">
@@ -17865,6 +23368,22 @@
         <f aca="false">L340+((G340+C341)+J340)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>134703.608085842</v>
       </c>
+      <c r="M341" s="19" t="n">
+        <f aca="false">(O340+C341)*(1+Předpoklady!$B$12)</f>
+        <v>3782990.28832709</v>
+      </c>
+      <c r="N341" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M341,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O341" s="19" t="n">
+        <f aca="false">M341*(1-N341/12)</f>
+        <v>3781666.24172618</v>
+      </c>
+      <c r="P341" s="19" t="n">
+        <f aca="false">P340+M341*N341/12</f>
+        <v>172121.174726704</v>
+      </c>
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="18" t="n">
@@ -17914,6 +23433,22 @@
         <f aca="false">L341+((G341+C342)+J341)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>135824.988592204</v>
       </c>
+      <c r="M342" s="19" t="n">
+        <f aca="false">(O341+C342)*(1+Předpoklady!$B$12)</f>
+        <v>3807070.94904509</v>
+      </c>
+      <c r="N342" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M342,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O342" s="19" t="n">
+        <f aca="false">M342*(1-N342/12)</f>
+        <v>3805738.47421292</v>
+      </c>
+      <c r="P342" s="19" t="n">
+        <f aca="false">P341+M342*N342/12</f>
+        <v>173453.64955887</v>
+      </c>
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="18" t="n">
@@ -17963,6 +23498,22 @@
         <f aca="false">L342+((G342+C343)+J342)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>136953.433270891</v>
       </c>
+      <c r="M343" s="19" t="n">
+        <f aca="false">(O342+C343)*(1+Předpoklady!$B$12)</f>
+        <v>3831279.28943412</v>
+      </c>
+      <c r="N343" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M343,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O343" s="19" t="n">
+        <f aca="false">M343*(1-N343/12)</f>
+        <v>3829938.34168281</v>
+      </c>
+      <c r="P343" s="19" t="n">
+        <f aca="false">P342+M343*N343/12</f>
+        <v>174794.597310172</v>
+      </c>
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="18" t="n">
@@ -18012,6 +23563,22 @@
         <f aca="false">L343+((G343+C344)+J343)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>138088.980287731</v>
       </c>
+      <c r="M344" s="19" t="n">
+        <f aca="false">(O343+C344)*(1+Předpoklady!$B$12)</f>
+        <v>3855615.98647304</v>
+      </c>
+      <c r="N344" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M344,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O344" s="19" t="n">
+        <f aca="false">M344*(1-N344/12)</f>
+        <v>3854266.52087777</v>
+      </c>
+      <c r="P344" s="19" t="n">
+        <f aca="false">P343+M344*N344/12</f>
+        <v>176144.062905437</v>
+      </c>
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="18" t="n">
@@ -18061,6 +23628,22 @@
         <f aca="false">L344+((G344+C345)+J344)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>139231.668014753</v>
       </c>
+      <c r="M345" s="19" t="n">
+        <f aca="false">(O344+C345)*(1+Předpoklady!$B$12)</f>
+        <v>3880081.72073017</v>
+      </c>
+      <c r="N345" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M345,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O345" s="19" t="n">
+        <f aca="false">M345*(1-N345/12)</f>
+        <v>3878723.69212792</v>
+      </c>
+      <c r="P345" s="19" t="n">
+        <f aca="false">P344+M345*N345/12</f>
+        <v>177502.091507693</v>
+      </c>
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="18" t="n">
@@ -18110,6 +23693,22 @@
         <f aca="false">L345+((G345+C346)+J345)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>140381.535031298</v>
       </c>
+      <c r="M346" s="19" t="n">
+        <f aca="false">(O345+C346)*(1+Předpoklady!$B$12)</f>
+        <v>3904677.17638233</v>
+      </c>
+      <c r="N346" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M346,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O346" s="19" t="n">
+        <f aca="false">M346*(1-N346/12)</f>
+        <v>3903310.5393706</v>
+      </c>
+      <c r="P346" s="19" t="n">
+        <f aca="false">P345+M346*N346/12</f>
+        <v>178868.728519427</v>
+      </c>
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="18" t="n">
@@ -18159,6 +23758,22 @@
         <f aca="false">L346+((G346+C347)+J346)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>141538.620125144</v>
       </c>
+      <c r="M347" s="19" t="n">
+        <f aca="false">(O346+C347)*(1+Předpoklady!$B$12)</f>
+        <v>3929403.04123394</v>
+      </c>
+      <c r="N347" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M347,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O347" s="19" t="n">
+        <f aca="false">M347*(1-N347/12)</f>
+        <v>3928027.75016951</v>
+      </c>
+      <c r="P347" s="19" t="n">
+        <f aca="false">P346+M347*N347/12</f>
+        <v>180244.019583859</v>
+      </c>
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="18" t="n">
@@ -18208,6 +23823,22 @@
         <f aca="false">L347+((G347+C348)+J347)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>142702.962293626</v>
       </c>
+      <c r="M348" s="19" t="n">
+        <f aca="false">(O347+C348)*(1+Předpoklady!$B$12)</f>
+        <v>3954260.00673628</v>
+      </c>
+      <c r="N348" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M348,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O348" s="19" t="n">
+        <f aca="false">M348*(1-N348/12)</f>
+        <v>3952876.01573392</v>
+      </c>
+      <c r="P348" s="19" t="n">
+        <f aca="false">P347+M348*N348/12</f>
+        <v>181628.010586216</v>
+      </c>
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="18" t="n">
@@ -18257,6 +23888,22 @@
         <f aca="false">L348+((G348+C349)+J348)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>143874.600744772</v>
       </c>
+      <c r="M349" s="19" t="n">
+        <f aca="false">(O348+C349)*(1+Předpoklady!$B$12)</f>
+        <v>3979248.76800682</v>
+      </c>
+      <c r="N349" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M349,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O349" s="19" t="n">
+        <f aca="false">M349*(1-N349/12)</f>
+        <v>3977856.03093801</v>
+      </c>
+      <c r="P349" s="19" t="n">
+        <f aca="false">P348+M349*N349/12</f>
+        <v>183020.747655019</v>
+      </c>
     </row>
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="18" t="n">
@@ -18306,6 +23953,22 @@
         <f aca="false">L349+((G349+C350)+J349)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>145053.574898442</v>
       </c>
+      <c r="M350" s="19" t="n">
+        <f aca="false">(O349+C350)*(1+Předpoklady!$B$12)</f>
+        <v>4004370.02384865</v>
+      </c>
+      <c r="N350" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M350,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O350" s="19" t="n">
+        <f aca="false">M350*(1-N350/12)</f>
+        <v>4002968.49434031</v>
+      </c>
+      <c r="P350" s="19" t="n">
+        <f aca="false">P349+M350*N350/12</f>
+        <v>184422.277163366</v>
+      </c>
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="18" t="n">
@@ -18355,6 +24018,22 @@
         <f aca="false">L350+((G350+C351)+J350)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>146239.924387469</v>
       </c>
+      <c r="M351" s="19" t="n">
+        <f aca="false">(O350+C351)*(1+Předpoklady!$B$12)</f>
+        <v>4029624.47677006</v>
+      </c>
+      <c r="N351" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M351,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O351" s="19" t="n">
+        <f aca="false">M351*(1-N351/12)</f>
+        <v>4028214.10820319</v>
+      </c>
+      <c r="P351" s="19" t="n">
+        <f aca="false">P350+M351*N351/12</f>
+        <v>185832.645730235</v>
+      </c>
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="18" t="n">
@@ -18404,6 +24083,22 @@
         <f aca="false">L351+((G351+C352)+J351)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>147433.689058812</v>
       </c>
+      <c r="M352" s="19" t="n">
+        <f aca="false">(O351+C352)*(1+Předpoklady!$B$12)</f>
+        <v>4055012.83300412</v>
+      </c>
+      <c r="N352" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M352,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O352" s="19" t="n">
+        <f aca="false">M352*(1-N352/12)</f>
+        <v>4053593.57851257</v>
+      </c>
+      <c r="P352" s="19" t="n">
+        <f aca="false">P351+M352*N352/12</f>
+        <v>187251.900221787</v>
+      </c>
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="18" t="n">
@@ -18453,6 +24148,22 @@
         <f aca="false">L352+((G352+C353)+J352)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>148634.908974713</v>
       </c>
+      <c r="M353" s="19" t="n">
+        <f aca="false">(O352+C353)*(1+Předpoklady!$B$12)</f>
+        <v>4080535.80252848</v>
+      </c>
+      <c r="N353" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M353,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O353" s="19" t="n">
+        <f aca="false">M353*(1-N353/12)</f>
+        <v>4079107.61499759</v>
+      </c>
+      <c r="P353" s="19" t="n">
+        <f aca="false">P352+M353*N353/12</f>
+        <v>188680.087752672</v>
+      </c>
     </row>
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="18" t="n">
@@ -18502,6 +24213,22 @@
         <f aca="false">L353+((G353+C354)+J353)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>149845.434591321</v>
       </c>
+      <c r="M354" s="19" t="n">
+        <f aca="false">(O353+C354)*(1+Předpoklady!$B$12)</f>
+        <v>4106194.09908521</v>
+      </c>
+      <c r="N354" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M354,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O354" s="19" t="n">
+        <f aca="false">M354*(1-N354/12)</f>
+        <v>4104756.93115053</v>
+      </c>
+      <c r="P354" s="19" t="n">
+        <f aca="false">P353+M354*N354/12</f>
+        <v>190117.255687351</v>
+      </c>
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="18" t="n">
@@ -18551,6 +24278,22 @@
         <f aca="false">L354+((G354+C355)+J354)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>151063.506007379</v>
       </c>
+      <c r="M355" s="19" t="n">
+        <f aca="false">(O354+C355)*(1+Předpoklady!$B$12)</f>
+        <v>4131988.44020077</v>
+      </c>
+      <c r="N355" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M355,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O355" s="19" t="n">
+        <f aca="false">M355*(1-N355/12)</f>
+        <v>4130542.2442467</v>
+      </c>
+      <c r="P355" s="19" t="n">
+        <f aca="false">P354+M355*N355/12</f>
+        <v>191563.451641422</v>
+      </c>
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="18" t="n">
@@ -18600,6 +24343,22 @@
         <f aca="false">L355+((G355+C356)+J355)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>152289.16399082</v>
       </c>
+      <c r="M356" s="19" t="n">
+        <f aca="false">(O355+C356)*(1+Předpoklady!$B$12)</f>
+        <v>4157919.54720604</v>
+      </c>
+      <c r="N356" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M356,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O356" s="19" t="n">
+        <f aca="false">M356*(1-N356/12)</f>
+        <v>4156464.27536451</v>
+      </c>
+      <c r="P356" s="19" t="n">
+        <f aca="false">P355+M356*N356/12</f>
+        <v>193018.723482944</v>
+      </c>
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="18" t="n">
@@ -18649,6 +24408,22 @@
         <f aca="false">L356+((G356+C357)+J356)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>153522.449529831</v>
       </c>
+      <c r="M357" s="19" t="n">
+        <f aca="false">(O356+C357)*(1+Předpoklady!$B$12)</f>
+        <v>4183988.14525653</v>
+      </c>
+      <c r="N357" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M357,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O357" s="19" t="n">
+        <f aca="false">M357*(1-N357/12)</f>
+        <v>4182523.74940569</v>
+      </c>
+      <c r="P357" s="19" t="n">
+        <f aca="false">P356+M357*N357/12</f>
+        <v>194483.119333784</v>
+      </c>
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="18" t="n">
@@ -18698,6 +24473,22 @@
         <f aca="false">L357+((G357+C358)+J357)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>154763.403834051</v>
       </c>
+      <c r="M358" s="19" t="n">
+        <f aca="false">(O357+C358)*(1+Předpoklady!$B$12)</f>
+        <v>4210194.96335266</v>
+      </c>
+      <c r="N358" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M358,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O358" s="19" t="n">
+        <f aca="false">M358*(1-N358/12)</f>
+        <v>4208721.39511548</v>
+      </c>
+      <c r="P358" s="19" t="n">
+        <f aca="false">P357+M358*N358/12</f>
+        <v>195956.687570957</v>
+      </c>
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="18" t="n">
@@ -18747,6 +24538,22 @@
         <f aca="false">L358+((G358+C359)+J358)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>156012.068335761</v>
       </c>
+      <c r="M359" s="19" t="n">
+        <f aca="false">(O358+C359)*(1+Předpoklady!$B$12)</f>
+        <v>4236540.7343601</v>
+      </c>
+      <c r="N359" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M359,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O359" s="19" t="n">
+        <f aca="false">M359*(1-N359/12)</f>
+        <v>4235057.94510307</v>
+      </c>
+      <c r="P359" s="19" t="n">
+        <f aca="false">P358+M359*N359/12</f>
+        <v>197439.476827983</v>
+      </c>
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="18" t="n">
@@ -18796,6 +24603,22 @@
         <f aca="false">L359+((G359+C360)+J359)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>157268.484691092</v>
       </c>
+      <c r="M360" s="19" t="n">
+        <f aca="false">(O359+C360)*(1+Předpoklady!$B$12)</f>
+        <v>4263026.19503032</v>
+      </c>
+      <c r="N360" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M360,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O360" s="19" t="n">
+        <f aca="false">M360*(1-N360/12)</f>
+        <v>4261534.13586206</v>
+      </c>
+      <c r="P360" s="19" t="n">
+        <f aca="false">P359+M360*N360/12</f>
+        <v>198931.535996244</v>
+      </c>
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="18" t="n">
@@ -18844,6 +24667,22 @@
       <c r="L361" s="19" t="n">
         <f aca="false">L360+((G360+C361)+J360)*(1+Předpoklady!$B$12)*Předpoklady!$B$9/12</f>
         <v>158532.694781229</v>
+      </c>
+      <c r="M361" s="19" t="n">
+        <f aca="false">(O360+C361)*(1+Předpoklady!$B$12)</f>
+        <v>4289652.08602116</v>
+      </c>
+      <c r="N361" s="13" t="n">
+        <f aca="false">INDEX(Předpoklady!$D$18:$D$21,MATCH(M361,Předpoklady!$A$18:$A$21,1))</f>
+        <v>0.0042</v>
+      </c>
+      <c r="O361" s="19" t="n">
+        <f aca="false">M361*(1-N361/12)</f>
+        <v>4288150.70779106</v>
+      </c>
+      <c r="P361" s="19" t="n">
+        <f aca="false">P360+M361*N361/12</f>
+        <v>200432.914226351</v>
       </c>
     </row>
   </sheetData>
@@ -18862,7 +24701,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -18873,38 +24712,53 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J1" s="15" t="s">
-        <v>58</v>
+        <v>61</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18945,6 +24799,22 @@
       </c>
       <c r="J2" s="19" t="n">
         <f aca="false">IF(A2=0,0,INDEX(Měsíce!$L$2:$L$361,B2))</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="19" t="n">
+        <f aca="false">IF(A2=0,0,INDEX(Měsíce!$O$2:$O$361,B2))</f>
+        <v>0</v>
+      </c>
+      <c r="L2" s="19" t="n">
+        <f aca="false">E2-K2</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="19" t="n">
+        <f aca="false">F2-K2</f>
+        <v>0</v>
+      </c>
+      <c r="N2" s="19" t="n">
+        <f aca="false">IF(A2=0,0,INDEX(Měsíce!$P$2:$P$361,B2))</f>
         <v>0</v>
       </c>
     </row>
@@ -18988,6 +24858,22 @@
         <f aca="false">IF(A3=0,0,INDEX(Měsíce!$L$2:$L$361,B3))</f>
         <v>80.0161354247323</v>
       </c>
+      <c r="K3" s="19" t="n">
+        <f aca="false">IF(A3=0,0,INDEX(Měsíce!$O$2:$O$361,B3))</f>
+        <v>49610.817474814</v>
+      </c>
+      <c r="L3" s="19" t="n">
+        <f aca="false">E3-K3</f>
+        <v>7308.68311270174</v>
+      </c>
+      <c r="M3" s="19" t="n">
+        <f aca="false">F3-K3</f>
+        <v>7308.68311270174</v>
+      </c>
+      <c r="N3" s="19" t="n">
+        <f aca="false">IF(A3=0,0,INDEX(Měsíce!$P$2:$P$361,B3))</f>
+        <v>186.47337627469</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="n">
@@ -19029,6 +24915,22 @@
         <f aca="false">IF(A4=0,0,INDEX(Měsíce!$L$2:$L$361,B4))</f>
         <v>329.330938122363</v>
       </c>
+      <c r="K4" s="19" t="n">
+        <f aca="false">IF(A4=0,0,INDEX(Měsíce!$O$2:$O$361,B4))</f>
+        <v>102323.997003528</v>
+      </c>
+      <c r="L4" s="19" t="n">
+        <f aca="false">E4-K4</f>
+        <v>14835.988882418</v>
+      </c>
+      <c r="M4" s="19" t="n">
+        <f aca="false">F4-K4</f>
+        <v>15153.1348597224</v>
+      </c>
+      <c r="N4" s="19" t="n">
+        <f aca="false">IF(A4=0,0,INDEX(Měsíce!$P$2:$P$361,B4))</f>
+        <v>732.086093699116</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="n">
@@ -19070,6 +24972,22 @@
         <f aca="false">IF(A5=0,0,INDEX(Měsíce!$L$2:$L$361,B5))</f>
         <v>766.873746808518</v>
       </c>
+      <c r="K5" s="19" t="n">
+        <f aca="false">IF(A5=0,0,INDEX(Měsíce!$O$2:$O$361,B5))</f>
+        <v>158333.541644413</v>
+      </c>
+      <c r="L5" s="19" t="n">
+        <f aca="false">E5-K5</f>
+        <v>22609.7374655069</v>
+      </c>
+      <c r="M5" s="19" t="n">
+        <f aca="false">F5-K5</f>
+        <v>23746.1327511095</v>
+      </c>
+      <c r="N5" s="19" t="n">
+        <f aca="false">IF(A5=0,0,INDEX(Měsíce!$P$2:$P$361,B5))</f>
+        <v>1659.29656599749</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="n">
@@ -19111,6 +25029,22 @@
         <f aca="false">IF(A6=0,0,INDEX(Měsíce!$L$2:$L$361,B6))</f>
         <v>1405.21714010259</v>
       </c>
+      <c r="K6" s="19" t="n">
+        <f aca="false">IF(A6=0,0,INDEX(Měsíce!$O$2:$O$361,B6))</f>
+        <v>217845.586239835</v>
+      </c>
+      <c r="L6" s="19" t="n">
+        <f aca="false">E6-K6</f>
+        <v>30660.4337849953</v>
+      </c>
+      <c r="M6" s="19" t="n">
+        <f aca="false">F6-K6</f>
+        <v>33151.7194056796</v>
+      </c>
+      <c r="N6" s="19" t="n">
+        <f aca="false">IF(A6=0,0,INDEX(Měsíce!$P$2:$P$361,B6))</f>
+        <v>2991.96762097293</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="n">
@@ -19152,6 +25086,22 @@
         <f aca="false">IF(A7=0,0,INDEX(Měsíce!$L$2:$L$361,B7))</f>
         <v>2257.77347459598</v>
       </c>
+      <c r="K7" s="19" t="n">
+        <f aca="false">IF(A7=0,0,INDEX(Měsíce!$O$2:$O$361,B7))</f>
+        <v>281079.156065043</v>
+      </c>
+      <c r="L7" s="19" t="n">
+        <f aca="false">E7-K7</f>
+        <v>39021.4985445552</v>
+      </c>
+      <c r="M7" s="19" t="n">
+        <f aca="false">F7-K7</f>
+        <v>43439.0933535004</v>
+      </c>
+      <c r="N7" s="19" t="n">
+        <f aca="false">IF(A7=0,0,INDEX(Měsíce!$P$2:$P$361,B7))</f>
+        <v>4755.45432411471</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="n">
@@ -19193,6 +25143,22 @@
         <f aca="false">IF(A8=0,0,INDEX(Měsíce!$L$2:$L$361,B8))</f>
         <v>3338.85097732629</v>
       </c>
+      <c r="K8" s="19" t="n">
+        <f aca="false">IF(A8=0,0,INDEX(Měsíce!$O$2:$O$361,B8))</f>
+        <v>348266.97291829</v>
+      </c>
+      <c r="L8" s="19" t="n">
+        <f aca="false">E8-K8</f>
+        <v>47729.5179050936</v>
+      </c>
+      <c r="M8" s="19" t="n">
+        <f aca="false">F8-K8</f>
+        <v>54683.008340682</v>
+      </c>
+      <c r="N8" s="19" t="n">
+        <f aca="false">IF(A8=0,0,INDEX(Měsíce!$P$2:$P$361,B8))</f>
+        <v>6976.69729416542</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="n">
@@ -19234,6 +25200,22 @@
         <f aca="false">IF(A9=0,0,INDEX(Měsíce!$L$2:$L$361,B9))</f>
         <v>4663.71358491532</v>
       </c>
+      <c r="K9" s="19" t="n">
+        <f aca="false">IF(A9=0,0,INDEX(Měsíce!$O$2:$O$361,B9))</f>
+        <v>419656.311618978</v>
+      </c>
+      <c r="L9" s="19" t="n">
+        <f aca="false">E9-K9</f>
+        <v>56824.5132726261</v>
+      </c>
+      <c r="M9" s="19" t="n">
+        <f aca="false">F9-K9</f>
+        <v>66964.2027397807</v>
+      </c>
+      <c r="N9" s="19" t="n">
+        <f aca="false">IF(A9=0,0,INDEX(Měsíce!$P$2:$P$361,B9))</f>
+        <v>9684.32185408238</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="n">
@@ -19275,6 +25257,22 @@
         <f aca="false">IF(A10=0,0,INDEX(Měsíce!$L$2:$L$361,B10))</f>
         <v>6248.64477962692</v>
       </c>
+      <c r="K10" s="19" t="n">
+        <f aca="false">IF(A10=0,0,INDEX(Měsíce!$O$2:$O$361,B10))</f>
+        <v>495509.910066051</v>
+      </c>
+      <c r="L10" s="19" t="n">
+        <f aca="false">E10-K10</f>
+        <v>66350.2327555233</v>
+      </c>
+      <c r="M10" s="19" t="n">
+        <f aca="false">F10-K10</f>
+        <v>80369.8612914683</v>
+      </c>
+      <c r="N10" s="19" t="n">
+        <f aca="false">IF(A10=0,0,INDEX(Měsíce!$P$2:$P$361,B10))</f>
+        <v>12908.7433823036</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="n">
@@ -19316,6 +25314,22 @@
         <f aca="false">IF(A11=0,0,INDEX(Měsíce!$L$2:$L$361,B11))</f>
         <v>8111.0156893167</v>
       </c>
+      <c r="K11" s="19" t="n">
+        <f aca="false">IF(A11=0,0,INDEX(Měsíce!$O$2:$O$361,B11))</f>
+        <v>576882.943377932</v>
+      </c>
+      <c r="L11" s="19" t="n">
+        <f aca="false">E11-K11</f>
+        <v>75578.4587947273</v>
+      </c>
+      <c r="M11" s="19" t="n">
+        <f aca="false">F11-K11</f>
+        <v>94218.1043932177</v>
+      </c>
+      <c r="N11" s="19" t="n">
+        <f aca="false">IF(A11=0,0,INDEX(Měsíce!$P$2:$P$361,B11))</f>
+        <v>15929.5000452207</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="n">
@@ -19357,6 +25371,22 @@
         <f aca="false">IF(A12=0,0,INDEX(Měsíce!$L$2:$L$361,B12))</f>
         <v>10269.3577360777</v>
       </c>
+      <c r="K12" s="19" t="n">
+        <f aca="false">IF(A12=0,0,INDEX(Měsíce!$O$2:$O$361,B12))</f>
+        <v>663465.751335199</v>
+      </c>
+      <c r="L12" s="19" t="n">
+        <f aca="false">E12-K12</f>
+        <v>85167.6481063255</v>
+      </c>
+      <c r="M12" s="19" t="n">
+        <f aca="false">F12-K12</f>
+        <v>109216.821834118</v>
+      </c>
+      <c r="N12" s="19" t="n">
+        <f aca="false">IF(A12=0,0,INDEX(Měsíce!$P$2:$P$361,B12))</f>
+        <v>19421.8189220149</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="n">
@@ -19398,6 +25428,22 @@
         <f aca="false">IF(A13=0,0,INDEX(Měsíce!$L$2:$L$361,B13))</f>
         <v>12743.4401374096</v>
       </c>
+      <c r="K13" s="19" t="n">
+        <f aca="false">IF(A13=0,0,INDEX(Měsíce!$O$2:$O$361,B13))</f>
+        <v>755591.881192402</v>
+      </c>
+      <c r="L13" s="19" t="n">
+        <f aca="false">E13-K13</f>
+        <v>95156.3475886608</v>
+      </c>
+      <c r="M13" s="19" t="n">
+        <f aca="false">F13-K13</f>
+        <v>125457.295438463</v>
+      </c>
+      <c r="N13" s="19" t="n">
+        <f aca="false">IF(A13=0,0,INDEX(Měsíce!$P$2:$P$361,B13))</f>
+        <v>23415.8910079778</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="n">
@@ -19439,6 +25485,22 @@
         <f aca="false">IF(A14=0,0,INDEX(Měsíce!$L$2:$L$361,B14))</f>
         <v>15554.3525840323</v>
       </c>
+      <c r="K14" s="19" t="n">
+        <f aca="false">IF(A14=0,0,INDEX(Měsíce!$O$2:$O$361,B14))</f>
+        <v>853616.235018572</v>
+      </c>
+      <c r="L14" s="19" t="n">
+        <f aca="false">E14-K14</f>
+        <v>105586.603135034</v>
+      </c>
+      <c r="M14" s="19" t="n">
+        <f aca="false">F14-K14</f>
+        <v>143037.828423773</v>
+      </c>
+      <c r="N14" s="19" t="n">
+        <f aca="false">IF(A14=0,0,INDEX(Měsíce!$P$2:$P$361,B14))</f>
+        <v>27943.8402272275</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="n">
@@ -19480,6 +25542,22 @@
         <f aca="false">IF(A15=0,0,INDEX(Měsíce!$L$2:$L$361,B15))</f>
         <v>18724.5934401164</v>
       </c>
+      <c r="K15" s="19" t="n">
+        <f aca="false">IF(A15=0,0,INDEX(Měsíce!$O$2:$O$361,B15))</f>
+        <v>957916.436904092</v>
+      </c>
+      <c r="L15" s="19" t="n">
+        <f aca="false">E15-K15</f>
+        <v>116504.252522363</v>
+      </c>
+      <c r="M15" s="19" t="n">
+        <f aca="false">F15-K15</f>
+        <v>162064.27356597</v>
+      </c>
+      <c r="N15" s="19" t="n">
+        <f aca="false">IF(A15=0,0,INDEX(Měsíce!$P$2:$P$361,B15))</f>
+        <v>33039.847185298</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="n">
@@ -19521,6 +25599,22 @@
         <f aca="false">IF(A16=0,0,INDEX(Měsíce!$L$2:$L$361,B16))</f>
         <v>22278.1638347945</v>
       </c>
+      <c r="K16" s="19" t="n">
+        <f aca="false">IF(A16=0,0,INDEX(Měsíce!$O$2:$O$361,B16))</f>
+        <v>1069879.510532</v>
+      </c>
+      <c r="L16" s="19" t="n">
+        <f aca="false">E16-K16</f>
+        <v>126974.018820531</v>
+      </c>
+      <c r="M16" s="19" t="n">
+        <f aca="false">F16-K16</f>
+        <v>181665.377600395</v>
+      </c>
+      <c r="N16" s="19" t="n">
+        <f aca="false">IF(A16=0,0,INDEX(Měsíce!$P$2:$P$361,B16))</f>
+        <v>37774.1414922147</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="n">
@@ -19562,6 +25656,22 @@
         <f aca="false">IF(A17=0,0,INDEX(Měsíce!$L$2:$L$361,B17))</f>
         <v>26240.6680384611</v>
       </c>
+      <c r="K17" s="19" t="n">
+        <f aca="false">IF(A17=0,0,INDEX(Měsíce!$O$2:$O$361,B17))</f>
+        <v>1189659.1500063</v>
+      </c>
+      <c r="L17" s="19" t="n">
+        <f aca="false">E17-K17</f>
+        <v>137324.128836313</v>
+      </c>
+      <c r="M17" s="19" t="n">
+        <f aca="false">F17-K17</f>
+        <v>202237.667422247</v>
+      </c>
+      <c r="N17" s="19" t="n">
+        <f aca="false">IF(A17=0,0,INDEX(Měsíce!$P$2:$P$361,B17))</f>
+        <v>42539.1601877979</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="n">
@@ -19603,6 +25713,22 @@
         <f aca="false">IF(A18=0,0,INDEX(Měsíce!$L$2:$L$361,B18))</f>
         <v>30639.4205436467</v>
       </c>
+      <c r="K18" s="19" t="n">
+        <f aca="false">IF(A18=0,0,INDEX(Měsíce!$O$2:$O$361,B18))</f>
+        <v>1317286.10954372</v>
+      </c>
+      <c r="L18" s="19" t="n">
+        <f aca="false">E18-K18</f>
+        <v>148037.938886705</v>
+      </c>
+      <c r="M18" s="19" t="n">
+        <f aca="false">F18-K18</f>
+        <v>224337.361501056</v>
+      </c>
+      <c r="N18" s="19" t="n">
+        <f aca="false">IF(A18=0,0,INDEX(Měsíce!$P$2:$P$361,B18))</f>
+        <v>47825.1152810118</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="n">
@@ -19644,6 +25770,22 @@
         <f aca="false">IF(A19=0,0,INDEX(Měsíce!$L$2:$L$361,B19))</f>
         <v>35503.5602982971</v>
       </c>
+      <c r="K19" s="19" t="n">
+        <f aca="false">IF(A19=0,0,INDEX(Měsíce!$O$2:$O$361,B19))</f>
+        <v>1453274.50349994</v>
+      </c>
+      <c r="L19" s="19" t="n">
+        <f aca="false">E19-K19</f>
+        <v>159149.784859551</v>
+      </c>
+      <c r="M19" s="19" t="n">
+        <f aca="false">F19-K19</f>
+        <v>248076.5246617</v>
+      </c>
+      <c r="N19" s="19" t="n">
+        <f aca="false">IF(A19=0,0,INDEX(Měsíce!$P$2:$P$361,B19))</f>
+        <v>53666.135732861</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="n">
@@ -19685,6 +25827,22 @@
         <f aca="false">IF(A20=0,0,INDEX(Měsíce!$L$2:$L$361,B20))</f>
         <v>40864.1725691962</v>
       </c>
+      <c r="K20" s="19" t="n">
+        <f aca="false">IF(A20=0,0,INDEX(Měsíce!$O$2:$O$361,B20))</f>
+        <v>1598172.12824804</v>
+      </c>
+      <c r="L20" s="19" t="n">
+        <f aca="false">E20-K20</f>
+        <v>170696.954035789</v>
+      </c>
+      <c r="M20" s="19" t="n">
+        <f aca="false">F20-K20</f>
+        <v>273575.364980645</v>
+      </c>
+      <c r="N20" s="19" t="n">
+        <f aca="false">IF(A20=0,0,INDEX(Měsíce!$P$2:$P$361,B20))</f>
+        <v>60098.5864509732</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="18" t="n">
@@ -19726,6 +25884,22 @@
         <f aca="false">IF(A21=0,0,INDEX(Měsíce!$L$2:$L$361,B21))</f>
         <v>46754.4189451848</v>
       </c>
+      <c r="K21" s="19" t="n">
+        <f aca="false">IF(A21=0,0,INDEX(Měsíce!$O$2:$O$361,B21))</f>
+        <v>1752562.66884372</v>
+      </c>
+      <c r="L21" s="19" t="n">
+        <f aca="false">E21-K21</f>
+        <v>182719.925331222</v>
+      </c>
+      <c r="M21" s="19" t="n">
+        <f aca="false">F21-K21</f>
+        <v>300962.820814839</v>
+      </c>
+      <c r="N21" s="19" t="n">
+        <f aca="false">IF(A21=0,0,INDEX(Měsíce!$P$2:$P$361,B21))</f>
+        <v>67161.2147768392</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="18" t="n">
@@ -19767,6 +25941,22 @@
         <f aca="false">IF(A22=0,0,INDEX(Měsíce!$L$2:$L$361,B22))</f>
         <v>53209.6760238674</v>
       </c>
+      <c r="K22" s="19" t="n">
+        <f aca="false">IF(A22=0,0,INDEX(Měsíce!$O$2:$O$361,B22))</f>
+        <v>1917068.05025951</v>
+      </c>
+      <c r="L22" s="19" t="n">
+        <f aca="false">E22-K22</f>
+        <v>195262.628409118</v>
+      </c>
+      <c r="M22" s="19" t="n">
+        <f aca="false">F22-K22</f>
+        <v>330377.189864886</v>
+      </c>
+      <c r="N22" s="19" t="n">
+        <f aca="false">IF(A22=0,0,INDEX(Měsíce!$P$2:$P$361,B22))</f>
+        <v>74895.3065701124</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="18" t="n">
@@ -19808,6 +25998,22 @@
         <f aca="false">IF(A23=0,0,INDEX(Měsíce!$L$2:$L$361,B23))</f>
         <v>60267.6833618159</v>
       </c>
+      <c r="K23" s="19" t="n">
+        <f aca="false">IF(A23=0,0,INDEX(Měsíce!$O$2:$O$361,B23))</f>
+        <v>2092350.94265915</v>
+      </c>
+      <c r="L23" s="19" t="n">
+        <f aca="false">E23-K23</f>
+        <v>208372.723109115</v>
+      </c>
+      <c r="M23" s="19" t="n">
+        <f aca="false">F23-K23</f>
+        <v>361966.803265141</v>
+      </c>
+      <c r="N23" s="19" t="n">
+        <f aca="false">IF(A23=0,0,INDEX(Měsíce!$P$2:$P$361,B23))</f>
+        <v>83344.8525187141</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="18" t="n">
@@ -19849,6 +26055,22 @@
         <f aca="false">IF(A24=0,0,INDEX(Měsíce!$L$2:$L$361,B24))</f>
         <v>67968.7013070198</v>
       </c>
+      <c r="K24" s="19" t="n">
+        <f aca="false">IF(A24=0,0,INDEX(Měsíce!$O$2:$O$361,B24))</f>
+        <v>2279117.43080415</v>
+      </c>
+      <c r="L24" s="19" t="n">
+        <f aca="false">E24-K24</f>
+        <v>222101.900746597</v>
+      </c>
+      <c r="M24" s="19" t="n">
+        <f aca="false">F24-K24</f>
+        <v>395890.747905447</v>
+      </c>
+      <c r="N24" s="19" t="n">
+        <f aca="false">IF(A24=0,0,INDEX(Měsíce!$P$2:$P$361,B24))</f>
+        <v>92556.725344686</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="18" t="n">
@@ -19890,6 +26112,22 @@
         <f aca="false">IF(A25=0,0,INDEX(Měsíce!$L$2:$L$361,B25))</f>
         <v>76355.6793736621</v>
       </c>
+      <c r="K25" s="19" t="n">
+        <f aca="false">IF(A25=0,0,INDEX(Měsíce!$O$2:$O$361,B25))</f>
+        <v>2478119.85834563</v>
+      </c>
+      <c r="L25" s="19" t="n">
+        <f aca="false">E25-K25</f>
+        <v>236506.208953402</v>
+      </c>
+      <c r="M25" s="19" t="n">
+        <f aca="false">F25-K25</f>
+        <v>432319.640416142</v>
+      </c>
+      <c r="N25" s="19" t="n">
+        <f aca="false">IF(A25=0,0,INDEX(Měsíce!$P$2:$P$361,B25))</f>
+        <v>102580.868619621</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="18" t="n">
@@ -19931,6 +26169,22 @@
         <f aca="false">IF(A26=0,0,INDEX(Měsíce!$L$2:$L$361,B26))</f>
         <v>85474.4358633885</v>
       </c>
+      <c r="K26" s="19" t="n">
+        <f aca="false">IF(A26=0,0,INDEX(Měsíce!$O$2:$O$361,B26))</f>
+        <v>2690159.85845877</v>
+      </c>
+      <c r="L26" s="19" t="n">
+        <f aca="false">E26-K26</f>
+        <v>251646.401856111</v>
+      </c>
+      <c r="M26" s="19" t="n">
+        <f aca="false">F26-K26</f>
+        <v>471436.456490977</v>
+      </c>
+      <c r="N26" s="19" t="n">
+        <f aca="false">IF(A26=0,0,INDEX(Měsíce!$P$2:$P$361,B26))</f>
+        <v>113470.497950268</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="18" t="n">
@@ -19972,6 +26226,22 @@
         <f aca="false">IF(A27=0,0,INDEX(Měsíce!$L$2:$L$361,B27))</f>
         <v>95373.8494842738</v>
       </c>
+      <c r="K27" s="19" t="n">
+        <f aca="false">IF(A27=0,0,INDEX(Měsíce!$O$2:$O$361,B27))</f>
+        <v>2916091.58302839</v>
+      </c>
+      <c r="L27" s="19" t="n">
+        <f aca="false">E27-K27</f>
+        <v>267588.317522801</v>
+      </c>
+      <c r="M27" s="19" t="n">
+        <f aca="false">F27-K27</f>
+        <v>513437.419482671</v>
+      </c>
+      <c r="N27" s="19" t="n">
+        <f aca="false">IF(A27=0,0,INDEX(Měsíce!$P$2:$P$361,B27))</f>
+        <v>125282.315344742</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="n">
@@ -20013,6 +26283,22 @@
         <f aca="false">IF(A28=0,0,INDEX(Měsíce!$L$2:$L$361,B28))</f>
         <v>106106.063768864</v>
       </c>
+      <c r="K28" s="19" t="n">
+        <f aca="false">IF(A28=0,0,INDEX(Měsíce!$O$2:$O$361,B28))</f>
+        <v>3156825.14339323</v>
+      </c>
+      <c r="L28" s="19" t="n">
+        <f aca="false">E28-K28</f>
+        <v>284403.284753754</v>
+      </c>
+      <c r="M28" s="19" t="n">
+        <f aca="false">F28-K28</f>
+        <v>558532.952484325</v>
+      </c>
+      <c r="N28" s="19" t="n">
+        <f aca="false">IF(A28=0,0,INDEX(Měsíce!$P$2:$P$361,B28))</f>
+        <v>138076.737622853</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="18" t="n">
@@ -20054,6 +26340,22 @@
         <f aca="false">IF(A29=0,0,INDEX(Měsíce!$L$2:$L$361,B29))</f>
         <v>117726.7051462</v>
       </c>
+      <c r="K29" s="19" t="n">
+        <f aca="false">IF(A29=0,0,INDEX(Měsíce!$O$2:$O$361,B29))</f>
+        <v>3413330.27650956</v>
+      </c>
+      <c r="L29" s="19" t="n">
+        <f aca="false">E29-K29</f>
+        <v>302168.561446853</v>
+      </c>
+      <c r="M29" s="19" t="n">
+        <f aca="false">F29-K29</f>
+        <v>606948.698407868</v>
+      </c>
+      <c r="N29" s="19" t="n">
+        <f aca="false">IF(A29=0,0,INDEX(Měsíce!$P$2:$P$361,B29))</f>
+        <v>151918.139790666</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="18" t="n">
@@ -20095,6 +26397,22 @@
         <f aca="false">IF(A30=0,0,INDEX(Měsíce!$L$2:$L$361,B30))</f>
         <v>130295.115579835</v>
       </c>
+      <c r="K30" s="19" t="n">
+        <f aca="false">IF(A30=0,0,INDEX(Měsíce!$O$2:$O$361,B30))</f>
+        <v>3686640.25130209</v>
+      </c>
+      <c r="L30" s="19" t="n">
+        <f aca="false">E30-K30</f>
+        <v>320967.80693519</v>
+      </c>
+      <c r="M30" s="19" t="n">
+        <f aca="false">F30-K30</f>
+        <v>658926.612889918</v>
+      </c>
+      <c r="N30" s="19" t="n">
+        <f aca="false">IF(A30=0,0,INDEX(Měsíce!$P$2:$P$361,B30))</f>
+        <v>166875.114359647</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="18" t="n">
@@ -20136,6 +26454,22 @@
         <f aca="false">IF(A31=0,0,INDEX(Měsíce!$L$2:$L$361,B31))</f>
         <v>143874.600744772</v>
       </c>
+      <c r="K31" s="19" t="n">
+        <f aca="false">IF(A31=0,0,INDEX(Měsíce!$O$2:$O$361,B31))</f>
+        <v>3977856.03093801</v>
+      </c>
+      <c r="L31" s="19" t="n">
+        <f aca="false">E31-K31</f>
+        <v>340891.590873416</v>
+      </c>
+      <c r="M31" s="19" t="n">
+        <f aca="false">F31-K31</f>
+        <v>714726.135196863</v>
+      </c>
+      <c r="N31" s="19" t="n">
+        <f aca="false">IF(A31=0,0,INDEX(Měsíce!$P$2:$P$361,B31))</f>
+        <v>183020.747655019</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="18" t="n">
@@ -20177,10 +26511,26 @@
         <f aca="false">IF(A32=0,0,INDEX(Měsíce!$L$2:$L$361,B32))</f>
         <v>158532.694781229</v>
       </c>
+      <c r="K32" s="19" t="n">
+        <f aca="false">IF(A32=0,0,INDEX(Měsíce!$O$2:$O$361,B32))</f>
+        <v>4288150.70779106</v>
+      </c>
+      <c r="L32" s="19" t="n">
+        <f aca="false">E32-K32</f>
+        <v>362037.941441589</v>
+      </c>
+      <c r="M32" s="19" t="n">
+        <f aca="false">F32-K32</f>
+        <v>774625.442666594</v>
+      </c>
+      <c r="N32" s="19" t="n">
+        <f aca="false">IF(A32=0,0,INDEX(Měsíce!$P$2:$P$361,B32))</f>
+        <v>200432.914226351</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
